--- a/src/attributions/attributions_saliency_traj_114.xlsx
+++ b/src/attributions/attributions_saliency_traj_114.xlsx
@@ -2137,2278 +2137,2278 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1.24121579574421e-05</v>
+        <v>1.82538843872546e-24</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0008697346784174442</v>
+        <v>1.095959032204828e-24</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001382184127578512</v>
+        <v>2.835554015714459e-24</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003143299254588783</v>
+        <v>1.781619477475404e-24</v>
       </c>
       <c r="E4" t="n">
-        <v>5.928600148763508e-05</v>
+        <v>1.633548510628383e-25</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004969347501173615</v>
+        <v>3.385354913039415e-25</v>
       </c>
       <c r="G4" t="n">
-        <v>2.718000905588269e-05</v>
+        <v>2.722782207793363e-24</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0001321922754868865</v>
+        <v>2.552888390079534e-24</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001335984852630645</v>
+        <v>1.419243204457196e-24</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0001618679380044341</v>
+        <v>5.812183182553212e-25</v>
       </c>
       <c r="K4" t="n">
-        <v>0.000547311850823462</v>
+        <v>3.145006991107973e-25</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001496193581260741</v>
+        <v>3.230721461625667e-24</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0004052827425766736</v>
+        <v>1.475438894331972e-24</v>
       </c>
       <c r="N4" t="n">
-        <v>5.306148523231968e-05</v>
+        <v>4.746003649520477e-25</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0004233551444485784</v>
+        <v>1.066531660819303e-24</v>
       </c>
       <c r="P4" t="n">
-        <v>5.463894922286272e-06</v>
+        <v>3.804939230992831e-24</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0001991783065022901</v>
+        <v>2.41455413617043e-24</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0001041036884998903</v>
+        <v>5.730368199401445e-26</v>
       </c>
       <c r="S4" t="n">
-        <v>1.280580363527406e-05</v>
+        <v>1.382995538900356e-24</v>
       </c>
       <c r="T4" t="n">
-        <v>3.277830546721816e-05</v>
+        <v>1.800729435689156e-24</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0001273156813113019</v>
+        <v>1.324763799029204e-24</v>
       </c>
       <c r="V4" t="n">
-        <v>0.000125619990285486</v>
+        <v>5.328095236797878e-25</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0001818337332224473</v>
+        <v>1.803264242992858e-24</v>
       </c>
       <c r="X4" t="n">
-        <v>8.226640056818724e-05</v>
+        <v>7.975957155054912e-25</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0001275142712984234</v>
+        <v>6.436708583998583e-25</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0002016297949012369</v>
+        <v>4.385631280416757e-25</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.958483860827982e-05</v>
+        <v>5.061553435027605e-25</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.067039167741314e-05</v>
+        <v>2.264639206957456e-24</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.919205482816324e-05</v>
+        <v>1.272305239085299e-24</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0001978941436391324</v>
+        <v>1.070167915161919e-24</v>
       </c>
       <c r="AE4" t="n">
-        <v>5.870081076864153e-05</v>
+        <v>2.151781807628143e-24</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.391206933476496e-05</v>
+        <v>8.873529502510234e-25</v>
       </c>
       <c r="AG4" t="n">
-        <v>5.926873200223781e-06</v>
+        <v>1.635513070105223e-24</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0001246824103873223</v>
+        <v>2.781873411620753e-24</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.493267245677998e-05</v>
+        <v>1.046390957225266e-24</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.406814226356801e-05</v>
+        <v>6.192696156643356e-25</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.908888953039423e-05</v>
+        <v>1.073231555094958e-24</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0001143870904343203</v>
+        <v>4.595381999544037e-25</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0001451964053558186</v>
+        <v>3.16837305112062e-25</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.134978270391002e-05</v>
+        <v>1.335174199180179e-24</v>
       </c>
       <c r="AO4" t="n">
-        <v>8.666048961458728e-05</v>
+        <v>1.131962545311502e-24</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.823419269290753e-05</v>
+        <v>1.822317008790982e-25</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.339028237154707e-05</v>
+        <v>7.124279255951151e-25</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.237890046468237e-05</v>
+        <v>6.065316321086991e-25</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.619553748052567e-05</v>
+        <v>8.60933505497106e-25</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.134044375969097e-05</v>
+        <v>5.977041306678562e-25</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.0004295843828003854</v>
+        <v>2.707497633324253e-24</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.0002611943928059191</v>
+        <v>1.202246896523073e-24</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.0002538431144785136</v>
+        <v>3.972001679006402e-25</v>
       </c>
       <c r="AX4" t="n">
-        <v>8.482243174512405e-06</v>
+        <v>1.236763111000566e-24</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.284607611130923e-05</v>
+        <v>2.330479017221399e-25</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.000230246310820803</v>
+        <v>2.613543510651525e-25</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.811398922465742e-05</v>
+        <v>1.744486414160067e-24</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.0002219747402705252</v>
+        <v>8.01129270019009e-25</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0001748172508087009</v>
+        <v>1.261630274708235e-24</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.163893001736142e-05</v>
+        <v>7.323582498464911e-25</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.0001967824646271765</v>
+        <v>1.382997412445006e-24</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.083483221009374e-05</v>
+        <v>6.942139654582737e-25</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.0001326080819126219</v>
+        <v>7.609134861974878e-25</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0001850279950303957</v>
+        <v>1.086188743374633e-25</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0002789396094158292</v>
+        <v>1.710389084823246e-24</v>
       </c>
       <c r="BJ4" t="n">
-        <v>3.136709710815921e-05</v>
+        <v>2.462745451655156e-24</v>
       </c>
       <c r="BK4" t="n">
-        <v>3.033337634406053e-05</v>
+        <v>8.753549428763874e-26</v>
       </c>
       <c r="BL4" t="n">
-        <v>6.562283670064062e-05</v>
+        <v>1.603094239559486e-24</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.429119856766192e-05</v>
+        <v>3.972012772362881e-25</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.218696863565128e-05</v>
+        <v>9.414421842936336e-25</v>
       </c>
       <c r="BO4" t="n">
-        <v>7.151444151531905e-06</v>
+        <v>1.521024799461979e-24</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0001207660970976576</v>
+        <v>1.018619799310252e-24</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.131505637720693e-06</v>
+        <v>1.195121904827117e-24</v>
       </c>
       <c r="BR4" t="n">
-        <v>4.015672311652452e-05</v>
+        <v>1.752458198733971e-25</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.0001667673786869273</v>
+        <v>5.114680258765846e-25</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.156062929425389e-05</v>
+        <v>1.663862216544731e-25</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.0001366913493257016</v>
+        <v>4.121040676791742e-25</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.000319250306347385</v>
+        <v>8.269123012376394e-25</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0001931543229147792</v>
+        <v>1.133291381506347e-25</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0001012205102597363</v>
+        <v>1.621502999036111e-24</v>
       </c>
       <c r="BY4" t="n">
-        <v>5.324542871676385e-05</v>
+        <v>2.649441217789286e-24</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.035837653442286e-05</v>
+        <v>4.11766903597902e-25</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.34375644242391e-05</v>
+        <v>3.65963667288507e-25</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0001027640973916277</v>
+        <v>1.139648244547747e-25</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.0001173631462734193</v>
+        <v>2.83510397056803e-25</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.057653884752654e-05</v>
+        <v>9.711691256079164e-25</v>
       </c>
       <c r="CE4" t="n">
-        <v>8.061185508267954e-05</v>
+        <v>1.356236538830548e-25</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.0001165212524938397</v>
+        <v>8.268564400247884e-25</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.845198079943657e-05</v>
+        <v>1.756019412682978e-25</v>
       </c>
       <c r="CH4" t="n">
-        <v>4.780491872224957e-05</v>
+        <v>9.898675942519832e-27</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.0001064651078195311</v>
+        <v>4.218809385675472e-25</v>
       </c>
       <c r="CJ4" t="n">
-        <v>6.191174907144159e-05</v>
+        <v>2.178270770749333e-25</v>
       </c>
       <c r="CK4" t="n">
-        <v>4.868016185355373e-05</v>
+        <v>1.793220367339971e-25</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.00014328453107737</v>
+        <v>8.649076881299963e-25</v>
       </c>
       <c r="CM4" t="n">
-        <v>3.141928573313635e-06</v>
+        <v>2.180504824832919e-24</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0002314521843800321</v>
+        <v>2.082059717026768e-24</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.0001494516618549824</v>
+        <v>4.332616376319444e-25</v>
       </c>
       <c r="CP4" t="n">
-        <v>6.274486077018082e-05</v>
+        <v>2.730381502108583e-24</v>
       </c>
       <c r="CQ4" t="n">
-        <v>5.137296466273256e-05</v>
+        <v>9.821171344658e-25</v>
       </c>
       <c r="CR4" t="n">
-        <v>6.507157377200201e-05</v>
+        <v>3.098175277393396e-25</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.0002071571361739188</v>
+        <v>1.387245132596782e-24</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.0001250358327524737</v>
+        <v>4.862302454548816e-25</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0001926124386955053</v>
+        <v>2.479215536153393e-25</v>
       </c>
       <c r="CV4" t="n">
-        <v>3.060371909668902e-06</v>
+        <v>1.045210525488216e-24</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.0001070091384463012</v>
+        <v>5.449963892855143e-26</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.0001097450294764712</v>
+        <v>7.91439839431599e-25</v>
       </c>
       <c r="CY4" t="n">
-        <v>9.000486898003146e-05</v>
+        <v>1.213919128995756e-25</v>
       </c>
       <c r="CZ4" t="n">
-        <v>8.778273331699893e-05</v>
+        <v>1.264471061435549e-25</v>
       </c>
       <c r="DA4" t="n">
-        <v>8.480936958221719e-05</v>
+        <v>3.041915689785297e-25</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.544484257465228e-05</v>
+        <v>1.363873944988251e-25</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.815172592818271e-05</v>
+        <v>1.560113202442326e-25</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0001180572508019395</v>
+        <v>5.124982289149966e-25</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.0002652179100550711</v>
+        <v>1.441430607669829e-24</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.0001094726467272267</v>
+        <v>2.877405404015343e-25</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.520024852652568e-05</v>
+        <v>1.752029255616757e-25</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.0002684807113837451</v>
+        <v>9.486450760039804e-25</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0001208764806506224</v>
+        <v>2.217049940254834e-25</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0002084857260342687</v>
+        <v>2.888130214540855e-24</v>
       </c>
       <c r="DK4" t="n">
-        <v>7.523435488110408e-05</v>
+        <v>1.133623787770284e-24</v>
       </c>
       <c r="DL4" t="n">
-        <v>1.58807379193604e-05</v>
+        <v>9.258703658474103e-25</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0003454688121564686</v>
+        <v>7.325815960902818e-26</v>
       </c>
       <c r="DN4" t="n">
-        <v>5.931549821980298e-05</v>
+        <v>1.58657460473564e-24</v>
       </c>
       <c r="DO4" t="n">
-        <v>7.809103408362716e-08</v>
+        <v>6.53545227565736e-25</v>
       </c>
       <c r="DP4" t="n">
-        <v>4.313333192840219e-07</v>
+        <v>5.404692151580641e-25</v>
       </c>
       <c r="DQ4" t="n">
-        <v>8.312737918458879e-06</v>
+        <v>1.980070257173459e-24</v>
       </c>
       <c r="DR4" t="n">
-        <v>3.618920163717121e-05</v>
+        <v>3.610758111640478e-26</v>
       </c>
       <c r="DS4" t="n">
-        <v>5.698278255295008e-05</v>
+        <v>1.154720393566223e-24</v>
       </c>
       <c r="DT4" t="n">
-        <v>1.587698352523148e-05</v>
+        <v>1.070066546535598e-24</v>
       </c>
       <c r="DU4" t="n">
-        <v>8.314320439239964e-05</v>
+        <v>8.040851811346787e-26</v>
       </c>
       <c r="DV4" t="n">
-        <v>4.115619049116503e-06</v>
+        <v>6.040375990530363e-25</v>
       </c>
       <c r="DW4" t="n">
-        <v>5.150374272488989e-05</v>
+        <v>1.37498468105974e-25</v>
       </c>
       <c r="DX4" t="n">
-        <v>1.906314719235525e-05</v>
+        <v>8.280406681549449e-25</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.000173237087437883</v>
+        <v>1.4869375281017e-24</v>
       </c>
       <c r="DZ4" t="n">
-        <v>8.468197484035045e-05</v>
+        <v>1.606513458545554e-24</v>
       </c>
       <c r="EA4" t="n">
-        <v>4.045617606607266e-05</v>
+        <v>3.557260030238718e-25</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.0001317295536864549</v>
+        <v>9.024959241876459e-25</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.055971319554374e-05</v>
+        <v>7.54718709420207e-25</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.0001203620049636811</v>
+        <v>3.788203744103794e-25</v>
       </c>
       <c r="EE4" t="n">
-        <v>8.476735820295289e-05</v>
+        <v>1.079441369533245e-24</v>
       </c>
       <c r="EF4" t="n">
-        <v>2.999469143105671e-05</v>
+        <v>4.030083781824595e-25</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.0001124965929193422</v>
+        <v>1.950964445214425e-25</v>
       </c>
       <c r="EH4" t="n">
-        <v>8.560639253119007e-05</v>
+        <v>2.396487446503832e-25</v>
       </c>
       <c r="EI4" t="n">
-        <v>1.996482023969293e-05</v>
+        <v>4.087290988595091e-25</v>
       </c>
       <c r="EJ4" t="n">
-        <v>2.098502955050208e-05</v>
+        <v>6.160365678519005e-25</v>
       </c>
       <c r="EK4" t="n">
-        <v>1.87288060260471e-05</v>
+        <v>1.030157185871949e-24</v>
       </c>
       <c r="EL4" t="n">
-        <v>9.15773562155664e-05</v>
+        <v>4.544071035002002e-25</v>
       </c>
       <c r="EM4" t="n">
-        <v>5.943307405686937e-05</v>
+        <v>6.637849379383442e-25</v>
       </c>
       <c r="EN4" t="n">
-        <v>6.280782690737396e-05</v>
+        <v>1.443533316412695e-24</v>
       </c>
       <c r="EO4" t="n">
-        <v>6.263401701289695e-06</v>
+        <v>1.06857619107041e-24</v>
       </c>
       <c r="EP4" t="n">
-        <v>5.228782902122475e-05</v>
+        <v>7.307735268955152e-25</v>
       </c>
       <c r="EQ4" t="n">
-        <v>7.407937664538622e-05</v>
+        <v>3.220055026807141e-26</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.000123861973406747</v>
+        <v>1.469349183966506e-24</v>
       </c>
       <c r="ES4" t="n">
-        <v>4.518661808106117e-05</v>
+        <v>1.091204567529061e-24</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0002897042722906917</v>
+        <v>9.933388780577952e-25</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.0002691231202334166</v>
+        <v>5.595435760234687e-25</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0002278871834278107</v>
+        <v>5.853058503395305e-25</v>
       </c>
       <c r="EW4" t="n">
-        <v>6.702682003378868e-05</v>
+        <v>1.876191648015469e-26</v>
       </c>
       <c r="EX4" t="n">
-        <v>5.760459771408932e-06</v>
+        <v>1.005397504462617e-24</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0001166352521977387</v>
+        <v>7.64746413424537e-27</v>
       </c>
       <c r="EZ4" t="n">
-        <v>6.400271377060562e-05</v>
+        <v>6.595926845689668e-25</v>
       </c>
       <c r="FA4" t="n">
-        <v>7.118523353710771e-05</v>
+        <v>1.37206010251315e-25</v>
       </c>
       <c r="FB4" t="n">
-        <v>9.665080870036036e-05</v>
+        <v>2.614416927585025e-25</v>
       </c>
       <c r="FC4" t="n">
-        <v>4.194552820990793e-05</v>
+        <v>4.32091954124728e-25</v>
       </c>
       <c r="FD4" t="n">
-        <v>8.933524077292532e-05</v>
+        <v>3.739482955040245e-26</v>
       </c>
       <c r="FE4" t="n">
-        <v>4.278298729332164e-05</v>
+        <v>1.839636265075835e-26</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.0001687853364273906</v>
+        <v>5.264950372601396e-25</v>
       </c>
       <c r="FG4" t="n">
-        <v>9.7881187684834e-05</v>
+        <v>6.013808141318651e-25</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.0001395880535710603</v>
+        <v>7.662957855461976e-27</v>
       </c>
       <c r="FI4" t="n">
-        <v>6.157921598060057e-05</v>
+        <v>9.45740785973796e-25</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.0001719635329209268</v>
+        <v>2.560662219870035e-25</v>
       </c>
       <c r="FK4" t="n">
-        <v>9.262881212634966e-05</v>
+        <v>1.059337890313173e-25</v>
       </c>
       <c r="FL4" t="n">
-        <v>6.308307638391852e-05</v>
+        <v>2.210129657963782e-25</v>
       </c>
       <c r="FM4" t="n">
-        <v>6.917952850926667e-05</v>
+        <v>5.11965797107779e-25</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.0001474784512538463</v>
+        <v>7.50371987224826e-25</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.000181666313437745</v>
+        <v>2.369105492837932e-24</v>
       </c>
       <c r="FP4" t="n">
-        <v>4.778348375111818e-05</v>
+        <v>2.274017777044402e-25</v>
       </c>
       <c r="FQ4" t="n">
-        <v>5.95950405113399e-05</v>
+        <v>6.652277645339934e-25</v>
       </c>
       <c r="FR4" t="n">
-        <v>1.165592038887553e-05</v>
+        <v>5.086451857348643e-25</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.0001330308732576668</v>
+        <v>1.684066176922605e-24</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0005642255418933928</v>
+        <v>2.822533718562366e-25</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.0003765610163100064</v>
+        <v>2.101574755315352e-24</v>
       </c>
       <c r="FV4" t="n">
-        <v>9.561640035826713e-05</v>
+        <v>2.693421199331489e-24</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.0001083472961909138</v>
+        <v>4.346398762409787e-25</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.0001794768468244001</v>
+        <v>2.23144532057234e-24</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.0002078353281831369</v>
+        <v>1.355426132161853e-24</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.0001147802468040027</v>
+        <v>1.911540381918906e-25</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.0001207746608997695</v>
+        <v>1.206115075971825e-24</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.0002027640002779663</v>
+        <v>4.950609516431519e-25</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.0001371922553516924</v>
+        <v>8.344591363026625e-25</v>
       </c>
       <c r="GD4" t="n">
-        <v>6.869137723697349e-05</v>
+        <v>4.257070618692888e-26</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.0002082980936393142</v>
+        <v>1.705437799351627e-24</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.0002026784932240844</v>
+        <v>7.589170764615998e-25</v>
       </c>
       <c r="GG4" t="n">
-        <v>9.700335067464039e-05</v>
+        <v>8.327928648556094e-25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0001520510268164799</v>
+        <v>4.583005619451797e-08</v>
       </c>
       <c r="B5" t="n">
-        <v>0.000672454247251153</v>
+        <v>8.343337754013191e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.664746716618538e-06</v>
+        <v>9.91889308465943e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002166456979466602</v>
+        <v>3.752098791665048e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>4.853466089116409e-05</v>
+        <v>3.30140636606302e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000201610557269305</v>
+        <v>4.725133067040588e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>4.873017314821482e-05</v>
+        <v>7.189235873283906e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>9.960869647329673e-05</v>
+        <v>4.960081767535485e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001810707617551088</v>
+        <v>3.99350881252758e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001063050222001038</v>
+        <v>1.26804380329304e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0006332911434583366</v>
+        <v>8.567931217839941e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.365836578770541e-05</v>
+        <v>1.438007188880874e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0002491837367415428</v>
+        <v>6.245532517823449e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>5.336500908015296e-05</v>
+        <v>2.028072287885152e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>4.173614433966577e-05</v>
+        <v>3.256124330164312e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>7.08475781721063e-05</v>
+        <v>1.348201266182514e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.000155881600221619</v>
+        <v>5.590717933046108e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0001087610216927715</v>
+        <v>3.323431485569017e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.341525239695329e-05</v>
+        <v>5.801624070045364e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>4.578029256663285e-05</v>
+        <v>1.679592571690591e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>2.01358870981494e-05</v>
+        <v>9.501594178118467e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>3.008017074535019e-06</v>
+        <v>2.905587166424084e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>0.000188530728337355</v>
+        <v>4.928260182168742e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.27438033814542e-05</v>
+        <v>2.571654817984381e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.49457540223375e-05</v>
+        <v>3.971030082539073e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.295639908174053e-05</v>
+        <v>1.000326435018906e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.027674630284309e-05</v>
+        <v>3.695823522775754e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.411174500593916e-05</v>
+        <v>4.237660178318947e-08</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.14955180126708e-05</v>
+        <v>6.824892295753671e-08</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.486798621248454e-06</v>
+        <v>3.687200944568758e-08</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.134351209155284e-05</v>
+        <v>2.051873337904908e-09</v>
       </c>
       <c r="AF5" t="n">
-        <v>3.877571361954324e-05</v>
+        <v>5.487451559815781e-08</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.816530806943774e-05</v>
+        <v>4.708305922918044e-08</v>
       </c>
       <c r="AH5" t="n">
-        <v>8.649399387650192e-05</v>
+        <v>7.281699510031103e-08</v>
       </c>
       <c r="AI5" t="n">
-        <v>9.455893450649455e-05</v>
+        <v>6.748724246108395e-08</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6.123057391960174e-05</v>
+        <v>1.145856600714978e-07</v>
       </c>
       <c r="AK5" t="n">
-        <v>4.720078322861809e-06</v>
+        <v>8.39933811391802e-09</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.000148515886394307</v>
+        <v>2.955701177143055e-07</v>
       </c>
       <c r="AM5" t="n">
-        <v>5.731300916522741e-05</v>
+        <v>9.90809070344767e-08</v>
       </c>
       <c r="AN5" t="n">
-        <v>3.167058821418323e-05</v>
+        <v>3.565100143987365e-07</v>
       </c>
       <c r="AO5" t="n">
-        <v>8.220424206228927e-05</v>
+        <v>1.010763241993118e-07</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.141250534914434e-05</v>
+        <v>9.362913289123753e-08</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.254274659208022e-05</v>
+        <v>2.77525273872925e-08</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.009855911135674e-05</v>
+        <v>2.405213876954804e-07</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.013521018147003e-05</v>
+        <v>9.58992245614354e-08</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.437404353055172e-05</v>
+        <v>7.579013328040674e-08</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.0002515691739972681</v>
+        <v>4.728310614154907e-07</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.801098708005156e-05</v>
+        <v>1.464264265393922e-08</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.0001894070010166615</v>
+        <v>2.411802881852054e-07</v>
       </c>
       <c r="AX5" t="n">
-        <v>2.610163755889516e-05</v>
+        <v>9.428389091681311e-08</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.0001370664831483737</v>
+        <v>1.214184663922424e-07</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0002270554250571877</v>
+        <v>9.559628466604408e-08</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0002384190011071041</v>
+        <v>1.729163585650895e-07</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.50567720993422e-05</v>
+        <v>1.064438777120813e-07</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.832773498084862e-05</v>
+        <v>2.913192354014882e-08</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0001218463075929321</v>
+        <v>9.515886034705545e-08</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.060508293448947e-05</v>
+        <v>8.830630093825675e-08</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0001281033037230372</v>
+        <v>2.636009526213456e-07</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.0001350077945971861</v>
+        <v>1.070071533604278e-07</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.0001158719896920957</v>
+        <v>8.110723825893729e-08</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0001437549653928727</v>
+        <v>1.694901641258184e-07</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1.971933306776918e-05</v>
+        <v>2.161474981221545e-07</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0002428008592687547</v>
+        <v>1.04449867421863e-07</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.24231846712064e-05</v>
+        <v>1.429050211498861e-08</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0002258876338601112</v>
+        <v>8.213915236865432e-08</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.000107564774225466</v>
+        <v>6.974440225349099e-08</v>
       </c>
       <c r="BO5" t="n">
-        <v>8.077317761490121e-05</v>
+        <v>5.704370664716407e-08</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0001525942352600396</v>
+        <v>3.864916777729377e-07</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.358062480809167e-05</v>
+        <v>5.226022636861671e-08</v>
       </c>
       <c r="BR5" t="n">
-        <v>6.511504761874676e-05</v>
+        <v>9.221064090070286e-08</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.0001187125744763762</v>
+        <v>9.958608160332005e-08</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.47562852059491e-05</v>
+        <v>1.139768457392165e-07</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.854976239381358e-05</v>
+        <v>6.722342504872358e-08</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.0002429306332487613</v>
+        <v>2.024602565597888e-07</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.092472575692227e-05</v>
+        <v>3.835665296492152e-08</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.0001328594225924462</v>
+        <v>5.056442091699864e-07</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.00480644707568e-05</v>
+        <v>3.246034623316518e-07</v>
       </c>
       <c r="BZ5" t="n">
-        <v>9.733768092701212e-05</v>
+        <v>2.443137248064886e-07</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.000160247553139925</v>
+        <v>2.446189029114976e-08</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.0001385596551699564</v>
+        <v>1.602897299335382e-07</v>
       </c>
       <c r="CC5" t="n">
-        <v>1.749074908730108e-05</v>
+        <v>3.697368242683297e-07</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.067163197556511e-05</v>
+        <v>3.596844777575825e-08</v>
       </c>
       <c r="CE5" t="n">
-        <v>7.427793025271967e-05</v>
+        <v>3.23198577234507e-07</v>
       </c>
       <c r="CF5" t="n">
-        <v>1.876908936537802e-05</v>
+        <v>5.486545262556319e-08</v>
       </c>
       <c r="CG5" t="n">
-        <v>4.811225517187268e-05</v>
+        <v>1.066228421109372e-07</v>
       </c>
       <c r="CH5" t="n">
-        <v>3.023744284291752e-05</v>
+        <v>8.341733348515845e-08</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.511060665710829e-05</v>
+        <v>6.29045615596624e-08</v>
       </c>
       <c r="CJ5" t="n">
-        <v>7.747255585854873e-05</v>
+        <v>5.514771572734389e-08</v>
       </c>
       <c r="CK5" t="n">
-        <v>2.962192957056686e-05</v>
+        <v>2.309478119855157e-08</v>
       </c>
       <c r="CL5" t="n">
-        <v>3.099223977187648e-05</v>
+        <v>9.594830174819435e-08</v>
       </c>
       <c r="CM5" t="n">
-        <v>7.742414891254157e-05</v>
+        <v>1.535878197955753e-07</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0001135019992943853</v>
+        <v>3.509614430186048e-07</v>
       </c>
       <c r="CO5" t="n">
-        <v>6.636074249399826e-05</v>
+        <v>2.243043155658597e-07</v>
       </c>
       <c r="CP5" t="n">
-        <v>3.303758785477839e-05</v>
+        <v>1.681157328903282e-07</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.0001230710768140852</v>
+        <v>6.443283240287201e-08</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0001082922972273082</v>
+        <v>8.737092827004744e-09</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.0001949271536432207</v>
+        <v>6.663206875145988e-08</v>
       </c>
       <c r="CT5" t="n">
-        <v>9.229360148310661e-05</v>
+        <v>1.913811047415948e-07</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.201917802973185e-05</v>
+        <v>6.372567185053413e-08</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.987791958730668e-05</v>
+        <v>3.496158385019044e-08</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.000117737778055016</v>
+        <v>2.948801238744636e-07</v>
       </c>
       <c r="CX5" t="n">
-        <v>2.362308623560239e-05</v>
+        <v>7.29921438846759e-08</v>
       </c>
       <c r="CY5" t="n">
-        <v>5.101021815789863e-05</v>
+        <v>1.286677644429801e-07</v>
       </c>
       <c r="CZ5" t="n">
-        <v>1.229126246471424e-05</v>
+        <v>9.742696249759319e-08</v>
       </c>
       <c r="DA5" t="n">
-        <v>5.010690802009776e-05</v>
+        <v>7.808727531255499e-08</v>
       </c>
       <c r="DB5" t="n">
-        <v>6.3360232161358e-05</v>
+        <v>7.400586810035747e-08</v>
       </c>
       <c r="DC5" t="n">
-        <v>6.377143108693417e-06</v>
+        <v>5.054153362493707e-08</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.804840576369315e-05</v>
+        <v>1.012892028029455e-07</v>
       </c>
       <c r="DE5" t="n">
-        <v>7.778769213473424e-05</v>
+        <v>1.262398541257426e-07</v>
       </c>
       <c r="DF5" t="n">
-        <v>9.354410576634109e-05</v>
+        <v>1.72556866573359e-07</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.190554707543924e-05</v>
+        <v>2.408689425692501e-08</v>
       </c>
       <c r="DH5" t="n">
-        <v>6.862689042463899e-05</v>
+        <v>2.445246138904622e-08</v>
       </c>
       <c r="DI5" t="n">
-        <v>6.058977305656299e-05</v>
+        <v>1.029649823180989e-07</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.38368322950555e-05</v>
+        <v>1.842183365852179e-07</v>
       </c>
       <c r="DK5" t="n">
-        <v>7.443325739586726e-05</v>
+        <v>7.222332243372875e-08</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0001676723040873185</v>
+        <v>3.609375198720954e-07</v>
       </c>
       <c r="DM5" t="n">
-        <v>7.014400762272999e-05</v>
+        <v>1.343768900596842e-07</v>
       </c>
       <c r="DN5" t="n">
-        <v>4.606809307006188e-05</v>
+        <v>6.560937038102566e-08</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0002144337631762028</v>
+        <v>1.231738337992283e-07</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.0001492318115197122</v>
+        <v>4.222793137387271e-08</v>
       </c>
       <c r="DQ5" t="n">
-        <v>6.986493099248037e-05</v>
+        <v>2.159321752515098e-07</v>
       </c>
       <c r="DR5" t="n">
-        <v>1.582813638378866e-05</v>
+        <v>8.24443944225095e-08</v>
       </c>
       <c r="DS5" t="n">
-        <v>6.831215432612225e-05</v>
+        <v>9.652935517578953e-08</v>
       </c>
       <c r="DT5" t="n">
-        <v>6.932378892088309e-05</v>
+        <v>1.022280926576968e-07</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0001017955582938157</v>
+        <v>1.021385855892731e-07</v>
       </c>
       <c r="DV5" t="n">
-        <v>4.774989429279231e-05</v>
+        <v>7.48519823901006e-08</v>
       </c>
       <c r="DW5" t="n">
-        <v>1.119981061492581e-05</v>
+        <v>3.388738178955464e-08</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0001940820511663333</v>
+        <v>2.388861446434021e-07</v>
       </c>
       <c r="DY5" t="n">
-        <v>6.834035957581364e-06</v>
+        <v>5.887401499649059e-08</v>
       </c>
       <c r="DZ5" t="n">
-        <v>9.434930689167231e-05</v>
+        <v>2.486950734237325e-07</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0002410069137113169</v>
+        <v>4.839808909196108e-08</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.98276866285596e-05</v>
+        <v>3.835713471289637e-07</v>
       </c>
       <c r="EC5" t="n">
-        <v>5.734283149649855e-06</v>
+        <v>1.279327932479646e-07</v>
       </c>
       <c r="ED5" t="n">
-        <v>7.76547531131655e-05</v>
+        <v>3.552500800196867e-07</v>
       </c>
       <c r="EE5" t="n">
-        <v>6.367575679178117e-06</v>
+        <v>2.306912847416243e-07</v>
       </c>
       <c r="EF5" t="n">
-        <v>4.506531695369631e-06</v>
+        <v>1.043697892555429e-07</v>
       </c>
       <c r="EG5" t="n">
-        <v>4.951634764438495e-06</v>
+        <v>2.380595418571829e-07</v>
       </c>
       <c r="EH5" t="n">
-        <v>9.204804518958554e-05</v>
+        <v>3.151227900843878e-08</v>
       </c>
       <c r="EI5" t="n">
-        <v>9.167113603325561e-06</v>
+        <v>1.42599446917302e-07</v>
       </c>
       <c r="EJ5" t="n">
-        <v>4.226925011607818e-05</v>
+        <v>9.865607353276573e-08</v>
       </c>
       <c r="EK5" t="n">
-        <v>7.492153963539749e-05</v>
+        <v>5.144971382264885e-08</v>
       </c>
       <c r="EL5" t="n">
-        <v>5.588223939412273e-05</v>
+        <v>3.323136965605045e-08</v>
       </c>
       <c r="EM5" t="n">
-        <v>5.104549927636981e-05</v>
+        <v>3.230109513197021e-08</v>
       </c>
       <c r="EN5" t="n">
-        <v>1.297739345318405e-06</v>
+        <v>2.658441289327129e-08</v>
       </c>
       <c r="EO5" t="n">
-        <v>9.306239007855766e-06</v>
+        <v>6.879224656586302e-08</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0001967426796909422</v>
+        <v>1.667958713369444e-07</v>
       </c>
       <c r="EQ5" t="n">
-        <v>4.457577961147763e-05</v>
+        <v>3.573838824877384e-08</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0001149558374891058</v>
+        <v>9.509200538104778e-08</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0001598458329681307</v>
+        <v>2.176219311422756e-07</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.000184914271812886</v>
+        <v>1.482442790745608e-08</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.0001636379747651517</v>
+        <v>8.275448948324993e-08</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.0001555080234538764</v>
+        <v>2.891632000512345e-08</v>
       </c>
       <c r="EW5" t="n">
-        <v>3.767367161344737e-05</v>
+        <v>2.653820843079302e-07</v>
       </c>
       <c r="EX5" t="n">
-        <v>2.616768324514851e-05</v>
+        <v>2.57977177398061e-08</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.0001015578745864332</v>
+        <v>3.287277650088072e-07</v>
       </c>
       <c r="EZ5" t="n">
-        <v>3.611090960475849e-06</v>
+        <v>4.165094935615343e-08</v>
       </c>
       <c r="FA5" t="n">
-        <v>6.677103374386206e-05</v>
+        <v>1.000364520109542e-07</v>
       </c>
       <c r="FB5" t="n">
-        <v>5.23278140462935e-05</v>
+        <v>8.327707234911941e-08</v>
       </c>
       <c r="FC5" t="n">
-        <v>4.650603659683838e-05</v>
+        <v>9.152410740398409e-08</v>
       </c>
       <c r="FD5" t="n">
-        <v>8.426912245340645e-05</v>
+        <v>9.831366298840294e-08</v>
       </c>
       <c r="FE5" t="n">
-        <v>1.413258814864093e-05</v>
+        <v>1.006667318392829e-07</v>
       </c>
       <c r="FF5" t="n">
-        <v>3.5942139220424e-05</v>
+        <v>1.240230886878635e-07</v>
       </c>
       <c r="FG5" t="n">
-        <v>4.986146814189851e-05</v>
+        <v>1.008152707981935e-07</v>
       </c>
       <c r="FH5" t="n">
-        <v>6.371031486196443e-05</v>
+        <v>3.26410258821852e-08</v>
       </c>
       <c r="FI5" t="n">
-        <v>6.007470801705495e-05</v>
+        <v>1.537897560410784e-07</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.0001117415013140999</v>
+        <v>1.25617802382294e-07</v>
       </c>
       <c r="FK5" t="n">
-        <v>3.280497912783176e-05</v>
+        <v>3.635615541952575e-08</v>
       </c>
       <c r="FL5" t="n">
-        <v>8.716596494195983e-05</v>
+        <v>1.183223758971508e-07</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0001100490480894223</v>
+        <v>6.225835846862537e-08</v>
       </c>
       <c r="FN5" t="n">
-        <v>8.389313006773591e-05</v>
+        <v>1.074135909107099e-07</v>
       </c>
       <c r="FO5" t="n">
-        <v>4.18769741372671e-05</v>
+        <v>3.031329498526247e-08</v>
       </c>
       <c r="FP5" t="n">
-        <v>5.199289080337621e-05</v>
+        <v>2.485646461991564e-07</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0001281292061321437</v>
+        <v>2.292856891017436e-07</v>
       </c>
       <c r="FR5" t="n">
-        <v>9.043338650371879e-05</v>
+        <v>9.003048262457014e-08</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.0001041873183567077</v>
+        <v>4.760310616802599e-07</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0004945565015077591</v>
+        <v>2.103733578451283e-07</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0001278064446523786</v>
+        <v>2.956348339466786e-07</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0001718712301226333</v>
+        <v>2.520731534616516e-08</v>
       </c>
       <c r="FW5" t="n">
-        <v>1.096062715078006e-05</v>
+        <v>2.390996485246433e-07</v>
       </c>
       <c r="FX5" t="n">
-        <v>3.826893953373656e-05</v>
+        <v>1.125553126257728e-07</v>
       </c>
       <c r="FY5" t="n">
-        <v>5.471097210829612e-06</v>
+        <v>2.798514664448248e-08</v>
       </c>
       <c r="FZ5" t="n">
-        <v>1.028793121804483e-05</v>
+        <v>1.917615293223207e-07</v>
       </c>
       <c r="GA5" t="n">
-        <v>2.549259806983173e-05</v>
+        <v>3.73763029415386e-08</v>
       </c>
       <c r="GB5" t="n">
-        <v>8.887884177966043e-05</v>
+        <v>1.401545546286798e-11</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.0001653544459259138</v>
+        <v>3.500572915982048e-07</v>
       </c>
       <c r="GD5" t="n">
-        <v>4.989537410438061e-05</v>
+        <v>1.104482905134319e-07</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0001209671827382408</v>
+        <v>2.935765337497287e-07</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.0001033681546687149</v>
+        <v>2.069798910042664e-07</v>
       </c>
       <c r="GG5" t="n">
-        <v>4.83861003885977e-05</v>
+        <v>1.300719105756798e-07</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1.51335342479797e-07</v>
+        <v>8.423925132112439e-27</v>
       </c>
       <c r="B6" t="n">
-        <v>5.794438493467169e-07</v>
+        <v>2.132947013958893e-25</v>
       </c>
       <c r="C6" t="n">
-        <v>2.86611054889363e-07</v>
+        <v>5.429394344751505e-26</v>
       </c>
       <c r="D6" t="n">
-        <v>3.48543522932232e-07</v>
+        <v>1.975686421537678e-26</v>
       </c>
       <c r="E6" t="n">
-        <v>1.779484648523066e-07</v>
+        <v>2.300102695470699e-25</v>
       </c>
       <c r="F6" t="n">
-        <v>1.007287323773198e-06</v>
+        <v>2.400809418188312e-25</v>
       </c>
       <c r="G6" t="n">
-        <v>8.437550036433095e-08</v>
+        <v>5.44307171373384e-25</v>
       </c>
       <c r="H6" t="n">
-        <v>9.079057150529479e-08</v>
+        <v>4.821984759759102e-25</v>
       </c>
       <c r="I6" t="n">
-        <v>1.232650788551837e-06</v>
+        <v>7.153110273144232e-26</v>
       </c>
       <c r="J6" t="n">
-        <v>1.541795313642069e-07</v>
+        <v>4.934919073026673e-26</v>
       </c>
       <c r="K6" t="n">
-        <v>7.426530501675188e-09</v>
+        <v>1.696015694003473e-25</v>
       </c>
       <c r="L6" t="n">
-        <v>2.423781211291498e-07</v>
+        <v>9.961819327602117e-26</v>
       </c>
       <c r="M6" t="n">
-        <v>7.679982445552014e-07</v>
+        <v>1.845088957934384e-25</v>
       </c>
       <c r="N6" t="n">
-        <v>2.962389373806218e-07</v>
+        <v>3.745231039329945e-25</v>
       </c>
       <c r="O6" t="n">
-        <v>9.514128009868728e-07</v>
+        <v>5.06186010470451e-25</v>
       </c>
       <c r="P6" t="n">
-        <v>1.870352832611388e-07</v>
+        <v>8.097805596551481e-25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.553584070279612e-07</v>
+        <v>5.654531795835122e-25</v>
       </c>
       <c r="R6" t="n">
-        <v>4.749291804273525e-07</v>
+        <v>9.09707739886983e-26</v>
       </c>
       <c r="S6" t="n">
-        <v>2.447688132178882e-07</v>
+        <v>1.035929675545904e-25</v>
       </c>
       <c r="T6" t="n">
-        <v>7.463658135975493e-08</v>
+        <v>3.21583388140711e-25</v>
       </c>
       <c r="U6" t="n">
-        <v>9.796664102168506e-08</v>
+        <v>6.901679348532501e-26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.330660239773351e-07</v>
+        <v>1.66097399955549e-25</v>
       </c>
       <c r="W6" t="n">
-        <v>6.372654297592817e-07</v>
+        <v>5.417723640696826e-25</v>
       </c>
       <c r="X6" t="n">
-        <v>3.57361003011647e-08</v>
+        <v>1.681381338135492e-25</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.539866141494713e-08</v>
+        <v>9.296146448302352e-26</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.129203148295346e-07</v>
+        <v>3.535434714181581e-25</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.38972323940834e-08</v>
+        <v>6.14080759800728e-27</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.596387436275108e-08</v>
+        <v>1.19555900772432e-25</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.717701110237613e-07</v>
+        <v>3.494134887564867e-25</v>
       </c>
       <c r="AD6" t="n">
-        <v>5.269943699204305e-07</v>
+        <v>5.249228374760341e-26</v>
       </c>
       <c r="AE6" t="n">
-        <v>4.003192088930518e-07</v>
+        <v>2.097122128543445e-25</v>
       </c>
       <c r="AF6" t="n">
-        <v>7.041911942451407e-08</v>
+        <v>3.880449687093878e-25</v>
       </c>
       <c r="AG6" t="n">
-        <v>6.578377309551797e-08</v>
+        <v>1.887101347815643e-25</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.142334546486381e-07</v>
+        <v>3.883552375641726e-25</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.902496589740622e-07</v>
+        <v>2.221021854912621e-25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.916858932167088e-07</v>
+        <v>1.031163599823688e-25</v>
       </c>
       <c r="AK6" t="n">
-        <v>9.261235334179219e-08</v>
+        <v>5.707737135885335e-26</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.032972818393318e-07</v>
+        <v>1.190175278565219e-25</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.930908268832354e-07</v>
+        <v>1.149206018564159e-26</v>
       </c>
       <c r="AN6" t="n">
-        <v>3.990031700595864e-07</v>
+        <v>1.471408258840552e-25</v>
       </c>
       <c r="AO6" t="n">
-        <v>5.140033181305625e-07</v>
+        <v>1.569809289043624e-25</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.282621949234453e-07</v>
+        <v>4.504682039038911e-26</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.905773375365243e-08</v>
+        <v>1.365072274007089e-25</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.916308865039355e-08</v>
+        <v>1.182147262999914e-25</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.151199384239135e-09</v>
+        <v>8.381997791297524e-26</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.755141454395925e-08</v>
+        <v>5.39078330122643e-26</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.686259214598977e-07</v>
+        <v>6.87351910962789e-25</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.644408425567235e-07</v>
+        <v>8.795299892172696e-27</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.855814144226315e-07</v>
+        <v>4.768243857109953e-26</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.389103646142757e-07</v>
+        <v>3.31298999049413e-25</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.372361672722036e-07</v>
+        <v>3.215651210803745e-25</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7.04310082255688e-07</v>
+        <v>4.716366391830357e-26</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.966418138494191e-07</v>
+        <v>3.807467480890258e-25</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.740438950851967e-07</v>
+        <v>1.808886405360561e-26</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.810103687053925e-08</v>
+        <v>2.235128290271687e-26</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.484100450483311e-08</v>
+        <v>3.479807447892823e-25</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.859615844703512e-07</v>
+        <v>9.562441238001678e-26</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.016520284087164e-07</v>
+        <v>2.712658213454789e-25</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.4488997496519e-09</v>
+        <v>6.330101551488466e-26</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.404430231057631e-07</v>
+        <v>7.912771615218005e-26</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.496465754120436e-07</v>
+        <v>1.717726748488869e-25</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1.32864741431149e-08</v>
+        <v>4.470259292252735e-25</v>
       </c>
       <c r="BK6" t="n">
-        <v>2.091319259989177e-07</v>
+        <v>6.999318141885903e-26</v>
       </c>
       <c r="BL6" t="n">
-        <v>5.393769697548123e-08</v>
+        <v>1.358841721155161e-26</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.81392971146488e-07</v>
+        <v>2.918065267222697e-25</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.510807976501383e-07</v>
+        <v>3.200783093262834e-26</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.38878578531876e-07</v>
+        <v>1.82391531494067e-25</v>
       </c>
       <c r="BP6" t="n">
-        <v>2.62146755858339e-07</v>
+        <v>2.213699993117006e-25</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.314065679660416e-07</v>
+        <v>3.756703542082187e-26</v>
       </c>
       <c r="BR6" t="n">
-        <v>2.601752413511349e-08</v>
+        <v>1.624831104587625e-25</v>
       </c>
       <c r="BS6" t="n">
-        <v>4.964110758010065e-07</v>
+        <v>1.213629222613088e-25</v>
       </c>
       <c r="BT6" t="n">
-        <v>4.130188813178393e-07</v>
+        <v>2.136884415952077e-25</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.116382967822574e-08</v>
+        <v>1.034209219215423e-25</v>
       </c>
       <c r="BV6" t="n">
-        <v>2.176928006747403e-07</v>
+        <v>3.639513324230948e-26</v>
       </c>
       <c r="BW6" t="n">
-        <v>2.129175840082098e-07</v>
+        <v>7.530594391136877e-26</v>
       </c>
       <c r="BX6" t="n">
-        <v>1.717412771995441e-07</v>
+        <v>2.182060754360854e-25</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.429390744713601e-07</v>
+        <v>5.774107824886588e-25</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.621894227810117e-07</v>
+        <v>8.989686928873216e-26</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.479231741541298e-07</v>
+        <v>6.499950083655954e-26</v>
       </c>
       <c r="CB6" t="n">
-        <v>6.432612735807197e-07</v>
+        <v>1.326115610797913e-25</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.357290007637403e-08</v>
+        <v>1.493949219650144e-25</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.925877306050097e-08</v>
+        <v>6.594593670759845e-26</v>
       </c>
       <c r="CE6" t="n">
-        <v>3.833669026676034e-08</v>
+        <v>2.54324226056025e-26</v>
       </c>
       <c r="CF6" t="n">
-        <v>1.026510290103033e-07</v>
+        <v>2.803368835908088e-26</v>
       </c>
       <c r="CG6" t="n">
-        <v>8.24530417276037e-08</v>
+        <v>4.470712024456622e-26</v>
       </c>
       <c r="CH6" t="n">
-        <v>3.468761633484974e-08</v>
+        <v>1.66846053606507e-26</v>
       </c>
       <c r="CI6" t="n">
-        <v>8.66575433633443e-08</v>
+        <v>8.040289747951817e-26</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.599957499820448e-08</v>
+        <v>1.616163372131993e-29</v>
       </c>
       <c r="CK6" t="n">
-        <v>8.218827218797742e-08</v>
+        <v>2.272150672704236e-26</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.811110905691748e-08</v>
+        <v>1.178896046734756e-25</v>
       </c>
       <c r="CM6" t="n">
-        <v>4.660129349076669e-08</v>
+        <v>7.389717392011213e-26</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.540680270612938e-07</v>
+        <v>4.648088754850248e-25</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.438685188759337e-07</v>
+        <v>1.758248622667568e-26</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.310399966314435e-07</v>
+        <v>9.628830046151848e-27</v>
       </c>
       <c r="CQ6" t="n">
-        <v>8.133165607659976e-08</v>
+        <v>1.36547915367086e-25</v>
       </c>
       <c r="CR6" t="n">
-        <v>2.319096239489227e-07</v>
+        <v>4.773095659825854e-26</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.318785590205152e-07</v>
+        <v>4.619764211010222e-25</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.704072923937929e-07</v>
+        <v>7.033234846727331e-26</v>
       </c>
       <c r="CU6" t="n">
-        <v>3.717793788382551e-07</v>
+        <v>6.131320929324415e-26</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.049900077987331e-08</v>
+        <v>3.745363666569635e-26</v>
       </c>
       <c r="CW6" t="n">
-        <v>3.805808290735513e-08</v>
+        <v>1.483255562967412e-26</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.039453536577639e-07</v>
+        <v>3.58879326581073e-28</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.749931044514597e-08</v>
+        <v>7.863249639297591e-26</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.563095537449044e-07</v>
+        <v>1.1052508275922e-25</v>
       </c>
       <c r="DA6" t="n">
-        <v>3.946396276433006e-08</v>
+        <v>1.206299225689387e-25</v>
       </c>
       <c r="DB6" t="n">
-        <v>9.176635984431414e-08</v>
+        <v>2.734523465595253e-26</v>
       </c>
       <c r="DC6" t="n">
-        <v>4.113981333375705e-08</v>
+        <v>4.959554644428902e-26</v>
       </c>
       <c r="DD6" t="n">
-        <v>7.815800984189991e-08</v>
+        <v>6.87608389364599e-26</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.93203817389076e-07</v>
+        <v>1.700584431239867e-25</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.6085484705618e-07</v>
+        <v>3.776804950542383e-25</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.844425412400597e-07</v>
+        <v>2.680544672079373e-25</v>
       </c>
       <c r="DH6" t="n">
-        <v>1.275993213312177e-07</v>
+        <v>6.199784811433866e-26</v>
       </c>
       <c r="DI6" t="n">
-        <v>2.206366644941227e-07</v>
+        <v>2.191695211203932e-25</v>
       </c>
       <c r="DJ6" t="n">
-        <v>8.802932711660105e-07</v>
+        <v>6.63125844652032e-25</v>
       </c>
       <c r="DK6" t="n">
-        <v>7.096806697859392e-09</v>
+        <v>5.041267383811781e-26</v>
       </c>
       <c r="DL6" t="n">
-        <v>2.436847807985032e-07</v>
+        <v>5.854370970726366e-27</v>
       </c>
       <c r="DM6" t="n">
-        <v>8.628807108834735e-07</v>
+        <v>9.191309299188809e-26</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.685037176457627e-07</v>
+        <v>1.480391905436822e-25</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.418372477246521e-07</v>
+        <v>1.068499153872634e-25</v>
       </c>
       <c r="DP6" t="n">
-        <v>3.076684684799602e-09</v>
+        <v>8.755178919571222e-26</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1.30339401493984e-08</v>
+        <v>5.370081865440201e-25</v>
       </c>
       <c r="DR6" t="n">
-        <v>1.40853714469813e-07</v>
+        <v>3.600337752120574e-26</v>
       </c>
       <c r="DS6" t="n">
-        <v>1.652443728517028e-07</v>
+        <v>1.240612579654722e-26</v>
       </c>
       <c r="DT6" t="n">
-        <v>3.491387445819782e-08</v>
+        <v>1.518746199389151e-25</v>
       </c>
       <c r="DU6" t="n">
-        <v>1.158979898718826e-07</v>
+        <v>2.024394083462725e-25</v>
       </c>
       <c r="DV6" t="n">
-        <v>4.683290626417147e-07</v>
+        <v>9.427022786561594e-26</v>
       </c>
       <c r="DW6" t="n">
-        <v>5.657461343844261e-08</v>
+        <v>4.477922398019617e-26</v>
       </c>
       <c r="DX6" t="n">
-        <v>6.424392040571547e-08</v>
+        <v>3.043327011248544e-25</v>
       </c>
       <c r="DY6" t="n">
-        <v>2.290845912966688e-07</v>
+        <v>8.613407056356197e-26</v>
       </c>
       <c r="DZ6" t="n">
-        <v>1.584961140110863e-08</v>
+        <v>4.755501041781272e-25</v>
       </c>
       <c r="EA6" t="n">
-        <v>4.035359495446755e-07</v>
+        <v>7.901406471504582e-26</v>
       </c>
       <c r="EB6" t="n">
-        <v>3.928386433926789e-07</v>
+        <v>3.47120171497396e-25</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.534575512276206e-07</v>
+        <v>1.167269099808413e-25</v>
       </c>
       <c r="ED6" t="n">
-        <v>1.79201734340495e-07</v>
+        <v>1.006360333849342e-26</v>
       </c>
       <c r="EE6" t="n">
-        <v>4.469378112048616e-08</v>
+        <v>2.476667022391463e-26</v>
       </c>
       <c r="EF6" t="n">
-        <v>7.111463418141284e-08</v>
+        <v>1.99189889980953e-26</v>
       </c>
       <c r="EG6" t="n">
-        <v>3.109367341380675e-08</v>
+        <v>3.622428938954673e-26</v>
       </c>
       <c r="EH6" t="n">
-        <v>5.471672537282757e-08</v>
+        <v>1.19275075534637e-26</v>
       </c>
       <c r="EI6" t="n">
-        <v>3.067166289838497e-07</v>
+        <v>8.553834499465202e-26</v>
       </c>
       <c r="EJ6" t="n">
-        <v>1.524847164091625e-07</v>
+        <v>1.316072671917351e-25</v>
       </c>
       <c r="EK6" t="n">
-        <v>3.485947530634803e-08</v>
+        <v>1.71909431282378e-26</v>
       </c>
       <c r="EL6" t="n">
-        <v>1.78397527861307e-07</v>
+        <v>8.948081603545003e-27</v>
       </c>
       <c r="EM6" t="n">
-        <v>3.993239943156368e-07</v>
+        <v>3.339415844742902e-26</v>
       </c>
       <c r="EN6" t="n">
-        <v>9.069486139878791e-08</v>
+        <v>2.551947032500573e-25</v>
       </c>
       <c r="EO6" t="n">
-        <v>1.487585450377082e-07</v>
+        <v>1.770039936159084e-25</v>
       </c>
       <c r="EP6" t="n">
-        <v>1.051390654538409e-07</v>
+        <v>1.544307388130092e-25</v>
       </c>
       <c r="EQ6" t="n">
-        <v>8.743522528220637e-08</v>
+        <v>2.790922089937897e-27</v>
       </c>
       <c r="ER6" t="n">
-        <v>1.3616619298773e-07</v>
+        <v>3.576584410707271e-27</v>
       </c>
       <c r="ES6" t="n">
-        <v>3.79187838461803e-07</v>
+        <v>3.351739331196652e-25</v>
       </c>
       <c r="ET6" t="n">
-        <v>4.165747213846771e-07</v>
+        <v>1.236207161277612e-25</v>
       </c>
       <c r="EU6" t="n">
-        <v>2.748637939475884e-07</v>
+        <v>5.434924999254203e-26</v>
       </c>
       <c r="EV6" t="n">
-        <v>6.348069518935517e-07</v>
+        <v>8.279399035002545e-26</v>
       </c>
       <c r="EW6" t="n">
-        <v>5.160191562936234e-08</v>
+        <v>3.520359582282808e-26</v>
       </c>
       <c r="EX6" t="n">
-        <v>4.288942534458329e-10</v>
+        <v>4.13629847929388e-26</v>
       </c>
       <c r="EY6" t="n">
-        <v>3.510385937488536e-08</v>
+        <v>5.180410121541123e-26</v>
       </c>
       <c r="EZ6" t="n">
-        <v>3.870302744957144e-09</v>
+        <v>9.368786362828817e-27</v>
       </c>
       <c r="FA6" t="n">
-        <v>7.695658155171259e-08</v>
+        <v>5.188446642013063e-26</v>
       </c>
       <c r="FB6" t="n">
-        <v>1.214438896113279e-07</v>
+        <v>9.265188588153085e-26</v>
       </c>
       <c r="FC6" t="n">
-        <v>3.068571174935641e-09</v>
+        <v>9.227722009238163e-26</v>
       </c>
       <c r="FD6" t="n">
-        <v>1.946476402281405e-08</v>
+        <v>3.105971565067792e-26</v>
       </c>
       <c r="FE6" t="n">
-        <v>1.141685572747519e-07</v>
+        <v>6.268375034547668e-26</v>
       </c>
       <c r="FF6" t="n">
-        <v>4.460400759853655e-08</v>
+        <v>7.129009956192148e-26</v>
       </c>
       <c r="FG6" t="n">
-        <v>1.131399187670468e-07</v>
+        <v>2.383688178316622e-25</v>
       </c>
       <c r="FH6" t="n">
-        <v>4.87448019725889e-08</v>
+        <v>5.684423214648143e-26</v>
       </c>
       <c r="FI6" t="n">
-        <v>7.127855639055269e-08</v>
+        <v>7.475167051783786e-26</v>
       </c>
       <c r="FJ6" t="n">
-        <v>3.107913926214678e-07</v>
+        <v>1.185543309196891e-25</v>
       </c>
       <c r="FK6" t="n">
-        <v>2.82999138789819e-07</v>
+        <v>1.265974827536127e-25</v>
       </c>
       <c r="FL6" t="n">
-        <v>4.583908435051853e-07</v>
+        <v>2.108469399626983e-25</v>
       </c>
       <c r="FM6" t="n">
-        <v>1.066525285864373e-07</v>
+        <v>2.694718653653448e-26</v>
       </c>
       <c r="FN6" t="n">
-        <v>2.212891843100806e-07</v>
+        <v>8.523897844409647e-26</v>
       </c>
       <c r="FO6" t="n">
-        <v>2.189476191460926e-07</v>
+        <v>1.961621740339807e-26</v>
       </c>
       <c r="FP6" t="n">
-        <v>1.597447436552102e-07</v>
+        <v>9.925974227625973e-26</v>
       </c>
       <c r="FQ6" t="n">
-        <v>6.025929621955584e-08</v>
+        <v>4.354819852573021e-25</v>
       </c>
       <c r="FR6" t="n">
-        <v>1.055305958175268e-07</v>
+        <v>7.527348351771409e-26</v>
       </c>
       <c r="FS6" t="n">
-        <v>1.993046794268594e-08</v>
+        <v>2.372730160786003e-25</v>
       </c>
       <c r="FT6" t="n">
-        <v>1.654714537835389e-06</v>
+        <v>1.850676003665853e-26</v>
       </c>
       <c r="FU6" t="n">
-        <v>4.04469119530404e-07</v>
+        <v>1.411410210098804e-26</v>
       </c>
       <c r="FV6" t="n">
-        <v>3.736327585102117e-07</v>
+        <v>4.253187450886938e-25</v>
       </c>
       <c r="FW6" t="n">
-        <v>1.322527225511294e-07</v>
+        <v>1.568400309511189e-26</v>
       </c>
       <c r="FX6" t="n">
-        <v>2.152693383550286e-07</v>
+        <v>3.788208674484451e-26</v>
       </c>
       <c r="FY6" t="n">
-        <v>2.642608478709008e-07</v>
+        <v>6.65550297710664e-26</v>
       </c>
       <c r="FZ6" t="n">
-        <v>2.71742681690057e-08</v>
+        <v>2.640780597407753e-26</v>
       </c>
       <c r="GA6" t="n">
-        <v>2.839079229488561e-07</v>
+        <v>1.482872225871281e-26</v>
       </c>
       <c r="GB6" t="n">
-        <v>2.31476192880109e-07</v>
+        <v>3.440719143520089e-25</v>
       </c>
       <c r="GC6" t="n">
-        <v>2.446705877900968e-07</v>
+        <v>2.532021638629854e-27</v>
       </c>
       <c r="GD6" t="n">
-        <v>4.664136099563621e-07</v>
+        <v>1.928437535989707e-25</v>
       </c>
       <c r="GE6" t="n">
-        <v>2.649416046551778e-07</v>
+        <v>6.289072156250822e-26</v>
       </c>
       <c r="GF6" t="n">
-        <v>2.704527446439897e-07</v>
+        <v>1.901367527508015e-25</v>
       </c>
       <c r="GG6" t="n">
-        <v>8.70787175699661e-07</v>
+        <v>2.965929156127949e-25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8.221237294492312e-06</v>
+        <v>7.959893757796761e-40</v>
       </c>
       <c r="B7" t="n">
-        <v>1.490891190769617e-05</v>
+        <v>1.341128109565174e-39</v>
       </c>
       <c r="C7" t="n">
-        <v>1.643159066588851e-06</v>
+        <v>5.028699669076039e-40</v>
       </c>
       <c r="D7" t="n">
-        <v>1.283749952563085e-05</v>
+        <v>2.40718273188185e-39</v>
       </c>
       <c r="E7" t="n">
-        <v>1.473182237532455e-05</v>
+        <v>6.350152146903628e-40</v>
       </c>
       <c r="F7" t="n">
-        <v>4.672777322412003e-06</v>
+        <v>1.46246654359106e-39</v>
       </c>
       <c r="G7" t="n">
-        <v>8.908580639399588e-06</v>
+        <v>7.059461403575563e-41</v>
       </c>
       <c r="H7" t="n">
-        <v>1.221206002810504e-05</v>
+        <v>1.087046073312262e-39</v>
       </c>
       <c r="I7" t="n">
-        <v>2.038004822679795e-05</v>
+        <v>3.2267839867854e-39</v>
       </c>
       <c r="J7" t="n">
-        <v>8.819902177492622e-06</v>
+        <v>6.8032760183277e-40</v>
       </c>
       <c r="K7" t="n">
-        <v>1.180763774755178e-05</v>
+        <v>1.756110038088789e-39</v>
       </c>
       <c r="L7" t="n">
-        <v>8.625697773823049e-07</v>
+        <v>1.729496577654332e-40</v>
       </c>
       <c r="M7" t="n">
-        <v>1.433805118722375e-05</v>
+        <v>3.674030812450094e-39</v>
       </c>
       <c r="N7" t="n">
-        <v>2.079614205285907e-05</v>
+        <v>1.513395334978481e-39</v>
       </c>
       <c r="O7" t="n">
-        <v>6.851690613984829e-06</v>
+        <v>2.969244947220999e-39</v>
       </c>
       <c r="P7" t="n">
-        <v>6.927317599547678e-07</v>
+        <v>1.55277882831833e-40</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.026072934313561e-06</v>
+        <v>1.391618294533261e-39</v>
       </c>
       <c r="R7" t="n">
-        <v>1.132223133026855e-05</v>
+        <v>2.655557279489567e-39</v>
       </c>
       <c r="S7" t="n">
-        <v>6.682934667878726e-07</v>
+        <v>1.524048005904278e-39</v>
       </c>
       <c r="T7" t="n">
-        <v>4.969265319232363e-06</v>
+        <v>2.449178245559201e-39</v>
       </c>
       <c r="U7" t="n">
-        <v>4.800253009307198e-06</v>
+        <v>8.430211561378099e-40</v>
       </c>
       <c r="V7" t="n">
-        <v>5.964914635114837e-06</v>
+        <v>2.627654624467931e-39</v>
       </c>
       <c r="W7" t="n">
-        <v>1.367619006487075e-05</v>
+        <v>4.072892203440117e-39</v>
       </c>
       <c r="X7" t="n">
-        <v>4.022670054837363e-06</v>
+        <v>2.027100141612244e-39</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.618773123685969e-06</v>
+        <v>2.2981294814927e-40</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.107738732272992e-06</v>
+        <v>9.652255926146486e-40</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.716498213179875e-06</v>
+        <v>7.363599222272622e-40</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.256834593732492e-06</v>
+        <v>6.460966829462434e-41</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.894358880846994e-06</v>
+        <v>5.303326142114416e-40</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.056637120200321e-05</v>
+        <v>1.37530718040852e-39</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.056950895872433e-05</v>
+        <v>1.61729320831738e-39</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.763527734510717e-06</v>
+        <v>4.444176040652228e-40</v>
       </c>
       <c r="AG7" t="n">
-        <v>6.647308509855065e-06</v>
+        <v>5.595875222511508e-40</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.063496597453195e-06</v>
+        <v>2.807375356412982e-40</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.078641839238117e-06</v>
+        <v>8.69725700972448e-40</v>
       </c>
       <c r="AJ7" t="n">
-        <v>6.49716366751818e-06</v>
+        <v>3.075948220085476e-40</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.56654868987971e-06</v>
+        <v>2.35709331827456e-39</v>
       </c>
       <c r="AL7" t="n">
-        <v>6.534244676004164e-06</v>
+        <v>2.450659418035992e-39</v>
       </c>
       <c r="AM7" t="n">
-        <v>5.169204086996615e-06</v>
+        <v>5.321192697534558e-40</v>
       </c>
       <c r="AN7" t="n">
-        <v>3.632318112067878e-06</v>
+        <v>2.103826837727885e-39</v>
       </c>
       <c r="AO7" t="n">
-        <v>9.675952242105268e-06</v>
+        <v>2.781754015291267e-39</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.358934792340733e-06</v>
+        <v>4.941524891610392e-40</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.439985792079824e-06</v>
+        <v>3.71156319051857e-40</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.745733692994691e-06</v>
+        <v>1.511645113196539e-39</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.575735488288046e-07</v>
+        <v>5.707866995780348e-40</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.014983692788519e-06</v>
+        <v>1.680645911889505e-39</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.023642289510462e-05</v>
+        <v>1.719950932515352e-39</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.539497811289039e-06</v>
+        <v>1.083256962264728e-39</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.006464935926488e-05</v>
+        <v>2.387896661117348e-40</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.279152906543459e-06</v>
+        <v>1.286802570700229e-39</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.240954406966921e-05</v>
+        <v>2.061127872221444e-40</v>
       </c>
       <c r="AZ7" t="n">
-        <v>9.758488886291161e-06</v>
+        <v>7.264317226075208e-40</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.34098700073082e-05</v>
+        <v>2.114082941188279e-40</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.828935849829577e-06</v>
+        <v>8.929648347048108e-40</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.973495146667119e-06</v>
+        <v>5.063970351423094e-40</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.228782801073976e-06</v>
+        <v>1.554142291724118e-39</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.934981577913277e-06</v>
+        <v>7.070853960090524e-40</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.557214303233195e-06</v>
+        <v>1.767827695847474e-39</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.808297025098e-07</v>
+        <v>1.667120579111842e-39</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.055041245010216e-06</v>
+        <v>1.03910765284771e-39</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.577610414140509e-06</v>
+        <v>1.180047449792572e-39</v>
       </c>
       <c r="BJ7" t="n">
-        <v>5.135731953487266e-06</v>
+        <v>4.76140198700608e-40</v>
       </c>
       <c r="BK7" t="n">
-        <v>2.427619983791374e-05</v>
+        <v>5.99041080514216e-40</v>
       </c>
       <c r="BL7" t="n">
-        <v>7.891859240771737e-06</v>
+        <v>2.483225594346901e-39</v>
       </c>
       <c r="BM7" t="n">
-        <v>7.946090590849053e-06</v>
+        <v>1.553471069759706e-39</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.279740172321908e-05</v>
+        <v>3.891027484844649e-40</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.225916366820456e-05</v>
+        <v>1.363351301910901e-40</v>
       </c>
       <c r="BP7" t="n">
-        <v>1.20815320769907e-05</v>
+        <v>9.061034091063202e-40</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.064234872203087e-06</v>
+        <v>1.36398609011524e-39</v>
       </c>
       <c r="BR7" t="n">
-        <v>6.127491360530257e-06</v>
+        <v>1.797701977808414e-39</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.87603494245559e-06</v>
+        <v>1.901421886242344e-41</v>
       </c>
       <c r="BT7" t="n">
-        <v>3.680435838759877e-06</v>
+        <v>2.636739242412149e-40</v>
       </c>
       <c r="BU7" t="n">
-        <v>6.749413842044305e-06</v>
+        <v>1.896465493574027e-39</v>
       </c>
       <c r="BV7" t="n">
-        <v>1.391183468513191e-05</v>
+        <v>4.458721518711919e-40</v>
       </c>
       <c r="BW7" t="n">
-        <v>3.513446699798806e-06</v>
+        <v>1.668151934781585e-39</v>
       </c>
       <c r="BX7" t="n">
-        <v>5.475842499436112e-06</v>
+        <v>1.589717055837932e-39</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.310517841891851e-06</v>
+        <v>2.74121445071835e-39</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.662955234380206e-06</v>
+        <v>1.528450885679187e-39</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.529624104383402e-06</v>
+        <v>2.583798186429957e-40</v>
       </c>
       <c r="CB7" t="n">
-        <v>8.680442988406867e-06</v>
+        <v>6.03609313507915e-40</v>
       </c>
       <c r="CC7" t="n">
-        <v>8.911745680961758e-06</v>
+        <v>1.994965565228347e-39</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.729798668748117e-06</v>
+        <v>1.783021975096148e-39</v>
       </c>
       <c r="CE7" t="n">
-        <v>6.736377144989092e-08</v>
+        <v>7.236991906020875e-40</v>
       </c>
       <c r="CF7" t="n">
-        <v>1.859105282164819e-06</v>
+        <v>1.331625904678587e-40</v>
       </c>
       <c r="CG7" t="n">
-        <v>1.988169060496148e-06</v>
+        <v>1.332490505831076e-39</v>
       </c>
       <c r="CH7" t="n">
-        <v>3.504657570374548e-06</v>
+        <v>2.45930683085934e-40</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.381658421450993e-06</v>
+        <v>2.75395785895292e-40</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.620549821585882e-08</v>
+        <v>5.986164870795256e-40</v>
       </c>
       <c r="CK7" t="n">
-        <v>4.887791419605492e-06</v>
+        <v>2.288320392242426e-41</v>
       </c>
       <c r="CL7" t="n">
-        <v>4.137322775932262e-06</v>
+        <v>1.05143627673684e-39</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.059848839053302e-06</v>
+        <v>1.384138163330695e-39</v>
       </c>
       <c r="CN7" t="n">
-        <v>9.00275608728407e-06</v>
+        <v>5.160982244108301e-40</v>
       </c>
       <c r="CO7" t="n">
-        <v>3.929297690774547e-06</v>
+        <v>4.200097874136131e-40</v>
       </c>
       <c r="CP7" t="n">
-        <v>5.307161700329743e-06</v>
+        <v>1.41411754267646e-39</v>
       </c>
       <c r="CQ7" t="n">
-        <v>9.63006095844321e-06</v>
+        <v>7.768756647262856e-40</v>
       </c>
       <c r="CR7" t="n">
-        <v>9.371399301016936e-08</v>
+        <v>1.439259639723376e-40</v>
       </c>
       <c r="CS7" t="n">
-        <v>1.375717783957953e-05</v>
+        <v>1.140190317571781e-39</v>
       </c>
       <c r="CT7" t="n">
-        <v>1.132253782998305e-05</v>
+        <v>1.613652634907064e-39</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.263761191694357e-06</v>
+        <v>1.126704221151119e-39</v>
       </c>
       <c r="CV7" t="n">
-        <v>7.729616982032894e-07</v>
+        <v>1.775625921801441e-39</v>
       </c>
       <c r="CW7" t="n">
-        <v>3.438930434640497e-06</v>
+        <v>4.076769596290904e-40</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.249230535904644e-06</v>
+        <v>3.732022148097712e-40</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.43926183682197e-06</v>
+        <v>1.228086763746555e-39</v>
       </c>
       <c r="CZ7" t="n">
-        <v>3.074237838518457e-06</v>
+        <v>2.051627068633321e-40</v>
       </c>
       <c r="DA7" t="n">
-        <v>3.479545966911246e-07</v>
+        <v>1.19121579855324e-40</v>
       </c>
       <c r="DB7" t="n">
-        <v>2.452031822031131e-06</v>
+        <v>2.657660628484518e-40</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.659568508533994e-06</v>
+        <v>2.845350544796184e-40</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.827097662499e-06</v>
+        <v>8.309840023292598e-40</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.29918335005641e-05</v>
+        <v>1.678860657645955e-39</v>
       </c>
       <c r="DF7" t="n">
-        <v>3.847715106530814e-06</v>
+        <v>1.027618406738711e-39</v>
       </c>
       <c r="DG7" t="n">
-        <v>6.057000064174645e-06</v>
+        <v>4.081814270762473e-40</v>
       </c>
       <c r="DH7" t="n">
-        <v>1.401600184181007e-05</v>
+        <v>3.72692142168757e-40</v>
       </c>
       <c r="DI7" t="n">
-        <v>5.265421350486577e-06</v>
+        <v>1.43694749725724e-40</v>
       </c>
       <c r="DJ7" t="n">
-        <v>7.945541256049182e-06</v>
+        <v>5.045557289601866e-40</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.781988991453545e-07</v>
+        <v>1.982893378958189e-40</v>
       </c>
       <c r="DL7" t="n">
-        <v>7.244888365676161e-06</v>
+        <v>1.104207775604848e-39</v>
       </c>
       <c r="DM7" t="n">
-        <v>5.619100193143822e-06</v>
+        <v>2.794161111894399e-40</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.734638317429926e-06</v>
+        <v>1.001365080009586e-39</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.596566221451212e-06</v>
+        <v>5.341189226620473e-41</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.884782230074052e-06</v>
+        <v>1.139240237212969e-39</v>
       </c>
       <c r="DQ7" t="n">
-        <v>7.974666004884057e-06</v>
+        <v>2.651532750300026e-39</v>
       </c>
       <c r="DR7" t="n">
-        <v>4.342027750681154e-06</v>
+        <v>1.588960354667197e-39</v>
       </c>
       <c r="DS7" t="n">
-        <v>3.480425220914185e-06</v>
+        <v>3.403165424489964e-40</v>
       </c>
       <c r="DT7" t="n">
-        <v>5.162646175449481e-06</v>
+        <v>1.336918608978342e-39</v>
       </c>
       <c r="DU7" t="n">
-        <v>7.484539423785463e-07</v>
+        <v>1.056710764156559e-39</v>
       </c>
       <c r="DV7" t="n">
-        <v>1.031198735290673e-06</v>
+        <v>1.436881636229417e-39</v>
       </c>
       <c r="DW7" t="n">
-        <v>8.091702738965978e-07</v>
+        <v>1.056513181073089e-39</v>
       </c>
       <c r="DX7" t="n">
-        <v>2.992060672113439e-06</v>
+        <v>7.676873506957078e-40</v>
       </c>
       <c r="DY7" t="n">
-        <v>1.154328970187635e-06</v>
+        <v>6.297729571353236e-40</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.440160526224645e-06</v>
+        <v>1.525355417371493e-40</v>
       </c>
       <c r="EA7" t="n">
-        <v>1.309194158238824e-05</v>
+        <v>1.414764942566979e-40</v>
       </c>
       <c r="EB7" t="n">
-        <v>3.283345222371281e-07</v>
+        <v>1.740784036784469e-39</v>
       </c>
       <c r="EC7" t="n">
-        <v>8.105193387564213e-07</v>
+        <v>9.06585455778048e-40</v>
       </c>
       <c r="ED7" t="n">
-        <v>4.818381057702936e-06</v>
+        <v>9.630956189488749e-40</v>
       </c>
       <c r="EE7" t="n">
-        <v>5.672837232850725e-06</v>
+        <v>2.041002423676811e-39</v>
       </c>
       <c r="EF7" t="n">
-        <v>1.543942744319793e-06</v>
+        <v>2.106696696982822e-39</v>
       </c>
       <c r="EG7" t="n">
-        <v>2.741895968938479e-06</v>
+        <v>4.347682628398821e-40</v>
       </c>
       <c r="EH7" t="n">
-        <v>3.176954351147288e-06</v>
+        <v>7.992305791276594e-41</v>
       </c>
       <c r="EI7" t="n">
-        <v>3.170440322719514e-06</v>
+        <v>6.023061059360929e-40</v>
       </c>
       <c r="EJ7" t="n">
-        <v>4.810892278328538e-06</v>
+        <v>1.39975703601406e-39</v>
       </c>
       <c r="EK7" t="n">
-        <v>3.73158763977699e-06</v>
+        <v>1.019083097792509e-39</v>
       </c>
       <c r="EL7" t="n">
-        <v>9.03808086150093e-08</v>
+        <v>8.636482695326713e-41</v>
       </c>
       <c r="EM7" t="n">
-        <v>8.510760380886495e-06</v>
+        <v>3.663260432453294e-40</v>
       </c>
       <c r="EN7" t="n">
-        <v>3.98614884034032e-06</v>
+        <v>1.35149211300732e-39</v>
       </c>
       <c r="EO7" t="n">
-        <v>4.141842850913235e-07</v>
+        <v>1.547594024000328e-39</v>
       </c>
       <c r="EP7" t="n">
-        <v>3.599702722567599e-06</v>
+        <v>1.015827881459882e-39</v>
       </c>
       <c r="EQ7" t="n">
-        <v>4.360912839729281e-07</v>
+        <v>9.977090923161622e-40</v>
       </c>
       <c r="ER7" t="n">
-        <v>8.246496690844651e-06</v>
+        <v>1.121320432451183e-39</v>
       </c>
       <c r="ES7" t="n">
-        <v>1.091886133508524e-05</v>
+        <v>2.751869924241076e-40</v>
       </c>
       <c r="ET7" t="n">
-        <v>5.512759344128426e-06</v>
+        <v>2.336176136097583e-39</v>
       </c>
       <c r="EU7" t="n">
-        <v>6.622488854191033e-06</v>
+        <v>1.553768145034143e-39</v>
       </c>
       <c r="EV7" t="n">
-        <v>1.274814439966576e-05</v>
+        <v>1.227531849554682e-39</v>
       </c>
       <c r="EW7" t="n">
-        <v>4.4586022340809e-07</v>
+        <v>6.580021146991471e-40</v>
       </c>
       <c r="EX7" t="n">
-        <v>2.117554345204553e-07</v>
+        <v>2.049648435201695e-39</v>
       </c>
       <c r="EY7" t="n">
-        <v>3.867243322019931e-06</v>
+        <v>4.317358529630832e-40</v>
       </c>
       <c r="EZ7" t="n">
-        <v>2.68737085207249e-06</v>
+        <v>1.07015762422022e-40</v>
       </c>
       <c r="FA7" t="n">
-        <v>1.127049245042144e-06</v>
+        <v>1.196448247019029e-39</v>
       </c>
       <c r="FB7" t="n">
-        <v>2.514327889002743e-06</v>
+        <v>1.395370971820723e-40</v>
       </c>
       <c r="FC7" t="n">
-        <v>2.087971324726823e-07</v>
+        <v>4.893978834715851e-40</v>
       </c>
       <c r="FD7" t="n">
-        <v>1.696700905995385e-06</v>
+        <v>6.879408563894468e-40</v>
       </c>
       <c r="FE7" t="n">
-        <v>3.963855306210462e-06</v>
+        <v>7.121258665852288e-41</v>
       </c>
       <c r="FF7" t="n">
-        <v>1.160539227385016e-06</v>
+        <v>8.375729077085151e-40</v>
       </c>
       <c r="FG7" t="n">
-        <v>2.607615670058294e-06</v>
+        <v>2.197912819219582e-39</v>
       </c>
       <c r="FH7" t="n">
-        <v>7.962158633745275e-06</v>
+        <v>4.527735468079916e-40</v>
       </c>
       <c r="FI7" t="n">
-        <v>1.903084012155887e-06</v>
+        <v>1.012449350862395e-39</v>
       </c>
       <c r="FJ7" t="n">
-        <v>1.023195181915071e-07</v>
+        <v>1.263264960394965e-39</v>
       </c>
       <c r="FK7" t="n">
-        <v>7.796526006131899e-06</v>
+        <v>1.123269638615059e-39</v>
       </c>
       <c r="FL7" t="n">
-        <v>7.670170816709287e-06</v>
+        <v>1.763213220004452e-39</v>
       </c>
       <c r="FM7" t="n">
-        <v>2.931208655354567e-06</v>
+        <v>1.165503373031344e-39</v>
       </c>
       <c r="FN7" t="n">
-        <v>4.155123860982712e-06</v>
+        <v>1.017650970761969e-40</v>
       </c>
       <c r="FO7" t="n">
-        <v>7.446476047334727e-06</v>
+        <v>1.434586309344853e-39</v>
       </c>
       <c r="FP7" t="n">
-        <v>1.201390773530875e-06</v>
+        <v>2.584638965508552e-40</v>
       </c>
       <c r="FQ7" t="n">
-        <v>8.617666026111692e-06</v>
+        <v>1.304351031368969e-39</v>
       </c>
       <c r="FR7" t="n">
-        <v>6.341478638205444e-06</v>
+        <v>1.208130872316105e-39</v>
       </c>
       <c r="FS7" t="n">
-        <v>2.549254531913903e-06</v>
+        <v>8.610993076260644e-40</v>
       </c>
       <c r="FT7" t="n">
-        <v>3.344181823194958e-05</v>
+        <v>4.15358877810519e-40</v>
       </c>
       <c r="FU7" t="n">
-        <v>5.687324573955266e-06</v>
+        <v>3.675856704349109e-39</v>
       </c>
       <c r="FV7" t="n">
-        <v>6.213535925780889e-06</v>
+        <v>1.681761345467108e-39</v>
       </c>
       <c r="FW7" t="n">
-        <v>7.162719612097135e-06</v>
+        <v>1.295231380963143e-39</v>
       </c>
       <c r="FX7" t="n">
-        <v>3.715258344527683e-06</v>
+        <v>2.151721817940043e-40</v>
       </c>
       <c r="FY7" t="n">
-        <v>4.361312676337548e-06</v>
+        <v>5.93454103536953e-40</v>
       </c>
       <c r="FZ7" t="n">
-        <v>7.193739293143153e-07</v>
+        <v>1.775247571216073e-39</v>
       </c>
       <c r="GA7" t="n">
-        <v>3.27431871482986e-06</v>
+        <v>6.709557177033657e-40</v>
       </c>
       <c r="GB7" t="n">
-        <v>2.345540906389942e-06</v>
+        <v>5.510564172003413e-40</v>
       </c>
       <c r="GC7" t="n">
-        <v>2.803340976242907e-06</v>
+        <v>7.715269084879578e-41</v>
       </c>
       <c r="GD7" t="n">
-        <v>4.885106591245858e-06</v>
+        <v>6.529798610030069e-40</v>
       </c>
       <c r="GE7" t="n">
-        <v>9.212285476678517e-07</v>
+        <v>1.817828827651512e-39</v>
       </c>
       <c r="GF7" t="n">
-        <v>1.417768430655997e-06</v>
+        <v>1.866333372695651e-40</v>
       </c>
       <c r="GG7" t="n">
-        <v>4.574437753035454e-06</v>
+        <v>2.649467236363611e-39</v>
       </c>
     </row>
     <row r="8">
@@ -4982,5123 +4982,5123 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3.11771282213158e-06</v>
+        <v>1.153242621398931e-07</v>
       </c>
       <c r="B9" t="n">
-        <v>2.212326762673911e-05</v>
+        <v>1.517577629783773e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>1.467133415644639e-06</v>
+        <v>4.687889259002986e-07</v>
       </c>
       <c r="D9" t="n">
-        <v>1.188205260405084e-05</v>
+        <v>9.793848221306689e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.960024565050844e-05</v>
+        <v>1.645181555431918e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>8.459283890260849e-06</v>
+        <v>6.840061246293772e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>4.646848537959158e-06</v>
+        <v>2.761974258191913e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>7.744516551611014e-06</v>
+        <v>1.269768734601939e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>9.398635484103579e-06</v>
+        <v>3.43104389344262e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>4.372547209641198e-06</v>
+        <v>8.417664787430112e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>1.571254324517213e-05</v>
+        <v>1.483926439505012e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>1.498723690929182e-06</v>
+        <v>6.201389624038711e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>5.908109415031504e-06</v>
+        <v>1.396740344716818e-06</v>
       </c>
       <c r="N9" t="n">
-        <v>1.984555638046004e-05</v>
+        <v>3.932484275992465e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>4.297903615224641e-07</v>
+        <v>3.765166241009865e-07</v>
       </c>
       <c r="P9" t="n">
-        <v>3.529052946760203e-06</v>
+        <v>3.769130216824124e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.492879613986588e-06</v>
+        <v>6.600510715770724e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>4.205315235594753e-06</v>
+        <v>3.853111962826006e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>8.938975497585488e-07</v>
+        <v>1.227130326242332e-07</v>
       </c>
       <c r="T9" t="n">
-        <v>1.156556095338601e-06</v>
+        <v>1.869744181703936e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>1.06189065718354e-06</v>
+        <v>1.550315147369474e-07</v>
       </c>
       <c r="V9" t="n">
-        <v>6.929716619197279e-06</v>
+        <v>1.82252847480413e-07</v>
       </c>
       <c r="W9" t="n">
-        <v>1.726535447232891e-05</v>
+        <v>4.296006466120161e-07</v>
       </c>
       <c r="X9" t="n">
-        <v>4.152184828853933e-06</v>
+        <v>2.686734603685181e-07</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.961600552633172e-06</v>
+        <v>1.898364700991806e-07</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.620117013269919e-06</v>
+        <v>1.971375951370646e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.911011165451782e-07</v>
+        <v>3.717533445524168e-07</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.280620376244769e-06</v>
+        <v>1.013337964650418e-07</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.595949129296059e-06</v>
+        <v>1.713555661808641e-07</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.927539298980264e-06</v>
+        <v>2.407587373909337e-07</v>
       </c>
       <c r="AE9" t="n">
-        <v>4.076384811924072e-06</v>
+        <v>2.355753281335637e-07</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.144794441643171e-05</v>
+        <v>9.358344499332816e-08</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.459712039941223e-06</v>
+        <v>3.839975022401632e-07</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.731041826744331e-06</v>
+        <v>1.354855925228549e-07</v>
       </c>
       <c r="AI9" t="n">
-        <v>8.3921725035907e-07</v>
+        <v>9.484955043603804e-09</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.531175482545223e-07</v>
+        <v>2.903154161515431e-08</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.103452516166726e-06</v>
+        <v>9.6729372955906e-08</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.425790287612472e-06</v>
+        <v>4.47406762305036e-07</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.483837195337401e-07</v>
+        <v>3.556955334715894e-07</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.643452319261996e-07</v>
+        <v>4.602713943313574e-07</v>
       </c>
       <c r="AO9" t="n">
-        <v>9.58390228333883e-06</v>
+        <v>1.366194055663073e-07</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.08535822518752e-06</v>
+        <v>2.055244578968995e-07</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.928930371126626e-06</v>
+        <v>9.890518981592322e-08</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.970152415102348e-06</v>
+        <v>2.660082714101009e-07</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.988938144379063e-06</v>
+        <v>1.225405821259073e-08</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.570064682709926e-06</v>
+        <v>1.302043415307708e-07</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.332499651762191e-06</v>
+        <v>8.481354711875611e-07</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.780802676876192e-06</v>
+        <v>2.172866686578345e-07</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.198197297635488e-06</v>
+        <v>3.024471766366332e-07</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.326948950008955e-05</v>
+        <v>7.823318242117239e-07</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.669155608396977e-05</v>
+        <v>3.02966327581089e-07</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.832075657963287e-06</v>
+        <v>1.258301836060127e-07</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.27462126329192e-05</v>
+        <v>2.003623507107477e-07</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.713438673003111e-06</v>
+        <v>4.394828323484035e-08</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.569340944726719e-06</v>
+        <v>1.553090100969712e-09</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.386838893173262e-06</v>
+        <v>2.759646235972468e-07</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.347554300285992e-06</v>
+        <v>2.533546137328813e-07</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.253276190662291e-06</v>
+        <v>2.848400413313357e-07</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.533683179237414e-06</v>
+        <v>5.70559450352448e-07</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.565375664038584e-06</v>
+        <v>2.750382748217817e-07</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.456199349078815e-06</v>
+        <v>2.871712467822363e-08</v>
       </c>
       <c r="BJ9" t="n">
-        <v>4.839273969992064e-06</v>
+        <v>9.085744068215718e-08</v>
       </c>
       <c r="BK9" t="n">
-        <v>3.948908670281526e-06</v>
+        <v>1.408119061352409e-07</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.804467729016324e-06</v>
+        <v>4.807604625511885e-08</v>
       </c>
       <c r="BM9" t="n">
-        <v>4.48942273578723e-06</v>
+        <v>7.602076124157975e-08</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.963614917916857e-07</v>
+        <v>8.968243037088541e-08</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.280689609004185e-06</v>
+        <v>1.985011977012618e-07</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.853398877457948e-06</v>
+        <v>2.317009091257205e-07</v>
       </c>
       <c r="BQ9" t="n">
-        <v>2.113314849339076e-06</v>
+        <v>1.881316435969893e-08</v>
       </c>
       <c r="BR9" t="n">
-        <v>2.912119953180081e-06</v>
+        <v>2.972902457543114e-08</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.416245140717365e-06</v>
+        <v>1.03782106464223e-07</v>
       </c>
       <c r="BT9" t="n">
-        <v>1.934876536324737e-06</v>
+        <v>3.802794168450419e-08</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.399478037455992e-06</v>
+        <v>1.166072962632825e-07</v>
       </c>
       <c r="BV9" t="n">
-        <v>5.682995833922178e-06</v>
+        <v>5.656237362927641e-07</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.086790121007652e-06</v>
+        <v>3.386182925169123e-07</v>
       </c>
       <c r="BX9" t="n">
-        <v>8.969272130343597e-06</v>
+        <v>8.241020168497926e-07</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.386395615554648e-05</v>
+        <v>2.775004190880281e-07</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.060714621165971e-07</v>
+        <v>2.4914777441154e-07</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.152599103690591e-06</v>
+        <v>2.90081061393721e-08</v>
       </c>
       <c r="CB9" t="n">
-        <v>6.601637323910836e-06</v>
+        <v>1.082291660736701e-07</v>
       </c>
       <c r="CC9" t="n">
-        <v>6.94207983542583e-07</v>
+        <v>2.477405587342218e-07</v>
       </c>
       <c r="CD9" t="n">
-        <v>1.559580482535239e-06</v>
+        <v>4.422673072213001e-08</v>
       </c>
       <c r="CE9" t="n">
-        <v>3.370500735400128e-06</v>
+        <v>5.057479484094074e-07</v>
       </c>
       <c r="CF9" t="n">
-        <v>1.565203888276301e-06</v>
+        <v>1.063289900571363e-07</v>
       </c>
       <c r="CG9" t="n">
-        <v>1.878518332887325e-06</v>
+        <v>3.665952306164399e-07</v>
       </c>
       <c r="CH9" t="n">
-        <v>3.461572305241134e-06</v>
+        <v>6.556613030284097e-09</v>
       </c>
       <c r="CI9" t="n">
-        <v>5.477415925270179e-07</v>
+        <v>1.251419092795913e-07</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.768792230905092e-06</v>
+        <v>2.760864958872844e-08</v>
       </c>
       <c r="CK9" t="n">
-        <v>7.628801768078119e-07</v>
+        <v>4.336147796379919e-08</v>
       </c>
       <c r="CL9" t="n">
-        <v>9.85164206213085e-07</v>
+        <v>3.007612825456363e-09</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.834287215591758e-06</v>
+        <v>2.714531319725211e-07</v>
       </c>
       <c r="CN9" t="n">
-        <v>5.538430741580669e-06</v>
+        <v>6.492438160421443e-07</v>
       </c>
       <c r="CO9" t="n">
-        <v>2.544937842685613e-06</v>
+        <v>4.757636418162292e-07</v>
       </c>
       <c r="CP9" t="n">
-        <v>3.585094873415073e-06</v>
+        <v>3.036337261619337e-07</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.365335487615084e-06</v>
+        <v>7.930300682801317e-08</v>
       </c>
       <c r="CR9" t="n">
-        <v>5.701530881196959e-06</v>
+        <v>8.681107743768735e-08</v>
       </c>
       <c r="CS9" t="n">
-        <v>1.527410631751991e-06</v>
+        <v>2.715044615797524e-07</v>
       </c>
       <c r="CT9" t="n">
-        <v>8.768166708250646e-07</v>
+        <v>8.914391713688019e-08</v>
       </c>
       <c r="CU9" t="n">
-        <v>5.289858108881162e-06</v>
+        <v>1.424831452823128e-07</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.097820927498105e-06</v>
+        <v>5.330733898745166e-08</v>
       </c>
       <c r="CW9" t="n">
-        <v>4.206429366604425e-06</v>
+        <v>4.798912982550974e-07</v>
       </c>
       <c r="CX9" t="n">
-        <v>9.673968861534377e-07</v>
+        <v>1.253510362175803e-07</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.160722831627936e-06</v>
+        <v>3.612289276588854e-07</v>
       </c>
       <c r="CZ9" t="n">
-        <v>4.469994109967956e-06</v>
+        <v>1.114526568812835e-07</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.047006890075863e-06</v>
+        <v>1.248564984734912e-07</v>
       </c>
       <c r="DB9" t="n">
-        <v>2.268716798425885e-06</v>
+        <v>1.362705859264679e-08</v>
       </c>
       <c r="DC9" t="n">
-        <v>6.101024609961314e-07</v>
+        <v>2.13556816675009e-08</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.801859011469787e-07</v>
+        <v>4.894127769716761e-08</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.903207703435328e-06</v>
+        <v>2.662309839251975e-07</v>
       </c>
       <c r="DF9" t="n">
-        <v>8.164562132151332e-06</v>
+        <v>2.359477093705209e-07</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.819792254944332e-06</v>
+        <v>1.06143957623317e-07</v>
       </c>
       <c r="DH9" t="n">
-        <v>1.316306315857219e-05</v>
+        <v>2.286936222617442e-07</v>
       </c>
       <c r="DI9" t="n">
-        <v>1.037580204865662e-06</v>
+        <v>4.707563761030542e-08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>8.030813660298008e-06</v>
+        <v>7.688121286264504e-07</v>
       </c>
       <c r="DK9" t="n">
-        <v>7.142699359974358e-06</v>
+        <v>9.417291835234209e-08</v>
       </c>
       <c r="DL9" t="n">
-        <v>4.565857125271577e-06</v>
+        <v>8.069005730249046e-07</v>
       </c>
       <c r="DM9" t="n">
-        <v>4.042079126520548e-06</v>
+        <v>1.614939861838138e-07</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.285575535803218e-06</v>
+        <v>4.576062195837949e-08</v>
       </c>
       <c r="DO9" t="n">
-        <v>5.849880380992545e-06</v>
+        <v>2.830630023709091e-07</v>
       </c>
       <c r="DP9" t="n">
-        <v>1.808933689062542e-06</v>
+        <v>1.362888610856317e-07</v>
       </c>
       <c r="DQ9" t="n">
-        <v>2.831266556313494e-06</v>
+        <v>4.429296325270116e-07</v>
       </c>
       <c r="DR9" t="n">
-        <v>3.691392748805811e-06</v>
+        <v>2.153237943502972e-08</v>
       </c>
       <c r="DS9" t="n">
-        <v>6.000200301059522e-06</v>
+        <v>1.114061802809374e-07</v>
       </c>
       <c r="DT9" t="n">
-        <v>2.120846602338133e-06</v>
+        <v>8.897391978734959e-08</v>
       </c>
       <c r="DU9" t="n">
-        <v>2.159715677407803e-06</v>
+        <v>2.903268239151657e-07</v>
       </c>
       <c r="DV9" t="n">
-        <v>1.497610469414212e-06</v>
+        <v>4.660381875964958e-07</v>
       </c>
       <c r="DW9" t="n">
-        <v>5.042401880928082e-06</v>
+        <v>2.353520045517143e-09</v>
       </c>
       <c r="DX9" t="n">
-        <v>6.439265689550666e-07</v>
+        <v>3.733443065812025e-08</v>
       </c>
       <c r="DY9" t="n">
-        <v>3.615538844314869e-06</v>
+        <v>1.561766822533173e-07</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.219168204144808e-06</v>
+        <v>3.237287558022217e-07</v>
       </c>
       <c r="EA9" t="n">
-        <v>8.736706149647944e-06</v>
+        <v>2.055368355513565e-07</v>
       </c>
       <c r="EB9" t="n">
-        <v>5.886087706130638e-07</v>
+        <v>5.005571210858761e-07</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.875253133221122e-06</v>
+        <v>6.116537321076976e-08</v>
       </c>
       <c r="ED9" t="n">
-        <v>2.798570051254501e-07</v>
+        <v>8.382159535358369e-07</v>
       </c>
       <c r="EE9" t="n">
-        <v>3.617900574681698e-06</v>
+        <v>3.807996336036013e-07</v>
       </c>
       <c r="EF9" t="n">
-        <v>1.50124463971224e-07</v>
+        <v>1.557479123448502e-07</v>
       </c>
       <c r="EG9" t="n">
-        <v>1.26824988910812e-06</v>
+        <v>3.305661380181846e-07</v>
       </c>
       <c r="EH9" t="n">
-        <v>2.867100647563348e-06</v>
+        <v>1.602595602889778e-07</v>
       </c>
       <c r="EI9" t="n">
-        <v>4.128831278649159e-06</v>
+        <v>2.689177449610725e-07</v>
       </c>
       <c r="EJ9" t="n">
-        <v>4.731304215965793e-06</v>
+        <v>1.76427992215622e-08</v>
       </c>
       <c r="EK9" t="n">
-        <v>1.540285211376613e-06</v>
+        <v>9.715620308270445e-08</v>
       </c>
       <c r="EL9" t="n">
-        <v>2.053225216513965e-06</v>
+        <v>7.667944856848408e-08</v>
       </c>
       <c r="EM9" t="n">
-        <v>1.800915811145387e-06</v>
+        <v>8.518644278865395e-08</v>
       </c>
       <c r="EN9" t="n">
-        <v>9.592702099325834e-07</v>
+        <v>1.41894709315693e-08</v>
       </c>
       <c r="EO9" t="n">
-        <v>2.743172217378742e-06</v>
+        <v>1.453619660196637e-07</v>
       </c>
       <c r="EP9" t="n">
-        <v>5.512190455192467e-06</v>
+        <v>4.444105456968828e-07</v>
       </c>
       <c r="EQ9" t="n">
-        <v>2.177154328819597e-06</v>
+        <v>1.604521742137877e-07</v>
       </c>
       <c r="ER9" t="n">
-        <v>2.182616071877419e-06</v>
+        <v>8.487218394748197e-08</v>
       </c>
       <c r="ES9" t="n">
-        <v>1.902251142382738e-06</v>
+        <v>1.322987657204067e-07</v>
       </c>
       <c r="ET9" t="n">
-        <v>1.026205336529529e-05</v>
+        <v>5.527103752456242e-08</v>
       </c>
       <c r="EU9" t="n">
-        <v>6.739948275935603e-06</v>
+        <v>1.835398819594047e-07</v>
       </c>
       <c r="EV9" t="n">
-        <v>2.300087771800463e-06</v>
+        <v>1.563007288041263e-07</v>
       </c>
       <c r="EW9" t="n">
-        <v>2.7216822218179e-07</v>
+        <v>3.659853575754823e-07</v>
       </c>
       <c r="EX9" t="n">
-        <v>1.885832261905307e-06</v>
+        <v>4.315819879252558e-08</v>
       </c>
       <c r="EY9" t="n">
-        <v>2.676145413715858e-06</v>
+        <v>5.500361339727533e-07</v>
       </c>
       <c r="EZ9" t="n">
-        <v>4.852623192164174e-09</v>
+        <v>9.570922543389315e-08</v>
       </c>
       <c r="FA9" t="n">
-        <v>2.732991561060771e-06</v>
+        <v>4.080995381627872e-07</v>
       </c>
       <c r="FB9" t="n">
-        <v>4.232369064993691e-06</v>
+        <v>6.027509868999914e-08</v>
       </c>
       <c r="FC9" t="n">
-        <v>1.749857347022044e-06</v>
+        <v>1.416239570062316e-07</v>
       </c>
       <c r="FD9" t="n">
-        <v>1.918351244967198e-06</v>
+        <v>4.587189295079952e-08</v>
       </c>
       <c r="FE9" t="n">
-        <v>4.97682151490153e-07</v>
+        <v>6.761801074617324e-08</v>
       </c>
       <c r="FF9" t="n">
-        <v>1.233037210113253e-06</v>
+        <v>9.723855498577905e-08</v>
       </c>
       <c r="FG9" t="n">
-        <v>6.681443665002007e-07</v>
+        <v>4.170737710751382e-08</v>
       </c>
       <c r="FH9" t="n">
-        <v>5.725788923882646e-06</v>
+        <v>2.083074690517606e-07</v>
       </c>
       <c r="FI9" t="n">
-        <v>4.539930159808137e-06</v>
+        <v>4.450465240779522e-08</v>
       </c>
       <c r="FJ9" t="n">
-        <v>4.367791007098276e-06</v>
+        <v>4.220119365072605e-09</v>
       </c>
       <c r="FK9" t="n">
-        <v>6.938602837180952e-06</v>
+        <v>1.069330721747974e-07</v>
       </c>
       <c r="FL9" t="n">
-        <v>1.568521383887855e-06</v>
+        <v>3.870792397719924e-08</v>
       </c>
       <c r="FM9" t="n">
-        <v>6.898314381942328e-07</v>
+        <v>5.148912407548778e-09</v>
       </c>
       <c r="FN9" t="n">
-        <v>5.060247985966271e-06</v>
+        <v>3.545279696481884e-07</v>
       </c>
       <c r="FO9" t="n">
-        <v>1.028056999530236e-06</v>
+        <v>8.191365807874718e-09</v>
       </c>
       <c r="FP9" t="n">
-        <v>6.445047802117188e-06</v>
+        <v>2.28774666766185e-07</v>
       </c>
       <c r="FQ9" t="n">
-        <v>3.223993871870334e-06</v>
+        <v>6.732982456014724e-07</v>
       </c>
       <c r="FR9" t="n">
-        <v>8.625747227597458e-07</v>
+        <v>1.909180440406999e-07</v>
       </c>
       <c r="FS9" t="n">
-        <v>8.40298639559478e-07</v>
+        <v>4.227507588439039e-07</v>
       </c>
       <c r="FT9" t="n">
-        <v>4.495139819482574e-06</v>
+        <v>5.345978593140899e-07</v>
       </c>
       <c r="FU9" t="n">
-        <v>2.224639047199162e-06</v>
+        <v>2.604858018173672e-08</v>
       </c>
       <c r="FV9" t="n">
-        <v>7.276216820173431e-06</v>
+        <v>1.962163764801517e-10</v>
       </c>
       <c r="FW9" t="n">
-        <v>6.532861334562767e-06</v>
+        <v>2.025131209393294e-07</v>
       </c>
       <c r="FX9" t="n">
-        <v>1.759675797075033e-06</v>
+        <v>3.205629468538973e-07</v>
       </c>
       <c r="FY9" t="n">
-        <v>6.394831871148199e-06</v>
+        <v>3.342845289466823e-08</v>
       </c>
       <c r="FZ9" t="n">
-        <v>1.852887976383499e-06</v>
+        <v>1.9646944338092e-07</v>
       </c>
       <c r="GA9" t="n">
-        <v>4.975053343514446e-06</v>
+        <v>9.389481192556559e-09</v>
       </c>
       <c r="GB9" t="n">
-        <v>2.382676711931708e-06</v>
+        <v>2.986947720273747e-07</v>
       </c>
       <c r="GC9" t="n">
-        <v>4.085713499080157e-06</v>
+        <v>4.666411825837713e-07</v>
       </c>
       <c r="GD9" t="n">
-        <v>2.504048097762279e-06</v>
+        <v>1.716836948162381e-07</v>
       </c>
       <c r="GE9" t="n">
-        <v>4.920233550365083e-06</v>
+        <v>4.652289931073028e-07</v>
       </c>
       <c r="GF9" t="n">
-        <v>4.813950454263249e-06</v>
+        <v>4.382869889241192e-08</v>
       </c>
       <c r="GG9" t="n">
-        <v>5.339000381354708e-06</v>
+        <v>1.859618805610808e-07</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0002599146973807365</v>
+        <v>1.232347415225377e-07</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0008242044132202864</v>
+        <v>4.734517062843224e-07</v>
       </c>
       <c r="C10" t="n">
-        <v>1.213458472193452e-05</v>
+        <v>2.580597708856658e-07</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0005212094401940703</v>
+        <v>1.072721374839603e-06</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001337003079243004</v>
+        <v>7.118850362530793e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0003899869625456631</v>
+        <v>1.398247491124494e-07</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0002788218553178012</v>
+        <v>9.323957783635706e-08</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001323973760008812</v>
+        <v>3.55475606284017e-07</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0002115378447342664</v>
+        <v>1.74418460119341e-07</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0004025087109766901</v>
+        <v>1.577777055672414e-07</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0005992384976707399</v>
+        <v>2.477481189089303e-07</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0001255188399227336</v>
+        <v>4.621184643838205e-07</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0002851375902537256</v>
+        <v>1.947797727552825e-06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0009455231484025717</v>
+        <v>1.226508743457089e-06</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0005874073831364512</v>
+        <v>1.189547944591141e-07</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0005620726733468473</v>
+        <v>1.148791852756403e-07</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0006967756780795753</v>
+        <v>6.262308147597651e-07</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001552500907564536</v>
+        <v>7.999010875892054e-08</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0001243180595338345</v>
+        <v>2.633020415032661e-07</v>
       </c>
       <c r="T10" t="n">
-        <v>9.627874533180147e-06</v>
+        <v>2.083327785840083e-07</v>
       </c>
       <c r="U10" t="n">
-        <v>0.000251847697654739</v>
+        <v>1.002143292794244e-07</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0003748171438928694</v>
+        <v>6.285134759309585e-07</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001004655961878598</v>
+        <v>1.104409534491424e-06</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0002168864739360288</v>
+        <v>3.325860120639845e-07</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0002307065005879849</v>
+        <v>2.217333445742042e-07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0004007784882560372</v>
+        <v>7.165368742789724e-07</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0002347230183659121</v>
+        <v>5.432581815512094e-07</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0004025475645903498</v>
+        <v>1.444370809622342e-07</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.0001331492385361344</v>
+        <v>2.97918745673087e-07</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.124912523664534e-05</v>
+        <v>7.25610149743261e-08</v>
       </c>
       <c r="AE10" t="n">
-        <v>4.768486542161554e-05</v>
+        <v>4.130339448238374e-07</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0002721432829275727</v>
+        <v>1.37846910774897e-07</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0005420828820206225</v>
+        <v>1.302524026414176e-07</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0004836602893192321</v>
+        <v>6.633638349740067e-08</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0003189383423887193</v>
+        <v>5.987894837744534e-07</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0002930330811068416</v>
+        <v>3.739169187610969e-07</v>
       </c>
       <c r="AK10" t="n">
-        <v>6.504019256681204e-05</v>
+        <v>4.89619083055004e-08</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.00027215521549806</v>
+        <v>3.691164920383017e-07</v>
       </c>
       <c r="AM10" t="n">
-        <v>4.92143735755235e-05</v>
+        <v>1.857565052887367e-07</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.0001997849758481607</v>
+        <v>3.824370651273057e-07</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.0004928166745230556</v>
+        <v>3.063807128000917e-07</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.0003768598253373057</v>
+        <v>3.66110469940395e-07</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0001915887405630201</v>
+        <v>1.856097640029475e-07</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0003705019480548799</v>
+        <v>3.84510514095382e-07</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.0001100744193536229</v>
+        <v>3.33262903495779e-07</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.872737240977585e-05</v>
+        <v>8.614689761543559e-08</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.63801552541554e-06</v>
+        <v>6.791040050302399e-07</v>
       </c>
       <c r="AV10" t="n">
-        <v>7.004552753642201e-05</v>
+        <v>3.121363079117145e-07</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.162001667078584e-05</v>
+        <v>2.450524334562942e-07</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.001073095249012113</v>
+        <v>1.60640820467961e-06</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.001097427564673126</v>
+        <v>3.401745516384835e-07</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0001520261721452698</v>
+        <v>2.68020500016064e-07</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0004113097966182977</v>
+        <v>1.101768020816962e-06</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.0004265780444256961</v>
+        <v>3.16864969818198e-08</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.0004693077062256634</v>
+        <v>4.651159457580434e-08</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0001291389926336706</v>
+        <v>5.336304553793525e-08</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.0001898967748275027</v>
+        <v>1.484182945432622e-07</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.0004593402263708413</v>
+        <v>2.087871564526722e-08</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.0003919420996680856</v>
+        <v>3.119934319784079e-07</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.0001335136184934527</v>
+        <v>2.936908458650578e-07</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.000132999790366739</v>
+        <v>4.45971295448544e-08</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.0004012571007478982</v>
+        <v>4.279799554751662e-07</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.0001989564188988879</v>
+        <v>3.628626927820733e-07</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.0004361738101579249</v>
+        <v>4.769593431319663e-08</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.0004093773022759706</v>
+        <v>3.206425276403024e-07</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.0002728332474362105</v>
+        <v>2.215746235378901e-07</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0002645365311764181</v>
+        <v>4.31920113896922e-07</v>
       </c>
       <c r="BP10" t="n">
-        <v>1.466443427489139e-05</v>
+        <v>3.147922598145669e-07</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.000111517365439795</v>
+        <v>3.074535754876706e-07</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0002201530442107469</v>
+        <v>2.648856778364461e-08</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.0001509134890511632</v>
+        <v>6.46088381017762e-07</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.0005435991915874183</v>
+        <v>8.504985515855878e-08</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.946401168126613e-05</v>
+        <v>1.935823661369795e-07</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.0002802524832077324</v>
+        <v>1.424667885885356e-07</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.246829485055059e-05</v>
+        <v>3.357792763836187e-07</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0004195471701677889</v>
+        <v>9.471729640608828e-07</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.001217225799337029</v>
+        <v>1.2028594937874e-06</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.0001222503487952054</v>
+        <v>6.19312459093635e-07</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0001897585607366636</v>
+        <v>8.826288677710181e-08</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.0004174132482148707</v>
+        <v>6.479999115072133e-07</v>
       </c>
       <c r="CC10" t="n">
-        <v>6.605614180443808e-05</v>
+        <v>3.490200413125422e-07</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0001964703551493585</v>
+        <v>1.110883829369413e-07</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.0001581578690093011</v>
+        <v>1.63907543537789e-07</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.0001253632945008576</v>
+        <v>1.518357919394475e-07</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.0001093600585591048</v>
+        <v>2.853053615581302e-07</v>
       </c>
       <c r="CH10" t="n">
-        <v>9.096513531403616e-05</v>
+        <v>1.765312305224143e-07</v>
       </c>
       <c r="CI10" t="n">
-        <v>9.982446499634534e-05</v>
+        <v>1.058775964679626e-07</v>
       </c>
       <c r="CJ10" t="n">
-        <v>3.982515045208856e-05</v>
+        <v>8.322969335949892e-08</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.0001152673357864842</v>
+        <v>1.872601274044428e-08</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0001649372716201469</v>
+        <v>1.386628554200797e-07</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.0001859800540842116</v>
+        <v>5.295915883607449e-08</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.000574829347897321</v>
+        <v>2.628729021125764e-07</v>
       </c>
       <c r="CO10" t="n">
-        <v>7.806283247191459e-05</v>
+        <v>3.183654371241573e-07</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.0004696878022514284</v>
+        <v>8.013892056624172e-07</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.0001488896377850324</v>
+        <v>7.512508091167547e-07</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.0005947623285464942</v>
+        <v>3.331458628963446e-07</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.000219912632019259</v>
+        <v>2.036662039017756e-07</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.0003079796442762017</v>
+        <v>1.11226768240158e-07</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.000729988852981478</v>
+        <v>9.375216336593439e-08</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0001602649572305381</v>
+        <v>1.207793474122809e-07</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.0002007198054343462</v>
+        <v>1.009734376111737e-07</v>
       </c>
       <c r="CX10" t="n">
-        <v>7.485144305974245e-05</v>
+        <v>1.49884357369956e-07</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0001555784983793274</v>
+        <v>4.58716044704488e-07</v>
       </c>
       <c r="CZ10" t="n">
-        <v>4.570191231323406e-05</v>
+        <v>2.576641122686851e-07</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.0001397355663357303</v>
+        <v>1.503774456068641e-07</v>
       </c>
       <c r="DB10" t="n">
-        <v>4.441020428203046e-05</v>
+        <v>1.022451030507909e-07</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.0001243532897206023</v>
+        <v>4.173215728542345e-08</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.0001318960858043283</v>
+        <v>2.008152506505212e-07</v>
       </c>
       <c r="DE10" t="n">
-        <v>3.381114947842434e-05</v>
+        <v>2.004723995696622e-07</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.0003753108321689069</v>
+        <v>3.823916472356359e-07</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.0005320108029991388</v>
+        <v>2.574979873770644e-07</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.0007779592415317893</v>
+        <v>1.679807724030979e-07</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.0002908005844801664</v>
+        <v>6.772506111474286e-09</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0001989520387724042</v>
+        <v>2.974004473799141e-07</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.0004804414638783783</v>
+        <v>6.293465162343637e-07</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.0001276471593882889</v>
+        <v>8.877287882569362e-07</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.0003367335011716932</v>
+        <v>6.384597099895473e-07</v>
       </c>
       <c r="DN10" t="n">
-        <v>7.963469397509471e-05</v>
+        <v>1.406735208320242e-07</v>
       </c>
       <c r="DO10" t="n">
-        <v>7.29703315300867e-05</v>
+        <v>1.00395531887898e-08</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.000345822365488857</v>
+        <v>9.792810828912479e-08</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.0001313661050517112</v>
+        <v>2.621843577799154e-07</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.0005007671425119042</v>
+        <v>3.558750165666424e-07</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.0007046172395348549</v>
+        <v>2.815485231622006e-07</v>
       </c>
       <c r="DT10" t="n">
-        <v>5.244071508059278e-05</v>
+        <v>7.562335646582596e-09</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.0003602582146413624</v>
+        <v>5.451580022963753e-07</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.000242445821641013</v>
+        <v>2.283998838947809e-07</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.0004633936914615333</v>
+        <v>5.889336662789901e-08</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.000521682552061975</v>
+        <v>2.799828848765173e-07</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.0001617141824681312</v>
+        <v>1.916160528026012e-07</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.0005848329165019095</v>
+        <v>2.645298309289501e-07</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.0007970592705532908</v>
+        <v>5.838807055624784e-07</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.0003506799694150686</v>
+        <v>2.496019533282379e-07</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.0001981749373953789</v>
+        <v>6.311973379524716e-07</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.0003278928634244949</v>
+        <v>1.081006416825403e-06</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.0001056198161677457</v>
+        <v>4.7289546500906e-08</v>
       </c>
       <c r="EF10" t="n">
-        <v>6.288503936957568e-05</v>
+        <v>2.995001295857946e-07</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.0003064347547478974</v>
+        <v>3.645680379804617e-08</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.0002215479034930468</v>
+        <v>3.108418411557068e-08</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.000108836917206645</v>
+        <v>2.869372224267863e-07</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.0001097250205930322</v>
+        <v>2.325225665344988e-07</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.0002182099706260487</v>
+        <v>1.796383060082007e-07</v>
       </c>
       <c r="EL10" t="n">
-        <v>7.457626634277403e-05</v>
+        <v>1.222991841132171e-08</v>
       </c>
       <c r="EM10" t="n">
-        <v>5.268082168186083e-05</v>
+        <v>6.511927352903513e-08</v>
       </c>
       <c r="EN10" t="n">
-        <v>4.333075048634782e-05</v>
+        <v>2.991750989167485e-07</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0002022084372583777</v>
+        <v>5.724603369117176e-08</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.0003730103489942849</v>
+        <v>1.374169311674223e-08</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.0003255119081586599</v>
+        <v>1.881069806586311e-07</v>
       </c>
       <c r="ER10" t="n">
-        <v>5.785614484921098e-05</v>
+        <v>4.03463076281696e-07</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.0001287769700866193</v>
+        <v>4.406492450925725e-07</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.0007154829800128937</v>
+        <v>1.075797939620315e-07</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.000314833625452593</v>
+        <v>4.220686378175742e-07</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.0001520310470368713</v>
+        <v>7.230313059380933e-08</v>
       </c>
       <c r="EW10" t="n">
-        <v>7.135987107176334e-05</v>
+        <v>2.175458746478398e-07</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0002098630357068032</v>
+        <v>1.114978189775684e-07</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.0001788393856259063</v>
+        <v>1.969314809002753e-07</v>
       </c>
       <c r="EZ10" t="n">
-        <v>9.820189006859437e-06</v>
+        <v>1.291142979198412e-07</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.0002155967522412539</v>
+        <v>4.119143852676643e-07</v>
       </c>
       <c r="FB10" t="n">
-        <v>7.77640743763186e-05</v>
+        <v>1.945510490486413e-07</v>
       </c>
       <c r="FC10" t="n">
-        <v>9.561909246258438e-05</v>
+        <v>1.176908313027525e-07</v>
       </c>
       <c r="FD10" t="n">
-        <v>1.25327587738866e-05</v>
+        <v>6.281179310008156e-08</v>
       </c>
       <c r="FE10" t="n">
-        <v>3.531301263137721e-05</v>
+        <v>6.777771943689004e-08</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.0002530439232941717</v>
+        <v>1.566519927109766e-07</v>
       </c>
       <c r="FG10" t="n">
-        <v>8.380684448638931e-05</v>
+        <v>2.093878634923385e-07</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.0003858683921862394</v>
+        <v>3.986095720165395e-08</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.0001406713563483208</v>
+        <v>1.072805630997209e-07</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.0001577286748215556</v>
+        <v>8.078556135160397e-08</v>
       </c>
       <c r="FK10" t="n">
-        <v>8.711268310435116e-05</v>
+        <v>2.268266641181071e-08</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.000148538063513115</v>
+        <v>5.29564090356871e-07</v>
       </c>
       <c r="FM10" t="n">
-        <v>6.606952229049057e-05</v>
+        <v>1.289310347374339e-07</v>
       </c>
       <c r="FN10" t="n">
-        <v>4.296409315429628e-05</v>
+        <v>5.284262556415342e-07</v>
       </c>
       <c r="FO10" t="n">
-        <v>8.735543815419078e-06</v>
+        <v>5.317073714650178e-08</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.0006362062995322049</v>
+        <v>1.025073146365685e-07</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0002879212843254209</v>
+        <v>5.82952225158806e-07</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.0002474947250448167</v>
+        <v>2.863642123429599e-07</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.0001343583135167137</v>
+        <v>2.397409559762309e-07</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.0003216005570720881</v>
+        <v>9.576552173484743e-08</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.0002636366116348654</v>
+        <v>4.248578875376552e-07</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.001194508629851043</v>
+        <v>1.080801155239897e-07</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.0008093391661532223</v>
+        <v>2.256188196270159e-07</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.0003076365683227777</v>
+        <v>1.012541360978503e-06</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.0007265650201588869</v>
+        <v>1.272586871436943e-07</v>
       </c>
       <c r="FZ10" t="n">
-        <v>1.758785947458819e-05</v>
+        <v>7.492650411222712e-08</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.0006880169385112822</v>
+        <v>4.002962441518321e-07</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.0002205306227551773</v>
+        <v>1.46802904055221e-07</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.0005116782849654555</v>
+        <v>4.609693462498399e-07</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.0001032314685289748</v>
+        <v>2.680154409517854e-07</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.0001068728961399756</v>
+        <v>8.47993362640409e-07</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.0004086504632141441</v>
+        <v>1.730451231196639e-07</v>
       </c>
       <c r="GG10" t="n">
-        <v>9.811597556108609e-05</v>
+        <v>8.215421303248149e-07</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4.727294799522497e-05</v>
+        <v>4.907992479274981e-05</v>
       </c>
       <c r="B11" t="n">
-        <v>1.152231288870098e-05</v>
+        <v>4.763191100209951e-05</v>
       </c>
       <c r="C11" t="n">
-        <v>3.476815982139669e-05</v>
+        <v>7.797149010002613e-06</v>
       </c>
       <c r="D11" t="n">
-        <v>1.479217644373421e-05</v>
+        <v>4.713101225206628e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000126077386084944</v>
+        <v>2.360051439609379e-06</v>
       </c>
       <c r="F11" t="n">
-        <v>4.799993621418253e-05</v>
+        <v>0.0001014467561617494</v>
       </c>
       <c r="G11" t="n">
-        <v>2.981656507472508e-05</v>
+        <v>3.619619747041725e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>3.935390850529075e-05</v>
+        <v>5.232528928900138e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>5.867159779882059e-05</v>
+        <v>1.640740083530545e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>1.606324622116517e-05</v>
+        <v>3.312323678983375e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>5.632570901070721e-05</v>
+        <v>5.585080725722946e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>7.362658652709797e-05</v>
+        <v>2.350020986341406e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>1.576205977471545e-05</v>
+        <v>1.312171480094548e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>9.278587822336704e-05</v>
+        <v>3.490226663416252e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>5.557696113100974e-06</v>
+        <v>0.0001125610069721006</v>
       </c>
       <c r="P11" t="n">
-        <v>5.3601004765369e-05</v>
+        <v>2.444812162138987e-05</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.746875492855906e-05</v>
+        <v>4.56779744126834e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>3.137086605420336e-05</v>
+        <v>3.233700408600271e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>2.366308399359696e-05</v>
+        <v>3.06929687212687e-05</v>
       </c>
       <c r="T11" t="n">
-        <v>2.602610220492352e-05</v>
+        <v>1.610035542398691e-05</v>
       </c>
       <c r="U11" t="n">
-        <v>5.716015039070044e-07</v>
+        <v>2.179825423809234e-05</v>
       </c>
       <c r="V11" t="n">
-        <v>1.949710713233799e-05</v>
+        <v>1.094899744202849e-05</v>
       </c>
       <c r="W11" t="n">
-        <v>9.144689829554409e-05</v>
+        <v>8.175235052476637e-06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.844864709710237e-05</v>
+        <v>2.407547981420066e-05</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.08681285585044e-05</v>
+        <v>1.296362552238861e-05</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.746908962260932e-05</v>
+        <v>1.907561272673775e-05</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.566819966887124e-05</v>
+        <v>7.638180250069126e-06</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.75744753505569e-05</v>
+        <v>2.724065780057572e-06</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.246170647093095e-05</v>
+        <v>1.114823317038827e-05</v>
       </c>
       <c r="AD11" t="n">
-        <v>5.625789344776422e-05</v>
+        <v>8.610882105131168e-06</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.678217086009681e-05</v>
+        <v>2.361783117521554e-06</v>
       </c>
       <c r="AF11" t="n">
-        <v>7.676683162571862e-05</v>
+        <v>1.389416320307646e-05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.741767391649773e-06</v>
+        <v>5.514174699783325e-05</v>
       </c>
       <c r="AH11" t="n">
-        <v>8.493373752571642e-05</v>
+        <v>2.452099761285353e-05</v>
       </c>
       <c r="AI11" t="n">
-        <v>6.419182318495587e-05</v>
+        <v>6.211498111952096e-05</v>
       </c>
       <c r="AJ11" t="n">
-        <v>9.078004222828895e-05</v>
+        <v>1.210406935570063e-05</v>
       </c>
       <c r="AK11" t="n">
-        <v>7.663793439860456e-06</v>
+        <v>2.643996049300767e-05</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.46044689649716e-05</v>
+        <v>1.668504046392627e-05</v>
       </c>
       <c r="AM11" t="n">
-        <v>3.041147920157528e-06</v>
+        <v>5.504282853507902e-06</v>
       </c>
       <c r="AN11" t="n">
-        <v>5.613354733213782e-05</v>
+        <v>5.464864443638362e-06</v>
       </c>
       <c r="AO11" t="n">
-        <v>6.664312968496233e-05</v>
+        <v>2.418087933619972e-05</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.527708991488907e-05</v>
+        <v>1.233026341651566e-05</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.746049358393066e-05</v>
+        <v>1.922667797771282e-05</v>
       </c>
       <c r="AR11" t="n">
-        <v>3.481979729258455e-05</v>
+        <v>1.880082709249109e-05</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.847475666902028e-06</v>
+        <v>1.163205425314118e-07</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.263306280132383e-05</v>
+        <v>8.961582352640107e-06</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.288278200372588e-06</v>
+        <v>4.763372271554545e-05</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.4497561500757e-06</v>
+        <v>2.974372910102829e-05</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.783197750337422e-05</v>
+        <v>1.88935810001567e-05</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.0001409634423907846</v>
+        <v>3.973790444433689e-05</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.035057256463915e-05</v>
+        <v>9.71069312072359e-05</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.0001131620083469898</v>
+        <v>2.129925996996462e-05</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.0001268840132979676</v>
+        <v>1.767131652741227e-05</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.967606840480585e-05</v>
+        <v>9.944480552803725e-06</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.281026147305965e-05</v>
+        <v>3.296375507488847e-05</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.161710497399326e-05</v>
+        <v>1.41762793646194e-05</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.443469904595986e-05</v>
+        <v>5.448657248052768e-06</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.976434941752814e-05</v>
+        <v>3.28388596244622e-05</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.20032733422704e-06</v>
+        <v>1.938903915288392e-05</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.08077251247596e-05</v>
+        <v>1.391112436976982e-05</v>
       </c>
       <c r="BI11" t="n">
-        <v>8.838380745146424e-05</v>
+        <v>4.115147748962045e-05</v>
       </c>
       <c r="BJ11" t="n">
-        <v>2.69497813860653e-05</v>
+        <v>7.019672193564475e-05</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.909441198222339e-05</v>
+        <v>1.600455289008096e-05</v>
       </c>
       <c r="BL11" t="n">
-        <v>8.327911928063259e-06</v>
+        <v>1.031945612339769e-05</v>
       </c>
       <c r="BM11" t="n">
-        <v>4.131677997065708e-05</v>
+        <v>1.242388771061087e-05</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.231739538023248e-05</v>
+        <v>6.799957645853283e-07</v>
       </c>
       <c r="BO11" t="n">
-        <v>8.531500498065725e-05</v>
+        <v>2.030572068179026e-05</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.463844768702984e-05</v>
+        <v>2.981299985549413e-06</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.894585435977206e-05</v>
+        <v>4.045906098326668e-05</v>
       </c>
       <c r="BR11" t="n">
-        <v>7.13362533133477e-06</v>
+        <v>1.538324431749061e-05</v>
       </c>
       <c r="BS11" t="n">
-        <v>4.283081216271967e-05</v>
+        <v>9.48330489336513e-06</v>
       </c>
       <c r="BT11" t="n">
-        <v>7.107818964868784e-05</v>
+        <v>3.101987022091635e-05</v>
       </c>
       <c r="BU11" t="n">
-        <v>2.71713452093536e-05</v>
+        <v>2.564571695984341e-05</v>
       </c>
       <c r="BV11" t="n">
-        <v>7.343734523601597e-06</v>
+        <v>3.200118953827769e-05</v>
       </c>
       <c r="BW11" t="n">
-        <v>3.840410136035644e-05</v>
+        <v>3.025890691787936e-06</v>
       </c>
       <c r="BX11" t="n">
-        <v>2.112225411110558e-05</v>
+        <v>4.213718057144433e-05</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.808901576325297e-05</v>
+        <v>5.361034709494561e-06</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.43614413193427e-05</v>
+        <v>3.306967482785694e-05</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.183351484243758e-05</v>
+        <v>1.398858239554102e-05</v>
       </c>
       <c r="CB11" t="n">
-        <v>5.917892121942714e-05</v>
+        <v>5.38178483111551e-07</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.321488086134195e-05</v>
+        <v>7.327365437959088e-06</v>
       </c>
       <c r="CD11" t="n">
-        <v>8.71662086865399e-06</v>
+        <v>5.58327701583039e-06</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.614201210031752e-05</v>
+        <v>1.963509566849098e-05</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.303232233520248e-06</v>
+        <v>5.49089781998191e-06</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.059110531467013e-05</v>
+        <v>1.173679265775718e-05</v>
       </c>
       <c r="CH11" t="n">
-        <v>2.459939423715696e-05</v>
+        <v>1.788352165021934e-06</v>
       </c>
       <c r="CI11" t="n">
-        <v>6.454488811868941e-06</v>
+        <v>2.162363671232015e-05</v>
       </c>
       <c r="CJ11" t="n">
-        <v>4.892583092441782e-06</v>
+        <v>6.350140893118805e-07</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.481783692725003e-05</v>
+        <v>3.127026729998761e-06</v>
       </c>
       <c r="CL11" t="n">
-        <v>5.983961273159366e-07</v>
+        <v>3.901896434399532e-06</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.616091685718857e-05</v>
+        <v>9.030414730659686e-06</v>
       </c>
       <c r="CN11" t="n">
-        <v>3.896683847415261e-05</v>
+        <v>2.024021523538977e-05</v>
       </c>
       <c r="CO11" t="n">
-        <v>5.460226930154022e-06</v>
+        <v>1.48026902024867e-05</v>
       </c>
       <c r="CP11" t="n">
-        <v>6.882190064061433e-06</v>
+        <v>2.188090365962125e-05</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.666551517904736e-05</v>
+        <v>2.370425590925151e-06</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.922324190672953e-05</v>
+        <v>1.068840174411889e-05</v>
       </c>
       <c r="CS11" t="n">
-        <v>1.768311449268367e-05</v>
+        <v>2.310514537384734e-05</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.225408752565272e-05</v>
+        <v>1.936821172421332e-05</v>
       </c>
       <c r="CU11" t="n">
-        <v>8.806820551399142e-05</v>
+        <v>2.196012019339832e-06</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.0036906132882e-05</v>
+        <v>4.775806701218244e-06</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.886124846350867e-05</v>
+        <v>1.15207321869093e-05</v>
       </c>
       <c r="CX11" t="n">
-        <v>6.285502877290128e-06</v>
+        <v>1.302405507885851e-06</v>
       </c>
       <c r="CY11" t="n">
-        <v>3.058222864638083e-05</v>
+        <v>7.965407348820008e-06</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.56127007358009e-05</v>
+        <v>5.028885425417684e-06</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.806333966669627e-05</v>
+        <v>2.46487143158447e-05</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.536700438009575e-05</v>
+        <v>4.861760316998698e-06</v>
       </c>
       <c r="DC11" t="n">
-        <v>3.00376223094645e-06</v>
+        <v>3.165994939990924e-06</v>
       </c>
       <c r="DD11" t="n">
-        <v>7.417454980895855e-06</v>
+        <v>6.594953447347507e-06</v>
       </c>
       <c r="DE11" t="n">
-        <v>7.93178187450394e-05</v>
+        <v>1.315623740083538e-05</v>
       </c>
       <c r="DF11" t="n">
-        <v>8.243042248068377e-05</v>
+        <v>1.165230605693068e-05</v>
       </c>
       <c r="DG11" t="n">
-        <v>5.843390681548044e-06</v>
+        <v>9.802382919588126e-06</v>
       </c>
       <c r="DH11" t="n">
-        <v>9.581977792549878e-06</v>
+        <v>1.049296770361252e-06</v>
       </c>
       <c r="DI11" t="n">
-        <v>3.305134669062681e-06</v>
+        <v>5.231122486293316e-07</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.0001331696548731998</v>
+        <v>5.465142021421343e-05</v>
       </c>
       <c r="DK11" t="n">
-        <v>1.60455092554912e-05</v>
+        <v>7.964637916302308e-06</v>
       </c>
       <c r="DL11" t="n">
-        <v>6.117184966569766e-06</v>
+        <v>4.784384873346426e-05</v>
       </c>
       <c r="DM11" t="n">
-        <v>7.665276643820107e-05</v>
+        <v>2.938409670605324e-05</v>
       </c>
       <c r="DN11" t="n">
-        <v>8.193146641133353e-07</v>
+        <v>7.848376299079973e-06</v>
       </c>
       <c r="DO11" t="n">
-        <v>3.156830644002184e-05</v>
+        <v>1.888692167995032e-06</v>
       </c>
       <c r="DP11" t="n">
-        <v>2.82357977994252e-05</v>
+        <v>1.467868241888937e-05</v>
       </c>
       <c r="DQ11" t="n">
-        <v>4.536203778116032e-05</v>
+        <v>1.925756077980623e-05</v>
       </c>
       <c r="DR11" t="n">
-        <v>5.337415132089518e-05</v>
+        <v>2.649846101121511e-05</v>
       </c>
       <c r="DS11" t="n">
-        <v>8.090055416687392e-06</v>
+        <v>2.826931222443818e-06</v>
       </c>
       <c r="DT11" t="n">
-        <v>4.179647658020258e-05</v>
+        <v>1.618421720195329e-06</v>
       </c>
       <c r="DU11" t="n">
-        <v>1.539338882139418e-05</v>
+        <v>3.894773726642597e-06</v>
       </c>
       <c r="DV11" t="n">
-        <v>7.49640166759491e-05</v>
+        <v>2.689879693207331e-06</v>
       </c>
       <c r="DW11" t="n">
-        <v>2.37071726587601e-05</v>
+        <v>1.521356625744374e-05</v>
       </c>
       <c r="DX11" t="n">
-        <v>1.647485260036774e-05</v>
+        <v>7.172194727900205e-06</v>
       </c>
       <c r="DY11" t="n">
-        <v>2.243140625068918e-05</v>
+        <v>3.170724448864348e-05</v>
       </c>
       <c r="DZ11" t="n">
-        <v>6.778533133910969e-05</v>
+        <v>2.045581823040266e-05</v>
       </c>
       <c r="EA11" t="n">
-        <v>5.222741310717538e-05</v>
+        <v>3.524005660437979e-05</v>
       </c>
       <c r="EB11" t="n">
-        <v>3.46701308444608e-05</v>
+        <v>1.799079473130405e-05</v>
       </c>
       <c r="EC11" t="n">
-        <v>4.067287591169588e-07</v>
+        <v>1.003540546662407e-05</v>
       </c>
       <c r="ED11" t="n">
-        <v>2.894667159125675e-05</v>
+        <v>3.826466490863822e-05</v>
       </c>
       <c r="EE11" t="n">
-        <v>1.542278187116608e-05</v>
+        <v>4.456246097106487e-05</v>
       </c>
       <c r="EF11" t="n">
-        <v>1.798007906472776e-05</v>
+        <v>2.496821707609342e-06</v>
       </c>
       <c r="EG11" t="n">
-        <v>3.931940227630548e-06</v>
+        <v>5.593073183263186e-06</v>
       </c>
       <c r="EH11" t="n">
-        <v>7.319160886254394e-07</v>
+        <v>2.119914097420406e-05</v>
       </c>
       <c r="EI11" t="n">
-        <v>6.706050771754235e-05</v>
+        <v>2.194801163568627e-05</v>
       </c>
       <c r="EJ11" t="n">
-        <v>3.160080450470559e-05</v>
+        <v>2.418239819235168e-05</v>
       </c>
       <c r="EK11" t="n">
-        <v>4.216342131257989e-05</v>
+        <v>6.052224307495635e-06</v>
       </c>
       <c r="EL11" t="n">
-        <v>1.699209315120243e-05</v>
+        <v>2.791932729451219e-07</v>
       </c>
       <c r="EM11" t="n">
-        <v>3.127621312160045e-05</v>
+        <v>1.032850650517503e-05</v>
       </c>
       <c r="EN11" t="n">
-        <v>3.868148269248195e-06</v>
+        <v>5.931870418862673e-06</v>
       </c>
       <c r="EO11" t="n">
-        <v>1.261100078409072e-05</v>
+        <v>5.38700669494574e-06</v>
       </c>
       <c r="EP11" t="n">
-        <v>7.627731065440457e-06</v>
+        <v>2.385560765105765e-05</v>
       </c>
       <c r="EQ11" t="n">
-        <v>5.881410288566258e-06</v>
+        <v>4.391527909319848e-06</v>
       </c>
       <c r="ER11" t="n">
-        <v>4.433088179212064e-06</v>
+        <v>1.13598089228617e-05</v>
       </c>
       <c r="ES11" t="n">
-        <v>1.763682848832104e-05</v>
+        <v>2.220874739577994e-05</v>
       </c>
       <c r="ET11" t="n">
-        <v>1.31638407765422e-05</v>
+        <v>2.786873119475786e-05</v>
       </c>
       <c r="EU11" t="n">
-        <v>2.7181191398995e-05</v>
+        <v>8.016566425794736e-06</v>
       </c>
       <c r="EV11" t="n">
-        <v>3.204071617801674e-05</v>
+        <v>2.710527951421682e-05</v>
       </c>
       <c r="EW11" t="n">
-        <v>5.188988143345341e-05</v>
+        <v>1.484059066569898e-05</v>
       </c>
       <c r="EX11" t="n">
-        <v>1.461169813410379e-05</v>
+        <v>4.900831754639512e-06</v>
       </c>
       <c r="EY11" t="n">
-        <v>1.278914623981109e-05</v>
+        <v>1.536483250674792e-05</v>
       </c>
       <c r="EZ11" t="n">
-        <v>1.427216034244339e-06</v>
+        <v>2.32472257266636e-06</v>
       </c>
       <c r="FA11" t="n">
-        <v>3.133345308015123e-05</v>
+        <v>9.154484359896742e-06</v>
       </c>
       <c r="FB11" t="n">
-        <v>2.104667146340944e-05</v>
+        <v>3.519506208249368e-06</v>
       </c>
       <c r="FC11" t="n">
-        <v>1.217110821016831e-06</v>
+        <v>1.834637987485621e-05</v>
       </c>
       <c r="FD11" t="n">
-        <v>6.194877641974017e-07</v>
+        <v>1.153052153313183e-06</v>
       </c>
       <c r="FE11" t="n">
-        <v>2.183113974751905e-05</v>
+        <v>6.852861588413361e-06</v>
       </c>
       <c r="FF11" t="n">
-        <v>1.637653622310609e-05</v>
+        <v>1.634029786146129e-06</v>
       </c>
       <c r="FG11" t="n">
-        <v>4.368550798972137e-05</v>
+        <v>3.549489065335365e-06</v>
       </c>
       <c r="FH11" t="n">
-        <v>3.268253203714266e-05</v>
+        <v>3.13103510052315e-06</v>
       </c>
       <c r="FI11" t="n">
-        <v>1.974583756236825e-05</v>
+        <v>5.458346095110755e-06</v>
       </c>
       <c r="FJ11" t="n">
-        <v>7.335863483604044e-05</v>
+        <v>1.587658698554151e-05</v>
       </c>
       <c r="FK11" t="n">
-        <v>2.142395169357769e-05</v>
+        <v>2.466944715706632e-05</v>
       </c>
       <c r="FL11" t="n">
-        <v>1.337116009381134e-05</v>
+        <v>2.869794479920529e-05</v>
       </c>
       <c r="FM11" t="n">
-        <v>1.752391472109593e-05</v>
+        <v>1.09632674138993e-06</v>
       </c>
       <c r="FN11" t="n">
-        <v>1.996911305468529e-05</v>
+        <v>9.272143870475702e-06</v>
       </c>
       <c r="FO11" t="n">
-        <v>3.224171814508736e-05</v>
+        <v>6.074888733564876e-05</v>
       </c>
       <c r="FP11" t="n">
-        <v>4.024476947961375e-05</v>
+        <v>1.933764178829733e-05</v>
       </c>
       <c r="FQ11" t="n">
-        <v>9.729303201311268e-06</v>
+        <v>2.961400241474621e-05</v>
       </c>
       <c r="FR11" t="n">
-        <v>1.113400003305287e-06</v>
+        <v>9.913477697409689e-06</v>
       </c>
       <c r="FS11" t="n">
-        <v>9.974011845770292e-06</v>
+        <v>2.863687041099183e-05</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.0002482719719409943</v>
+        <v>9.157106251223013e-05</v>
       </c>
       <c r="FU11" t="n">
-        <v>8.390613220399246e-05</v>
+        <v>2.325901004951447e-05</v>
       </c>
       <c r="FV11" t="n">
-        <v>2.76024602499092e-05</v>
+        <v>3.718130028573796e-05</v>
       </c>
       <c r="FW11" t="n">
-        <v>4.002643981948495e-05</v>
+        <v>0.0001132221295847557</v>
       </c>
       <c r="FX11" t="n">
-        <v>2.704158760025166e-05</v>
+        <v>8.489361789543182e-06</v>
       </c>
       <c r="FY11" t="n">
-        <v>4.544537659967318e-05</v>
+        <v>3.035864574485458e-05</v>
       </c>
       <c r="FZ11" t="n">
-        <v>6.35318292552256e-06</v>
+        <v>1.042932854034007e-05</v>
       </c>
       <c r="GA11" t="n">
-        <v>3.962527989642695e-05</v>
+        <v>3.127567833871581e-05</v>
       </c>
       <c r="GB11" t="n">
-        <v>4.835752042708918e-05</v>
+        <v>5.645154942612862e-06</v>
       </c>
       <c r="GC11" t="n">
-        <v>5.38640160812065e-05</v>
+        <v>3.354851287440397e-05</v>
       </c>
       <c r="GD11" t="n">
-        <v>2.870268690458033e-05</v>
+        <v>3.751826443476602e-05</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.0001029609265970066</v>
+        <v>1.912775042001158e-05</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.0001044816308422014</v>
+        <v>3.330379513499793e-06</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.0001172507327282801</v>
+        <v>2.292741010023747e-05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6.476431735791266e-05</v>
+        <v>0.0003938466834370047</v>
       </c>
       <c r="B12" t="n">
-        <v>0.003689462319016457</v>
+        <v>0.005301258526742458</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0001013493383652531</v>
+        <v>0.001373804523609579</v>
       </c>
       <c r="D12" t="n">
-        <v>0.003574553411453962</v>
+        <v>0.002376755932345986</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002419411204755306</v>
+        <v>0.0006465211627073586</v>
       </c>
       <c r="F12" t="n">
-        <v>0.002156298141926527</v>
+        <v>0.003310066414996982</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0008772690780460835</v>
+        <v>0.001156137208454311</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0001192630588775501</v>
+        <v>0.001436285907402635</v>
       </c>
       <c r="I12" t="n">
-        <v>0.001442212611436844</v>
+        <v>0.0005553849041461945</v>
       </c>
       <c r="J12" t="n">
-        <v>4.789241938851774e-05</v>
+        <v>0.00073531165253371</v>
       </c>
       <c r="K12" t="n">
-        <v>0.003016771981492639</v>
+        <v>0.005111346486955881</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0002382020466029644</v>
+        <v>0.00232106470502913</v>
       </c>
       <c r="M12" t="n">
-        <v>0.00295598991215229</v>
+        <v>0.003642917610704899</v>
       </c>
       <c r="N12" t="n">
-        <v>0.002135050017386675</v>
+        <v>0.000110476219560951</v>
       </c>
       <c r="O12" t="n">
-        <v>0.001595253008417785</v>
+        <v>0.003423819784075022</v>
       </c>
       <c r="P12" t="n">
-        <v>0.001082623959518969</v>
+        <v>0.00122728873975575</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.001193819683976471</v>
+        <v>0.001067631528712809</v>
       </c>
       <c r="R12" t="n">
-        <v>0.001292117754928768</v>
+        <v>0.000356190575985238</v>
       </c>
       <c r="S12" t="n">
-        <v>8.359763160115108e-05</v>
+        <v>5.442059773486108e-06</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0002842743415385485</v>
+        <v>0.0001813738927012309</v>
       </c>
       <c r="U12" t="n">
-        <v>7.484333764296025e-05</v>
+        <v>0.0002674298593774438</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0008653307450003922</v>
+        <v>0.0002280169574078172</v>
       </c>
       <c r="W12" t="n">
-        <v>0.002306736074388027</v>
+        <v>0.0006406112806871533</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0002262834750581533</v>
+        <v>0.0009439230198040605</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0007825040374882519</v>
+        <v>1.241397694684565e-05</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0001872809807537124</v>
+        <v>0.0006947253714315593</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0001343348121736199</v>
+        <v>0.0009876847034320235</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0001107764837797731</v>
+        <v>0.0003768176247831434</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.173678462393582e-06</v>
+        <v>0.0001174902135971934</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0004055494209751487</v>
+        <v>0.0008651903481222689</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.001165433088317513</v>
+        <v>0.0004861566703766584</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.001396602485328913</v>
+        <v>0.0008482611738145351</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0008575448882766068</v>
+        <v>0.001729587442241609</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.0004851625708397478</v>
+        <v>0.0001292474044021219</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.0001155560166807845</v>
+        <v>0.0007117700879462063</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.0002976259274873883</v>
+        <v>6.18457852397114e-06</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.000102670950582251</v>
+        <v>6.505883357021958e-05</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0002038843231275678</v>
+        <v>0.001325921155512333</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0001467481779400259</v>
+        <v>0.001287884311750531</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.0001877860340755433</v>
+        <v>0.001063736388459802</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0008637775899842381</v>
+        <v>0.0004609869793057442</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.0008652945980429649</v>
+        <v>0.0008360389620065689</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.0007601643446832895</v>
+        <v>0.0006381964776664972</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.0002395948249613866</v>
+        <v>0.0004238604160491377</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.0001167479931609705</v>
+        <v>0.0001805721549317241</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.388124554883689e-05</v>
+        <v>0.0001521884551038966</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.000980601878836751</v>
+        <v>0.001913928659632802</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.0006023548194207251</v>
+        <v>0.001257532509043813</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.002060260158032179</v>
+        <v>0.001419889507815242</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.002382686827331781</v>
+        <v>0.001959600718691945</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.0007882378995418549</v>
+        <v>0.002220163587480783</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.002433587098494172</v>
+        <v>0.0002577074046712369</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.002763168420642614</v>
+        <v>0.0001747916685417295</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.0001847746025305241</v>
+        <v>0.000291121075861156</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.0003588683612179011</v>
+        <v>0.0006019254215061665</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.001113133155740798</v>
+        <v>0.0007713799714110792</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.0002421821118332446</v>
+        <v>0.0006549608078785241</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.0002078428806271404</v>
+        <v>0.000667442218400538</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.315308615332469e-05</v>
+        <v>0.001037717564031482</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.0004956197226420045</v>
+        <v>0.0001068231358658522</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.001369894947856665</v>
+        <v>0.0008538212860003114</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.0005587396444752812</v>
+        <v>0.00141122646164149</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.001674797385931015</v>
+        <v>5.798559868708253e-06</v>
       </c>
       <c r="BL12" t="n">
-        <v>4.093704410479404e-05</v>
+        <v>5.745642556576058e-05</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0002686847583390772</v>
+        <v>0.0005724874790757895</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0003814712981693447</v>
+        <v>0.0001216068485518917</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.001565455691888928</v>
+        <v>0.0004532779566943645</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.0006464301841333508</v>
+        <v>7.880799239501357e-05</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0002289646945428103</v>
+        <v>0.0003514707495924085</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.000504594761878252</v>
+        <v>0.0001762203755788505</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.001200656522996724</v>
+        <v>0.0004228267061989754</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.000850049895234406</v>
+        <v>0.0006221469957381487</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.0004710675566457212</v>
+        <v>8.685571083333343e-05</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.001488002599216998</v>
+        <v>0.001635035965591669</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.543353083543479e-05</v>
+        <v>0.0008593467646278441</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.002391503658145666</v>
+        <v>0.001856299233622849</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.002232205588370562</v>
+        <v>0.0003597858594730496</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.0001589380844961852</v>
+        <v>0.001260109827853739</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.001148688490502536</v>
+        <v>9.405161836184561e-05</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.0009590049739927053</v>
+        <v>0.0002448301820550114</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.0003434720856603235</v>
+        <v>0.00050194445066154</v>
       </c>
       <c r="CD12" t="n">
-        <v>1.902611438708846e-05</v>
+        <v>0.0002274192665936425</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.0003858903946820647</v>
+        <v>0.001630033599212766</v>
       </c>
       <c r="CF12" t="n">
-        <v>6.334691715892404e-05</v>
+        <v>0.0002745748788584024</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.000504725961945951</v>
+        <v>0.0009299717494286597</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.0002882833359763026</v>
+        <v>0.0002962240832857788</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.000152933323988691</v>
+        <v>0.0005294422735460103</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.0003056626883335412</v>
+        <v>0.0001410943223163486</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.0001087410273612477</v>
+        <v>6.344191933749244e-05</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.0002597790444269776</v>
+        <v>0.0003411933139432222</v>
       </c>
       <c r="CM12" t="n">
-        <v>7.622162956977263e-05</v>
+        <v>0.0003464301116764545</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.0008763150544837117</v>
+        <v>0.0001442292705178261</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.0001329232909483835</v>
+        <v>0.00186010601464659</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.0004754085384774953</v>
+        <v>0.001873478991910815</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.0003415846731513739</v>
+        <v>0.000271886819973588</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.0009257665369659662</v>
+        <v>9.892586967907846e-05</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.0008178807329386473</v>
+        <v>1.819207682274282e-07</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.001338471658527851</v>
+        <v>0.001266805571503937</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.0001875134621514007</v>
+        <v>1.92713487194851e-05</v>
       </c>
       <c r="CV12" t="n">
-        <v>4.812631232198328e-06</v>
+        <v>0.000221598384086974</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.0005434461636468768</v>
+        <v>0.001548414118587971</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.0001148421288235113</v>
+        <v>0.0004431660054251552</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.0004572123289108276</v>
+        <v>0.000889566435944289</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.0005532422219403088</v>
+        <v>0.0001951338927028701</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.0002133629750460386</v>
+        <v>0.0006365391309373081</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.0002048357273451984</v>
+        <v>0.0001445602101739496</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.000154813242261298</v>
+        <v>0.0002415983472019434</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.0002672921109478921</v>
+        <v>0.0001622090640012175</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.0001296929258387536</v>
+        <v>0.0008340316126123071</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.001744428067468107</v>
+        <v>0.0005953856743872166</v>
       </c>
       <c r="DG12" t="n">
-        <v>5.715565930586308e-05</v>
+        <v>0.000734503788407892</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.002155802911147475</v>
+        <v>0.0008630658267065883</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.001481423154473305</v>
+        <v>0.0001938483474077657</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.0007799313170835376</v>
+        <v>0.003872042521834373</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.0008659720188006759</v>
+        <v>0.0001819943718146533</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.0004075327597092837</v>
+        <v>0.001991172786802053</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.0006993504357524216</v>
+        <v>0.00104782881680876</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.0007637236267328262</v>
+        <v>0.0003331177576910704</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.001248641288839281</v>
+        <v>0.0009753176127560437</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.0003667518321890384</v>
+        <v>0.0001996745122596622</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.001348872669041157</v>
+        <v>0.0004142674442846328</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.722947288537398e-05</v>
+        <v>0.0005084679578430951</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.0003637397312559187</v>
+        <v>0.0002202150790253654</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.0003500179445836693</v>
+        <v>0.0001553034817334265</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.0003975734289269894</v>
+        <v>0.0006843843730166554</v>
       </c>
       <c r="DV12" t="n">
-        <v>5.731577766709961e-05</v>
+        <v>0.00140591524541378</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.0003918645670637488</v>
+        <v>0.0001377095613861457</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.0001534587936475873</v>
+        <v>2.475255314493552e-05</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.0005347615806385875</v>
+        <v>0.001163887442089617</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.0007183498819358647</v>
+        <v>0.001220111269503832</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.001153181656263769</v>
+        <v>7.398318848572671e-05</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.0001131392054958269</v>
+        <v>0.001491120434366167</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.0001864559453679249</v>
+        <v>6.371052586473525e-05</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.0005112339276820421</v>
+        <v>0.001779022044502199</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.0001585400750627741</v>
+        <v>0.001994835212826729</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.0001994871709030122</v>
+        <v>0.0009406540775671601</v>
       </c>
       <c r="EG12" t="n">
-        <v>1.593484557815827e-05</v>
+        <v>0.001184555818326771</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.0003362866409588605</v>
+        <v>0.0007469286792911589</v>
       </c>
       <c r="EI12" t="n">
-        <v>5.950217018835247e-05</v>
+        <v>0.001022096956148744</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.0006673448369838297</v>
+        <v>0.0001828392851166427</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.000217535620322451</v>
+        <v>8.141218859236687e-05</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.0003391736245248467</v>
+        <v>0.0001620886177988723</v>
       </c>
       <c r="EM12" t="n">
-        <v>8.779355994192883e-05</v>
+        <v>7.54725479055196e-05</v>
       </c>
       <c r="EN12" t="n">
-        <v>3.105361975030974e-05</v>
+        <v>0.0001428701652912423</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.000287262286292389</v>
+        <v>0.0002946518361568451</v>
       </c>
       <c r="EP12" t="n">
-        <v>7.179007661761716e-05</v>
+        <v>0.001606882316991687</v>
       </c>
       <c r="EQ12" t="n">
-        <v>5.988707198412158e-05</v>
+        <v>0.0004211676423437893</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0009773252531886101</v>
+        <v>0.0001537537609692663</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.0003748291055671871</v>
+        <v>0.0001064516400219873</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.002065403154119849</v>
+        <v>0.0003571332199499011</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.001092858146876097</v>
+        <v>0.0005852284375578165</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.0003655434993561357</v>
+        <v>0.0005309389671310782</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.001341661787591875</v>
+        <v>0.001080867950804532</v>
       </c>
       <c r="EX12" t="n">
-        <v>3.282745819888078e-05</v>
+        <v>0.0001831238914746791</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.0002946004387922585</v>
+        <v>0.001565490383654833</v>
       </c>
       <c r="EZ12" t="n">
-        <v>4.526542034000158e-05</v>
+        <v>0.000382747792173177</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.0006651654257439077</v>
+        <v>0.00108336447738111</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.0002281649358337745</v>
+        <v>0.0002462248085066676</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.0002252738195238635</v>
+        <v>0.0005827965796925128</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.0005397381028160453</v>
+        <v>0.0002240222529508173</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.0002701209741644561</v>
+        <v>0.0002584187604952604</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.0003406309988349676</v>
+        <v>2.946807217085734e-05</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.0001082750095520169</v>
+        <v>0.0003749209281522781</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.0001203826832352206</v>
+        <v>0.0004325609188526869</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.0007689709309488535</v>
+        <v>7.412022387143224e-05</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.0003773757489398122</v>
+        <v>0.0001922642986755818</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.001196313765831292</v>
+        <v>0.001037585781887174</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.001109780743718147</v>
+        <v>0.0001541458477731794</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.0002471827319823205</v>
+        <v>0.0001068136189132929</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.0004131320456508547</v>
+        <v>0.0003126265364699066</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.0004968286375515163</v>
+        <v>0.001323115080595016</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.0002955674426630139</v>
+        <v>0.0007362968754023314</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.0009037049021571875</v>
+        <v>0.002335831988602877</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.0002101788122672588</v>
+        <v>0.0006798228714615107</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.001084987074136734</v>
+        <v>0.00112389971036464</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.002679796423763037</v>
+        <v>0.004323097411543131</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.001131005119532347</v>
+        <v>0.0007572126341983676</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.0008582128211855888</v>
+        <v>0.0002953739603981376</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.0007051944849081337</v>
+        <v>0.002068959875032306</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.0002932939387392253</v>
+        <v>0.001503862673416734</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.0001709775242488831</v>
+        <v>0.0005554175586439669</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.000262215849943459</v>
+        <v>6.802227289881557e-05</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.0002699347969610244</v>
+        <v>0.0008214651606976986</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.0004991810419596732</v>
+        <v>0.0009802265558391809</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.0008713961578905582</v>
+        <v>0.0001848992105806246</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.0003766109293792397</v>
+        <v>0.001125035691075027</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.0001617411617189646</v>
+        <v>0.00110574800055474</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.0007485542446374893</v>
+        <v>2.262448833789676e-05</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.0009215374593622983</v>
+        <v>0.0006676719058305025</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0003151681739836931</v>
+        <v>0.0001025500314426608</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0006266190321184695</v>
+        <v>0.0001120692249969579</v>
       </c>
       <c r="C13" t="n">
-        <v>0.000121188691991847</v>
+        <v>8.788135892245919e-05</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0002419720549369231</v>
+        <v>8.618462015874684e-05</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0001482743682572618</v>
+        <v>1.679224078543484e-05</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0006996582960709929</v>
+        <v>0.000385142513550818</v>
       </c>
       <c r="G13" t="n">
-        <v>4.29550746048335e-05</v>
+        <v>0.0001704967580735683</v>
       </c>
       <c r="H13" t="n">
-        <v>5.124978633830324e-05</v>
+        <v>0.0001550443266751245</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0006719641387462616</v>
+        <v>5.788894850411452e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>9.006045729620382e-06</v>
+        <v>9.777116065379232e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0004305895417928696</v>
+        <v>0.0001837049203459173</v>
       </c>
       <c r="L13" t="n">
-        <v>0.000154171691974625</v>
+        <v>7.538027421105653e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0002999374410137534</v>
+        <v>8.580975554650649e-05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.90588390675839e-05</v>
+        <v>3.868552448693663e-05</v>
       </c>
       <c r="O13" t="n">
-        <v>0.000250753597356379</v>
+        <v>0.0003889500221703202</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0004993141046725214</v>
+        <v>0.0002361229271627963</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0003093109407927841</v>
+        <v>0.0001604171848157421</v>
       </c>
       <c r="R13" t="n">
-        <v>0.000242721987888217</v>
+        <v>6.728843800374307e-06</v>
       </c>
       <c r="S13" t="n">
-        <v>8.883642294676974e-06</v>
+        <v>4.686524334829301e-05</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0001039918715832755</v>
+        <v>7.625786383869126e-05</v>
       </c>
       <c r="U13" t="n">
-        <v>5.581356163020246e-05</v>
+        <v>5.823560786666349e-05</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0001490057911723852</v>
+        <v>6.997639866312966e-05</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0005821306258440018</v>
+        <v>0.0001762127649271861</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0002661301114130765</v>
+        <v>0.0001142265318776481</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.0001077447959687561</v>
+        <v>2.21564041567035e-05</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0003248098655603826</v>
+        <v>3.308678060420789e-05</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0001064131865859963</v>
+        <v>9.570983820594847e-06</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.788047277135774e-05</v>
+        <v>3.349878170411102e-07</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.06009902083315e-05</v>
+        <v>7.886515959398821e-05</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0002554645470809191</v>
+        <v>8.430573507212102e-05</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0002340846403967589</v>
+        <v>7.271567301359028e-05</v>
       </c>
       <c r="AF13" t="n">
-        <v>7.371948595391586e-05</v>
+        <v>6.27756817266345e-05</v>
       </c>
       <c r="AG13" t="n">
-        <v>7.905986421974376e-06</v>
+        <v>6.905810732860118e-05</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.0002617991121951491</v>
+        <v>2.613746801216621e-05</v>
       </c>
       <c r="AI13" t="n">
-        <v>7.800583261996508e-06</v>
+        <v>0.0001118798318202607</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0004744451143778861</v>
+        <v>3.593726432882249e-05</v>
       </c>
       <c r="AK13" t="n">
-        <v>5.632135435007513e-05</v>
+        <v>4.167996667092666e-05</v>
       </c>
       <c r="AL13" t="n">
-        <v>7.361685129581019e-05</v>
+        <v>2.460404721205123e-05</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0001109121803892776</v>
+        <v>2.035827856161632e-05</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.0004217320820316672</v>
+        <v>8.573154627811164e-05</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0002422534744255245</v>
+        <v>3.103121343883686e-05</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.094315459544305e-05</v>
+        <v>9.764793503563851e-05</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.000148233724758029</v>
+        <v>5.198671715334058e-07</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.875337930978276e-06</v>
+        <v>2.891210169764236e-05</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.702867823245469e-05</v>
+        <v>7.124470721464604e-05</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.0002256617299281061</v>
+        <v>5.587517080130056e-05</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.000343170395353809</v>
+        <v>0.0002605353656690568</v>
       </c>
       <c r="AV13" t="n">
-        <v>8.516953676007688e-05</v>
+        <v>8.463983976980671e-05</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.0002597008133307099</v>
+        <v>5.392161619965918e-05</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.0005539905396290123</v>
+        <v>7.919957715785131e-05</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.000642010651063174</v>
+        <v>0.0001466168760089204</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.0006174823502078652</v>
+        <v>0.0001246420724783093</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0004954791511408985</v>
+        <v>0.0001407306990586221</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.0004447685787454247</v>
+        <v>1.997325125557836e-05</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.0003377945395186543</v>
+        <v>4.417350282892585e-05</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.623928594402969e-06</v>
+        <v>2.329777271370403e-05</v>
       </c>
       <c r="BE13" t="n">
-        <v>3.637203190010041e-05</v>
+        <v>5.257103111944161e-05</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.0005008413572795689</v>
+        <v>3.88604894396849e-05</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.589989349478856e-05</v>
+        <v>2.355574542889372e-05</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.0001173545242636465</v>
+        <v>0.0001375801221001893</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.0003998808679170907</v>
+        <v>2.574532300059218e-05</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.0002580850559752434</v>
+        <v>0.0001298433926422149</v>
       </c>
       <c r="BK13" t="n">
-        <v>9.896825213218108e-05</v>
+        <v>8.464582060696557e-05</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0001520485966466367</v>
+        <v>3.177259350195527e-05</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0001278154813917354</v>
+        <v>2.6386263925815e-05</v>
       </c>
       <c r="BN13" t="n">
-        <v>7.402936898870394e-05</v>
+        <v>1.821452133299317e-05</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.0005629956140182912</v>
+        <v>2.717371171456762e-05</v>
       </c>
       <c r="BP13" t="n">
-        <v>8.209295629058033e-06</v>
+        <v>3.399364504730329e-05</v>
       </c>
       <c r="BQ13" t="n">
-        <v>9.678406058810651e-05</v>
+        <v>8.599906141171232e-05</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.0001740985171636567</v>
+        <v>3.347013262100518e-05</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.0004478538176044822</v>
+        <v>2.354920616198797e-05</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0003047059872187674</v>
+        <v>7.609297426824924e-06</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.860819171881303e-05</v>
+        <v>2.011369360843673e-06</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.0002202602918259799</v>
+        <v>4.772866668645293e-05</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.0001336801797151566</v>
+        <v>7.562180690001696e-05</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.0001391384721500799</v>
+        <v>0.0001340571325272322</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.235738404328004e-05</v>
+        <v>0.0001377091684844345</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.0003534284478519112</v>
+        <v>0.0002386098931310698</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.0003470940864644945</v>
+        <v>4.354264456196688e-05</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0003992208803538233</v>
+        <v>8.336667815456167e-05</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.589576226659119e-05</v>
+        <v>3.186542380717583e-05</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.649880116223358e-05</v>
+        <v>3.812008071690798e-05</v>
       </c>
       <c r="CE13" t="n">
-        <v>7.856762385927141e-05</v>
+        <v>2.143627716577612e-05</v>
       </c>
       <c r="CF13" t="n">
-        <v>8.164438622770831e-05</v>
+        <v>8.857735338096973e-06</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0001394760620314628</v>
+        <v>5.302564022713341e-05</v>
       </c>
       <c r="CH13" t="n">
-        <v>4.102139791939408e-05</v>
+        <v>7.730768629699014e-06</v>
       </c>
       <c r="CI13" t="n">
-        <v>3.362181450938806e-05</v>
+        <v>0.0001006814127322286</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.293776560691185e-05</v>
+        <v>2.141834374924656e-05</v>
       </c>
       <c r="CK13" t="n">
-        <v>3.404244489502162e-05</v>
+        <v>6.619243504246697e-05</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.109687920892611e-05</v>
+        <v>7.5370562626631e-06</v>
       </c>
       <c r="CM13" t="n">
-        <v>5.150758079253137e-05</v>
+        <v>6.376503006322309e-05</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.0001396022271364927</v>
+        <v>7.686834578635171e-05</v>
       </c>
       <c r="CO13" t="n">
-        <v>4.667614120990038e-06</v>
+        <v>1.073005114449188e-05</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.0001997893996303901</v>
+        <v>2.445512654958293e-05</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.0003619250783231109</v>
+        <v>0.0001778177538653836</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0001117389474529773</v>
+        <v>0.0001442152715753764</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0003646982950158417</v>
+        <v>1.349572630715556e-05</v>
       </c>
       <c r="CT13" t="n">
-        <v>5.596910796157317e-06</v>
+        <v>3.602218203013763e-05</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.000564218033105135</v>
+        <v>5.104963929625228e-05</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.13488822535146e-05</v>
+        <v>4.923093365505338e-05</v>
       </c>
       <c r="CW13" t="n">
-        <v>8.134524978231639e-05</v>
+        <v>1.476478246331681e-05</v>
       </c>
       <c r="CX13" t="n">
-        <v>7.486390677513555e-05</v>
+        <v>1.79975395440124e-05</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0001601912954356521</v>
+        <v>5.676369983120821e-05</v>
       </c>
       <c r="CZ13" t="n">
-        <v>4.943111707689241e-05</v>
+        <v>1.32323748402996e-05</v>
       </c>
       <c r="DA13" t="n">
-        <v>4.733778769150376e-05</v>
+        <v>8.71970914886333e-05</v>
       </c>
       <c r="DB13" t="n">
-        <v>3.759940955205821e-05</v>
+        <v>2.079750629491173e-05</v>
       </c>
       <c r="DC13" t="n">
-        <v>3.664335963549092e-07</v>
+        <v>4.86566532345023e-05</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.122951991623268e-05</v>
+        <v>4.010717020719312e-07</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.0005457662045955658</v>
+        <v>5.666913784807548e-05</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.0006596943712793291</v>
+        <v>3.52122078766115e-05</v>
       </c>
       <c r="DG13" t="n">
-        <v>9.286552085541189e-06</v>
+        <v>9.532598778605461e-05</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.0004005678638350219</v>
+        <v>3.291251050541177e-05</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0003140107728540897</v>
+        <v>3.534696134011028e-06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.001160344923846424</v>
+        <v>2.808388671837747e-05</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.0003770226903725415</v>
+        <v>4.78615693282336e-05</v>
       </c>
       <c r="DL13" t="n">
-        <v>6.405575550161302e-05</v>
+        <v>4.412642010720447e-05</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.0003409453202039003</v>
+        <v>3.343846765346825e-05</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.0001806126965675503</v>
+        <v>2.10125399462413e-05</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.0004422327037900686</v>
+        <v>2.002432302106172e-05</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0003846600884571671</v>
+        <v>5.100631460663863e-05</v>
       </c>
       <c r="DQ13" t="n">
-        <v>9.718912770040333e-05</v>
+        <v>0.000148555074702017</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0003783040447160602</v>
+        <v>8.916485967347398e-05</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0001511014124844223</v>
+        <v>0.0001458510232623667</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.0003707685391418636</v>
+        <v>7.399442256428301e-05</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.0001139960368163884</v>
+        <v>0.0001501686201663688</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0003820861165877432</v>
+        <v>2.559875065344386e-05</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.0001302416494581848</v>
+        <v>5.668779340339825e-05</v>
       </c>
       <c r="DX13" t="n">
-        <v>6.146105442894623e-05</v>
+        <v>1.484904805693077e-05</v>
       </c>
       <c r="DY13" t="n">
-        <v>3.911337989848107e-05</v>
+        <v>0.0001396188599755988</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.0002534022787585855</v>
+        <v>2.497519017197192e-05</v>
       </c>
       <c r="EA13" t="n">
-        <v>4.457142495084554e-05</v>
+        <v>1.1952462955378e-05</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0007547535351477563</v>
+        <v>5.49444230273366e-05</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.313353777732118e-06</v>
+        <v>8.38085834402591e-05</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.0002427167928544804</v>
+        <v>1.396053903590655e-05</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0006116877193562686</v>
+        <v>8.155839168466628e-06</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0001911439176183194</v>
+        <v>5.451740435091779e-05</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0002461419499013573</v>
+        <v>7.26028811186552e-05</v>
       </c>
       <c r="EH13" t="n">
-        <v>4.962903403793462e-05</v>
+        <v>7.91209822637029e-06</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.000432470696978271</v>
+        <v>7.761023880448192e-05</v>
       </c>
       <c r="EJ13" t="n">
-        <v>3.584700607461855e-05</v>
+        <v>2.277336898259819e-05</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0003768519673030823</v>
+        <v>3.948303856304847e-05</v>
       </c>
       <c r="EL13" t="n">
-        <v>1.694409002084285e-05</v>
+        <v>3.598124385462143e-05</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.0002815543266478926</v>
+        <v>7.222010754048824e-05</v>
       </c>
       <c r="EN13" t="n">
-        <v>3.996186205768026e-05</v>
+        <v>2.512514402042143e-05</v>
       </c>
       <c r="EO13" t="n">
-        <v>1.56000278366264e-05</v>
+        <v>2.935552947747055e-05</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.0002344097592867911</v>
+        <v>1.948185490618926e-05</v>
       </c>
       <c r="EQ13" t="n">
-        <v>6.990472320467234e-05</v>
+        <v>6.631152064073831e-05</v>
       </c>
       <c r="ER13" t="n">
-        <v>7.677490793867037e-05</v>
+        <v>2.75516249530483e-05</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.0003163022047374398</v>
+        <v>1.485535358369816e-05</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.0003753837081603706</v>
+        <v>9.161674097413197e-05</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0004296514089219272</v>
+        <v>9.632838191464543e-05</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.0005067758029326797</v>
+        <v>5.957619123364566e-06</v>
       </c>
       <c r="EW13" t="n">
-        <v>2.748964470811188e-05</v>
+        <v>2.515494816179853e-05</v>
       </c>
       <c r="EX13" t="n">
-        <v>5.579374555964023e-05</v>
+        <v>6.05279128649272e-05</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0001170595060102642</v>
+        <v>2.478661190252751e-05</v>
       </c>
       <c r="EZ13" t="n">
-        <v>1.480519586039009e-05</v>
+        <v>2.80190088233212e-05</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.0002354298630962148</v>
+        <v>5.636917194351554e-05</v>
       </c>
       <c r="FB13" t="n">
-        <v>8.344815432792529e-05</v>
+        <v>5.640722520183772e-07</v>
       </c>
       <c r="FC13" t="n">
-        <v>1.125852031691466e-05</v>
+        <v>8.638685540063307e-05</v>
       </c>
       <c r="FD13" t="n">
-        <v>5.404236799222417e-05</v>
+        <v>2.081453203572892e-05</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.000138400515425019</v>
+        <v>4.296324914321303e-05</v>
       </c>
       <c r="FF13" t="n">
-        <v>7.851140981074423e-05</v>
+        <v>3.418788764975034e-06</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0001990946911973879</v>
+        <v>0.0001434471923857927</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.000133558947709389</v>
+        <v>6.182595097925514e-05</v>
       </c>
       <c r="FI13" t="n">
-        <v>8.295020961668342e-05</v>
+        <v>6.52134622214362e-05</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0003674827166832983</v>
+        <v>1.189497561426833e-05</v>
       </c>
       <c r="FK13" t="n">
-        <v>2.485538425389677e-05</v>
+        <v>5.298852920532227e-05</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0008615520200692117</v>
+        <v>5.420917659648694e-05</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.0003110317629761994</v>
+        <v>1.669564881012775e-05</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.000106479594251141</v>
+        <v>4.722657467937097e-05</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.0001568546140333638</v>
+        <v>8.562578841520008e-06</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0002149508218280971</v>
+        <v>8.206542406696826e-05</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.0001631923660170287</v>
+        <v>0.0002802488452289253</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.0003259720688220114</v>
+        <v>7.274802192114294e-05</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.000370229099644348</v>
+        <v>1.717651321087033e-05</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.001128379488363862</v>
+        <v>0.0003192142467014492</v>
       </c>
       <c r="FU13" t="n">
-        <v>8.515363151673228e-05</v>
+        <v>8.064100256888196e-05</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.000308898015646264</v>
+        <v>0.0001791649265214801</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.0004215522785671055</v>
+        <v>2.31780250032898e-05</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.000350690505001694</v>
+        <v>1.237782271346077e-05</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.0003559469187166542</v>
+        <v>1.328145663137548e-05</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.0001307215716224164</v>
+        <v>3.463896064204164e-05</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.0003816979879047722</v>
+        <v>9.344865975435823e-05</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.0004669248301070184</v>
+        <v>4.274059028830379e-05</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.000239191489527002</v>
+        <v>5.127516487846151e-05</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0002925667795352638</v>
+        <v>0.0001059964415617287</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.0002428027655696496</v>
+        <v>5.654789492837153e-05</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.0006412722868844867</v>
+        <v>1.468194750486873e-05</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0005533475778065622</v>
+        <v>2.980958015541546e-05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.000967502361163497</v>
+        <v>4.210965016682167e-07</v>
       </c>
       <c r="B14" t="n">
-        <v>0.00852595642209053</v>
+        <v>5.273794522508979e-05</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0004197786620352417</v>
+        <v>3.046096935577225e-06</v>
       </c>
       <c r="D14" t="n">
-        <v>0.004265564028173685</v>
+        <v>4.998724034521729e-05</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001956043764948845</v>
+        <v>4.08064170187572e-06</v>
       </c>
       <c r="F14" t="n">
-        <v>0.000207699034945108</v>
+        <v>4.947231718688272e-05</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0008155146497301757</v>
+        <v>1.961138332262635e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0001314278488280252</v>
+        <v>1.937218257808127e-05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0005722357891499996</v>
+        <v>2.608271074677759e-07</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0004430083208717406</v>
+        <v>6.868095624668058e-06</v>
       </c>
       <c r="K14" t="n">
-        <v>0.006518677808344364</v>
+        <v>4.235001688357443e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0006065979832783341</v>
+        <v>1.562252691655885e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>0.00357888313010335</v>
+        <v>7.214487413875759e-05</v>
       </c>
       <c r="N14" t="n">
-        <v>0.002578639425337315</v>
+        <v>1.028665792546235e-05</v>
       </c>
       <c r="O14" t="n">
-        <v>0.001179061480797827</v>
+        <v>5.754095400334336e-05</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0004948013229295611</v>
+        <v>1.827681626309641e-05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.001086679054424167</v>
+        <v>9.55826817516936e-06</v>
       </c>
       <c r="R14" t="n">
-        <v>2.409687294857576e-05</v>
+        <v>3.345192908454919e-06</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0001280844735447317</v>
+        <v>2.312724518560572e-06</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0008519915863871574</v>
+        <v>6.513611424452392e-06</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0003984073409810662</v>
+        <v>1.262364276044536e-05</v>
       </c>
       <c r="V14" t="n">
-        <v>0.001263028010725975</v>
+        <v>5.348112608771771e-06</v>
       </c>
       <c r="W14" t="n">
-        <v>0.001837437157519162</v>
+        <v>1.37812730827136e-05</v>
       </c>
       <c r="X14" t="n">
-        <v>0.000639065750874579</v>
+        <v>1.968807737284806e-05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0001616610825294629</v>
+        <v>1.797302502382081e-06</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0009031145018525422</v>
+        <v>3.663285951915896e-06</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.321772833762225e-05</v>
+        <v>7.599920081702294e-06</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0003709122538566589</v>
+        <v>1.691181751084514e-06</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.0007869121618568897</v>
+        <v>1.180105209641624e-05</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0005396876367740333</v>
+        <v>4.478666141949361e-06</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0005049000028520823</v>
+        <v>1.465860987082124e-05</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.000408332678489387</v>
+        <v>3.478940243439865e-06</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.001189554343000054</v>
+        <v>2.550511999288574e-05</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.0003491875540930778</v>
+        <v>1.16771684588457e-06</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0008215636480599642</v>
+        <v>1.970279663510155e-05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0001018820912577212</v>
+        <v>6.801155450375518e-06</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.001189468428492546</v>
+        <v>3.008071871590801e-06</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.0002123674639733508</v>
+        <v>1.538166543468833e-05</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0003339282411616296</v>
+        <v>1.674659142736346e-05</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0008053599740378559</v>
+        <v>1.847147177613806e-05</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.001388948992826045</v>
+        <v>2.990136408698163e-06</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.001394618884660304</v>
+        <v>9.2717837105738e-06</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.0001286265323869884</v>
+        <v>1.013748442346696e-05</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.0007983582327142358</v>
+        <v>5.202388365432853e-06</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.0001428536488674581</v>
+        <v>4.804355285159545e-06</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.0001035066670738161</v>
+        <v>5.472571046993835e-06</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.004965148400515318</v>
+        <v>2.684151513676625e-05</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.0001119531152653508</v>
+        <v>2.370955917285755e-05</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.002044166438281536</v>
+        <v>2.371083428442944e-05</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0006965530337765813</v>
+        <v>3.146882954752073e-05</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.0002791393781080842</v>
+        <v>3.833825030596927e-05</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0003548919630702585</v>
+        <v>3.106131089225528e-06</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.0002040346444118768</v>
+        <v>2.668429715413367e-06</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.0006354928482323885</v>
+        <v>2.598745822979254e-06</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.0009635114693082869</v>
+        <v>8.359755156561732e-06</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.001704305526800454</v>
+        <v>1.895582863653544e-05</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0013370958622545</v>
+        <v>4.240387170284521e-06</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.0006918506696820259</v>
+        <v>3.212335286661983e-06</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.002490552607923746</v>
+        <v>3.491055031190626e-05</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.0009924317710101604</v>
+        <v>1.062713999999687e-05</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.001169464085251093</v>
+        <v>5.036495167587418e-06</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.0002520391717553139</v>
+        <v>2.276017767144367e-05</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.0001525212137494236</v>
+        <v>5.615031568595441e-06</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0001097457716241479</v>
+        <v>1.441534323021187e-07</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.001271898509003222</v>
+        <v>4.15007980336668e-06</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0006637858459725976</v>
+        <v>5.240638984105317e-06</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.0003200953360646963</v>
+        <v>1.279431762668537e-05</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.001211775583215058</v>
+        <v>1.617402631381992e-05</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.0008446340798400342</v>
+        <v>2.963101621844544e-07</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.0003382993745617568</v>
+        <v>1.75308991856582e-06</v>
       </c>
       <c r="BS14" t="n">
-        <v>6.526672223117203e-05</v>
+        <v>9.647765182307921e-06</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.0005787818809039891</v>
+        <v>1.048961166816298e-05</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.001140029635280371</v>
+        <v>2.911351657530759e-06</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.002907905727624893</v>
+        <v>1.385869381920202e-05</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.0003526749496813864</v>
+        <v>1.502913164586062e-05</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.0009663106175139546</v>
+        <v>3.075427957810462e-05</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.0002660736790858209</v>
+        <v>1.387370730299153e-06</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.001025992212817073</v>
+        <v>2.45193914452102e-05</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.0003643662785179913</v>
+        <v>1.690133331067045e-06</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.0006372383795678616</v>
+        <v>1.254276753570593e-06</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.0002866405702661723</v>
+        <v>6.643693723162869e-06</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.0003967487427871674</v>
+        <v>1.344121073998394e-06</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.001383650000207126</v>
+        <v>1.428555697202682e-05</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.000406527251470834</v>
+        <v>1.928993924593669e-06</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0007413948187604547</v>
+        <v>1.663522562012076e-05</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.0001887361140688881</v>
+        <v>2.53065968536248e-06</v>
       </c>
       <c r="CI14" t="n">
-        <v>3.804841981036589e-06</v>
+        <v>5.807784873468336e-06</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.0004879189364146441</v>
+        <v>7.906727432782645e-07</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.0002688764943741262</v>
+        <v>5.433583282865584e-06</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.706488546915352e-06</v>
+        <v>3.887538241542643e-06</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.00287746568210423</v>
+        <v>1.012322172755376e-05</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.0004943539388477802</v>
+        <v>1.386710482620401e-05</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.0002206876524724066</v>
+        <v>3.030791049241088e-05</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.0003120345354545861</v>
+        <v>2.428251536912285e-05</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0003988136304542422</v>
+        <v>1.522631191619439e-05</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.002847625175490975</v>
+        <v>3.994348389824154e-06</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.0005601560114882886</v>
+        <v>7.393404757749522e-06</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.0005985230673104525</v>
+        <v>2.445949394314084e-05</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.001457032165490091</v>
+        <v>1.790970713955176e-06</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.0002859105879906565</v>
+        <v>1.336976197308104e-06</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.001420086482539773</v>
+        <v>1.328376129094977e-05</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.0008025558199733496</v>
+        <v>1.185203245768207e-06</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0008505707373842597</v>
+        <v>1.633669671718962e-05</v>
       </c>
       <c r="CZ14" t="n">
-        <v>7.322906458284706e-05</v>
+        <v>3.944558557122946e-06</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.000212388054933399</v>
+        <v>6.636334546783473e-06</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0002765342069324106</v>
+        <v>3.733985067810863e-07</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.0004945227992720902</v>
+        <v>8.310646080644801e-06</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.505257387179881e-06</v>
+        <v>4.238628207531292e-06</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.001163158332929015</v>
+        <v>6.347379894577898e-06</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.002539661945775151</v>
+        <v>9.205431524605956e-06</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.002310610841959715</v>
+        <v>4.888614967057947e-06</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.001582412514835596</v>
+        <v>1.523505488876253e-05</v>
       </c>
       <c r="DI14" t="n">
-        <v>4.549857840174809e-05</v>
+        <v>6.698256584058981e-06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.0006010631332173944</v>
+        <v>2.045437577180564e-05</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.001691895187832415</v>
+        <v>5.046062597102718e-06</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.001342695322819054</v>
+        <v>3.522492625052109e-05</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.0003228159621357918</v>
+        <v>7.416882908728439e-06</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0009131589904427528</v>
+        <v>8.684339718456613e-07</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.0001605471188668162</v>
+        <v>1.352592971670674e-05</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.0001069891368388198</v>
+        <v>4.60894943898893e-06</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.001437419792637229</v>
+        <v>4.498610906011891e-06</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.310956476023421e-05</v>
+        <v>4.730994078272488e-06</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.0001525335537735373</v>
+        <v>1.058507677953457e-06</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.0003824988089036196</v>
+        <v>7.358766197285149e-06</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.0006228307029232383</v>
+        <v>1.551047171233222e-05</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.0007545802509412169</v>
+        <v>1.283148503716802e-05</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.0009997414890676737</v>
+        <v>3.588550043787109e-07</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.000523529713973403</v>
+        <v>3.2827265386004e-06</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.0003114086284767836</v>
+        <v>1.684250855760183e-05</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.0005877759540453553</v>
+        <v>1.98965772142401e-05</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.000944644445553422</v>
+        <v>6.526071842927195e-07</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.001374996034428477</v>
+        <v>1.182695359602803e-05</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.001476479461416602</v>
+        <v>5.434736976894783e-06</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.0002401802485110238</v>
+        <v>3.373487561475486e-05</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.000376740179490298</v>
+        <v>1.941359005286358e-05</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.001353170489892364</v>
+        <v>9.331111868959852e-06</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.001291682245209813</v>
+        <v>3.300595835753484e-06</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.001733306329697371</v>
+        <v>1.15197562990943e-05</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.0008104014559648931</v>
+        <v>1.294470166612882e-05</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.0003541147452779114</v>
+        <v>7.455919330823235e-06</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.0001001452255877666</v>
+        <v>3.129053766315337e-06</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.0001919950009323657</v>
+        <v>2.440011257931474e-06</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.0002409931039437652</v>
+        <v>4.930596332997084e-06</v>
       </c>
       <c r="EN14" t="n">
-        <v>2.542747097322717e-05</v>
+        <v>4.037158305436606e-07</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.0003104005008935928</v>
+        <v>5.511521067091962e-06</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.001630718470551074</v>
+        <v>1.575306487211492e-05</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0001772833929862827</v>
+        <v>4.706127583631314e-06</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.001374505809508264</v>
+        <v>3.796487817453453e-06</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.0005024700076319277</v>
+        <v>4.035131951241056e-06</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.0003650495200417936</v>
+        <v>2.880748752431828e-06</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.0008880100795067847</v>
+        <v>1.091458670998691e-05</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.0004448239924386144</v>
+        <v>9.213616067427211e-06</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.0003704616974573582</v>
+        <v>1.979429544007871e-05</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.0006118585588410497</v>
+        <v>1.363811406918103e-06</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.001451265416108072</v>
+        <v>1.49919842442614e-05</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.0005907913437113166</v>
+        <v>5.062300942881848e-07</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.0009124042117036879</v>
+        <v>2.054758806480095e-05</v>
       </c>
       <c r="FB14" t="n">
-        <v>7.524651300627738e-05</v>
+        <v>2.363841986152693e-06</v>
       </c>
       <c r="FC14" t="n">
-        <v>3.900044248439372e-05</v>
+        <v>5.346903890313115e-06</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0004270193458069116</v>
+        <v>3.750026280613383e-06</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.0005005362909287214</v>
+        <v>1.028321366902674e-05</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.0001321090967394412</v>
+        <v>6.040253879291413e-07</v>
       </c>
       <c r="FG14" t="n">
-        <v>6.640981882810593e-05</v>
+        <v>5.611777851299848e-07</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.000182769654202275</v>
+        <v>8.114889169519302e-06</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.00072971370536834</v>
+        <v>8.106764653348364e-06</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.001215627766214311</v>
+        <v>1.063907438947354e-05</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.0007727413903921843</v>
+        <v>6.042785685167473e-07</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.000523111317306757</v>
+        <v>3.973255843447987e-06</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.0003611088613979518</v>
+        <v>2.532436610636069e-06</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.0003012418746948242</v>
+        <v>1.598849621586851e-06</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.0003056983696296811</v>
+        <v>2.066227534669451e-05</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.002160791773349047</v>
+        <v>1.501274527981877e-05</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.0005506153684109449</v>
+        <v>3.367810131749138e-05</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.002863760106265545</v>
+        <v>2.810909609252121e-05</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.0002999005664605647</v>
+        <v>1.931852966663428e-05</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.0003404461604077369</v>
+        <v>1.260019598703366e-05</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.0008104147273115814</v>
+        <v>3.293423105787951e-06</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.001132671721279621</v>
+        <v>6.377865702233976e-06</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.0007246696623042226</v>
+        <v>2.916665471275337e-05</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.0009876079857349396</v>
+        <v>3.296232989669079e-06</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.0001774828706402332</v>
+        <v>1.526033315712993e-06</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.0005960247362963855</v>
+        <v>5.73951820115326e-06</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.0002110272325808182</v>
+        <v>9.20608999877004e-06</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.0003094878629781306</v>
+        <v>1.344653355772607e-05</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.0006848124321550131</v>
+        <v>6.160939392430009e-06</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.0001638116373214871</v>
+        <v>2.067280911433045e-05</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.001295199617743492</v>
+        <v>2.000894892262295e-05</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.0002350246795685962</v>
+        <v>3.489922619337449e-06</v>
       </c>
       <c r="GG14" t="n">
-        <v>4.364835331216455e-05</v>
+        <v>2.095809122693026e-06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.1179532185196877</v>
+        <v>0.004862517118453979</v>
       </c>
       <c r="B15" t="n">
-        <v>0.4086227416992188</v>
+        <v>0.57892906665802</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2002087831497192</v>
+        <v>0.0811115950345993</v>
       </c>
       <c r="D15" t="n">
-        <v>0.02880354225635529</v>
+        <v>0.3092120587825775</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0197340939193964</v>
+        <v>0.1409305781126022</v>
       </c>
       <c r="F15" t="n">
-        <v>0.09786935150623322</v>
+        <v>0.002979236422106624</v>
       </c>
       <c r="G15" t="n">
-        <v>0.04083642363548279</v>
+        <v>0.3638571500778198</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1315550059080124</v>
+        <v>0.2534731328487396</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03557740524411201</v>
+        <v>0.03583661839365959</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1999771445989609</v>
+        <v>0.1665270328521729</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3822925388813019</v>
+        <v>0.6293869018554688</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1484428197145462</v>
+        <v>0.08152393251657486</v>
       </c>
       <c r="M15" t="n">
-        <v>0.02980890311300755</v>
+        <v>0.4981458783149719</v>
       </c>
       <c r="N15" t="n">
-        <v>0.08167183399200439</v>
+        <v>0.350399911403656</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01067967060953379</v>
+        <v>0.168790265917778</v>
       </c>
       <c r="P15" t="n">
-        <v>0.07658950984477997</v>
+        <v>0.418304979801178</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.153922364115715</v>
+        <v>0.2279553562402725</v>
       </c>
       <c r="R15" t="n">
-        <v>0.08392908424139023</v>
+        <v>0.06280895322561264</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0723525807261467</v>
+        <v>0.003854025388136506</v>
       </c>
       <c r="T15" t="n">
-        <v>0.08110932260751724</v>
+        <v>0.02129163779318333</v>
       </c>
       <c r="U15" t="n">
-        <v>0.08334069699048996</v>
+        <v>0.01913627982139587</v>
       </c>
       <c r="V15" t="n">
-        <v>0.04363056272268295</v>
+        <v>0.06482828408479691</v>
       </c>
       <c r="W15" t="n">
-        <v>0.03266989439725876</v>
+        <v>0.02835377305746078</v>
       </c>
       <c r="X15" t="n">
-        <v>0.01871062442660332</v>
+        <v>0.009755367413163185</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.01875350810587406</v>
+        <v>0.04346909746527672</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.05715025961399078</v>
+        <v>0.06795809417963028</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.03812981396913528</v>
+        <v>0.1160227879881859</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.07913784682750702</v>
+        <v>0.06970267742872238</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.08983607590198517</v>
+        <v>0.02095754072070122</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.03244347497820854</v>
+        <v>0.05674884840846062</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.05574305355548859</v>
+        <v>0.009538926184177399</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.02469319477677345</v>
+        <v>0.06403792649507523</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.02149097621440887</v>
+        <v>0.03014666587114334</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.0104520171880722</v>
+        <v>0.1170540452003479</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.009329242631793022</v>
+        <v>0.0634751096367836</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.03471457585692406</v>
+        <v>0.0309464018791914</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.02266672998666763</v>
+        <v>0.05894765630364418</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.03567603603005409</v>
+        <v>0.1134033724665642</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.02228700555860996</v>
+        <v>0.05643041431903839</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.0642467737197876</v>
+        <v>0.09605342149734497</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.02656114473938942</v>
+        <v>0.02279672957956791</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.08334390819072723</v>
+        <v>0.05008760467171669</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.08608324825763702</v>
+        <v>0.04720418900251389</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.01645106449723244</v>
+        <v>0.05323666706681252</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.03648939728736877</v>
+        <v>0.01731794513761997</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.09535138309001923</v>
+        <v>0.02938305772840977</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.1710586398839951</v>
+        <v>0.2329894751310349</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.09305837750434875</v>
+        <v>0.001866770908236504</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.0654342919588089</v>
+        <v>0.2507056891918182</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.06749409437179565</v>
+        <v>0.1743407249450684</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.1024126037955284</v>
+        <v>0.1653813272714615</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.04605337232351303</v>
+        <v>0.0840827077627182</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.04240697249770164</v>
+        <v>0.06966128945350647</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.1191306114196777</v>
+        <v>0.02120151184499264</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.1819460541009903</v>
+        <v>0.07580848783254623</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.126411959528923</v>
+        <v>0.04027719795703888</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.05621824041008949</v>
+        <v>0.04318001121282578</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.0194048210978508</v>
+        <v>0.09404948353767395</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.2654181122779846</v>
+        <v>0.01874203607439995</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.03233207762241364</v>
+        <v>0.1728531867265701</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.06587748974561691</v>
+        <v>0.1360796093940735</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.2850215137004852</v>
+        <v>0.0008061956614255905</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.009682102128863335</v>
+        <v>0.04427544772624969</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.04555127024650574</v>
+        <v>0.07987281680107117</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.02336122840642929</v>
+        <v>0.04213540628552437</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.08515588939189911</v>
+        <v>0.08124180883169174</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.001320643350481987</v>
+        <v>0.06422165036201477</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.1413855850696564</v>
+        <v>0.08003817498683929</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.02204727195203304</v>
+        <v>0.003324155695736408</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.1041426360607147</v>
+        <v>0.02890679985284805</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.05080123245716095</v>
+        <v>0.121446780860424</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.08159260451793671</v>
+        <v>0.1045395731925964</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.08699587732553482</v>
+        <v>0.01486362423747778</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.071816585958004</v>
+        <v>0.242663562297821</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.003451772965490818</v>
+        <v>0.01581126824021339</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.00631088949739933</v>
+        <v>0.3236873149871826</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.08830525726079941</v>
+        <v>0.09534905850887299</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.01661198958754539</v>
+        <v>0.01669333875179291</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.02057958766818047</v>
+        <v>0.04400327056646347</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.1012008115649223</v>
+        <v>0.02739381045103073</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.1052932664752007</v>
+        <v>0.08432628214359283</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.05528337135910988</v>
+        <v>0.01478649955242872</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.07120158523321152</v>
+        <v>0.1650655269622803</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.04420039057731628</v>
+        <v>0.02371499128639698</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.009509120136499405</v>
+        <v>0.09454011917114258</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.06987892091274261</v>
+        <v>0.05319451168179512</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.05357344448566437</v>
+        <v>0.04583252221345901</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.001718731597065926</v>
+        <v>0.01195109635591507</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.02495198324322701</v>
+        <v>0.03978394716978073</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.04736341163516045</v>
+        <v>0.003678911365568638</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.01853708177804947</v>
+        <v>0.02998438291251659</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.001532541587948799</v>
+        <v>0.1190177202224731</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.01505330298095942</v>
+        <v>0.01880870759487152</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.04900080338120461</v>
+        <v>0.06801272183656693</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.1176877915859222</v>
+        <v>0.225448951125145</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.07182469964027405</v>
+        <v>0.1419036537408829</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.05344386398792267</v>
+        <v>0.1935569494962692</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.02673957496881485</v>
+        <v>0.2496903985738754</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.05130927637219429</v>
+        <v>0.1052753329277039</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.04533301666378975</v>
+        <v>0.01770506054162979</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.0626537948846817</v>
+        <v>0.1663800776004791</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.02107900008559227</v>
+        <v>0.01149021275341511</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.01781320571899414</v>
+        <v>0.122112050652504</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.05272561684250832</v>
+        <v>0.06940098106861115</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.05004191026091576</v>
+        <v>0.04073585197329521</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.01658211462199688</v>
+        <v>0.04639160633087158</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.01215667836368084</v>
+        <v>0.04009919613599777</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.05144214630126953</v>
+        <v>0.03091385401785374</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.0489862859249115</v>
+        <v>0.0135652981698513</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.2777161300182343</v>
+        <v>0.07223713397979736</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.04551377892494202</v>
+        <v>0.0331234410405159</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.0395609624683857</v>
+        <v>0.1730127334594727</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.01729624904692173</v>
+        <v>0.1115302070975304</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.1195758506655693</v>
+        <v>0.3956951200962067</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.1521378755569458</v>
+        <v>0.166125699877739</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.007345899008214474</v>
+        <v>0.01412341557443142</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.03548282012343407</v>
+        <v>0.1109872311353683</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.08788251876831055</v>
+        <v>0.003151025623083115</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.04420487210154533</v>
+        <v>0.1439805626869202</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.2094965577125549</v>
+        <v>0.09126216918230057</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.07453557103872299</v>
+        <v>0.09123758226633072</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.1017899140715599</v>
+        <v>0.03196488693356514</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.04449403285980225</v>
+        <v>0.01736865565180779</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.01266328617930412</v>
+        <v>0.004641368985176086</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.0409417413175106</v>
+        <v>0.02857546135783195</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.03279996663331985</v>
+        <v>0.2245910316705704</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.0326286256313324</v>
+        <v>0.03637687116861343</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.002742650453001261</v>
+        <v>0.1623211205005646</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.1147305443882942</v>
+        <v>0.001876357942819595</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.04272805154323578</v>
+        <v>0.05268315225839615</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.04111255332827568</v>
+        <v>0.0911034420132637</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.1462526321411133</v>
+        <v>0.2055418640375137</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.05633468925952911</v>
+        <v>0.08834098279476166</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.08640597015619278</v>
+        <v>0.1110698729753494</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.01754320785403252</v>
+        <v>0.07231397926807404</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.06963533163070679</v>
+        <v>0.03822155296802521</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.08005863428115845</v>
+        <v>0.2224811911582947</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.03000848740339279</v>
+        <v>0.0548684149980545</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.05400396138429642</v>
+        <v>0.05420819297432899</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.02067911252379417</v>
+        <v>0.02407872676849365</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.01916174590587616</v>
+        <v>0.06134761124849319</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.009910685941576958</v>
+        <v>0.001744913053698838</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.0385466143488884</v>
+        <v>0.03913617506623268</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.0626135841012001</v>
+        <v>0.01085406914353371</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.01283648423850536</v>
+        <v>0.1124996095895767</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.03351132944226265</v>
+        <v>0.1803100407123566</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.01960892789065838</v>
+        <v>0.05628721788525581</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.01079333573579788</v>
+        <v>0.2184772342443466</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.03202393651008606</v>
+        <v>0.1135328859090805</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.01829752512276173</v>
+        <v>0.02042123861610889</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.07449523359537125</v>
+        <v>0.07970929145812988</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.09123957902193069</v>
+        <v>0.1386731266975403</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.0258848425000906</v>
+        <v>0.005120001267641783</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.03705021739006042</v>
+        <v>0.001470759510993958</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.08994768559932709</v>
+        <v>0.2094240188598633</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.0382656641304493</v>
+        <v>0.01536155119538307</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.01054329797625542</v>
+        <v>0.1078240871429443</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.0384264849126339</v>
+        <v>0.06214518472552299</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.04829097911715508</v>
+        <v>0.06202200800180435</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.0394853912293911</v>
+        <v>0.03619292005896568</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.0003525707288645208</v>
+        <v>0.05221964418888092</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.07277651876211166</v>
+        <v>0.03493447974324226</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.01005424745380878</v>
+        <v>0.05656313896179199</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.04034161567687988</v>
+        <v>0.07977105677127838</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.02184896171092987</v>
+        <v>0.05155176296830177</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.02367960102856159</v>
+        <v>0.01212763600051403</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.07050091773271561</v>
+        <v>0.02327556535601616</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.07295797765254974</v>
+        <v>0.0788385346531868</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.01359993033111095</v>
+        <v>0.06938225775957108</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.03458975628018379</v>
+        <v>0.04494727030396461</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.08076067268848419</v>
+        <v>0.1761486530303955</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.1615387499332428</v>
+        <v>0.2035724371671677</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.08839964866638184</v>
+        <v>0.06750556081533432</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.1785275787115097</v>
+        <v>0.08816028386354446</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.05235400423407555</v>
+        <v>0.4468719661235809</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.1083838120102882</v>
+        <v>0.3463898897171021</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.1292045712471008</v>
+        <v>0.2288990914821625</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.04856175184249878</v>
+        <v>0.1684434115886688</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.004166560247540474</v>
+        <v>0.1424101144075394</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.08793135732412338</v>
+        <v>0.08442202210426331</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.04913816601037979</v>
+        <v>0.05232744663953781</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.02725711278617382</v>
+        <v>0.02261326462030411</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.04981298744678497</v>
+        <v>0.03926663100719452</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.0001865271478891373</v>
+        <v>0.02033402398228645</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.09411296248435974</v>
+        <v>0.1557200700044632</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.1173205822706223</v>
+        <v>0.04584302753210068</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.03743978589773178</v>
+        <v>0.02570338547229767</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.03517181426286697</v>
+        <v>0.06703048199415207</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.05704796314239502</v>
+        <v>0.03900797292590141</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.0002942474966403097</v>
+        <v>1.302576401940314e-05</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0004199130926281214</v>
+        <v>6.590299017261714e-05</v>
       </c>
       <c r="C16" t="n">
-        <v>0.001670595956966281</v>
+        <v>0.0001037811889545992</v>
       </c>
       <c r="D16" t="n">
-        <v>0.001535473391413689</v>
+        <v>0.0001205968073918484</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001684274291619658</v>
+        <v>5.136233085067943e-06</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0007200372638180852</v>
+        <v>3.644244861789048e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0004457737086340785</v>
+        <v>2.551068610046059e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>5.914501525694504e-05</v>
+        <v>2.830893572536297e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0008779120398685336</v>
+        <v>7.926880789455026e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0002202334289904684</v>
+        <v>2.851666613423731e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0003920674207620323</v>
+        <v>7.505308894906193e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.001313574844971299</v>
+        <v>0.0001460399944335222</v>
       </c>
       <c r="M16" t="n">
-        <v>0.001879599643871188</v>
+        <v>0.0001683426380623132</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0004366682842373848</v>
+        <v>5.861302634002641e-05</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0006360848783515394</v>
+        <v>5.44948925380595e-05</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0003140670014545321</v>
+        <v>4.124536644667387e-06</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0002466386358719319</v>
+        <v>8.043673733482137e-05</v>
       </c>
       <c r="R16" t="n">
-        <v>0.001254096394404769</v>
+        <v>2.733102519414388e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>8.614236139692366e-05</v>
+        <v>1.785058157111052e-05</v>
       </c>
       <c r="T16" t="n">
-        <v>0.000504443421959877</v>
+        <v>2.983586000482319e-06</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0004529901198111475</v>
+        <v>2.477354064467363e-05</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0003382510039955378</v>
+        <v>2.655059142853133e-05</v>
       </c>
       <c r="W16" t="n">
-        <v>4.682510552811436e-05</v>
+        <v>4.47383317805361e-05</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0002580445725470781</v>
+        <v>4.155272472416982e-05</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.0001664894225541502</v>
+        <v>7.740299224678893e-06</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.320839798310772e-05</v>
+        <v>1.522041293355869e-05</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.0002263557107653469</v>
+        <v>2.792322447930928e-05</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0005895810318179429</v>
+        <v>2.431561915727798e-05</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.0002784435055218637</v>
+        <v>4.650108166970313e-06</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.0003120916371699423</v>
+        <v>1.51178201122093e-05</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.0006806404562667012</v>
+        <v>5.19085988344159e-05</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0003943428455386311</v>
+        <v>2.451470390951727e-05</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.0001676568354014307</v>
+        <v>4.35067977377912e-06</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.0001071766309905797</v>
+        <v>1.155870450020302e-05</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.0001434811129001901</v>
+        <v>2.823136310325935e-05</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.0003901653690263629</v>
+        <v>4.576717401505448e-06</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.0001081787995644845</v>
+        <v>5.804744432680309e-06</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.0001480485079810023</v>
+        <v>1.426450580765959e-06</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.0001434937003068626</v>
+        <v>2.65232320089126e-05</v>
       </c>
       <c r="AN16" t="n">
-        <v>8.409077418036759e-05</v>
+        <v>2.868976480385754e-05</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.0004864575457759202</v>
+        <v>2.975264760607388e-05</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.0001177804369945079</v>
+        <v>2.632355972309597e-06</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.0001712437806418166</v>
+        <v>1.317780515819322e-05</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.950254126219079e-05</v>
+        <v>2.476113877492025e-05</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.651486834627576e-06</v>
+        <v>4.675371019402519e-05</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.000657921948004514</v>
+        <v>2.61437708104495e-05</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.0009534002165310085</v>
+        <v>5.295952178130392e-06</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.0005927325692027807</v>
+        <v>0.0001769531518220901</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.001002954901196063</v>
+        <v>9.834455704549327e-05</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.0007276808028109372</v>
+        <v>3.376405220478773e-05</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.0004050051211379468</v>
+        <v>7.560849189758301e-05</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.0001009993138723075</v>
+        <v>6.711423338856548e-05</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.0001723976311041042</v>
+        <v>3.408557313377969e-05</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.0003644093230832368</v>
+        <v>5.909540050197393e-05</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.0002745870151557028</v>
+        <v>2.799552021315321e-05</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.00149239506572485</v>
+        <v>1.261297984456178e-05</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.0004053131269756705</v>
+        <v>3.968959572375752e-05</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.0004696226678788662</v>
+        <v>2.460297764628194e-05</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.450832031783648e-05</v>
+        <v>2.910446164605673e-05</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.001202852232381701</v>
+        <v>3.578653195290826e-05</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.0003574391885194927</v>
+        <v>5.331879219738767e-05</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.0007263527950271964</v>
+        <v>3.980257679359056e-05</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.001123597961850464</v>
+        <v>4.276625622878782e-05</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.0002690731780603528</v>
+        <v>4.816743967239745e-05</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.0003013023524545133</v>
+        <v>4.130985325900838e-05</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.0001226624444825575</v>
+        <v>2.181125273637008e-05</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.0003480173763819039</v>
+        <v>3.815069794654846e-05</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.0003282726975157857</v>
+        <v>4.176781658316031e-05</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.264306284720078e-05</v>
+        <v>1.593302476976532e-05</v>
       </c>
       <c r="BR16" t="n">
-        <v>0.0001497398188803345</v>
+        <v>1.946230986504816e-05</v>
       </c>
       <c r="BS16" t="n">
-        <v>0.0002195558481616899</v>
+        <v>8.075781806837767e-05</v>
       </c>
       <c r="BT16" t="n">
-        <v>9.253001189790666e-05</v>
+        <v>1.192149647977203e-05</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.0002872224140446633</v>
+        <v>4.608526978699956e-06</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.0003744478162843734</v>
+        <v>2.063804458884988e-05</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.0004011776763945818</v>
+        <v>9.393344225827605e-05</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.0008390638395212591</v>
+        <v>9.775020589586347e-05</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.0008641169406473637</v>
+        <v>3.564294456737116e-05</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.0002262976631755009</v>
+        <v>2.455637331877369e-05</v>
       </c>
       <c r="CA16" t="n">
-        <v>5.677293665939942e-05</v>
+        <v>4.829920726479031e-06</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.487680078251287e-05</v>
+        <v>2.304295958310831e-05</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.0004989798180758953</v>
+        <v>3.308330269646831e-05</v>
       </c>
       <c r="CD16" t="n">
-        <v>6.989643588894978e-05</v>
+        <v>2.946844460893772e-06</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.000147269616718404</v>
+        <v>1.756636083882768e-05</v>
       </c>
       <c r="CF16" t="n">
-        <v>0.000500353635288775</v>
+        <v>3.791653216467239e-05</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.0003083516494370997</v>
+        <v>4.981172969564795e-05</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.000451909756520763</v>
+        <v>9.589110050001182e-06</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.0001386952644679695</v>
+        <v>1.441880522179417e-05</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.0001668052427703515</v>
+        <v>4.552052814688068e-07</v>
       </c>
       <c r="CK16" t="n">
-        <v>0.0001745566260069609</v>
+        <v>1.088879616872873e-05</v>
       </c>
       <c r="CL16" t="n">
-        <v>7.236416422529146e-05</v>
+        <v>7.327390903810738e-06</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.0006699255318380892</v>
+        <v>6.756909897376318e-06</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.000684895203448832</v>
+        <v>1.843947757151909e-05</v>
       </c>
       <c r="CO16" t="n">
-        <v>3.857596311718225e-06</v>
+        <v>7.095848559401929e-05</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.0002990609791595489</v>
+        <v>0.0001002576973405667</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.0001024662924464792</v>
+        <v>1.874461304396391e-06</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.0002067367604468018</v>
+        <v>5.148208583705127e-05</v>
       </c>
       <c r="CS16" t="n">
-        <v>0.0002539907000027597</v>
+        <v>1.078461627912475e-05</v>
       </c>
       <c r="CT16" t="n">
-        <v>0.0006456360570155084</v>
+        <v>1.438295657862909e-05</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.696436811471358e-05</v>
+        <v>3.463188113528304e-05</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.132398301706417e-05</v>
+        <v>6.418874363589566e-06</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.0002277699531987309</v>
+        <v>3.086296783294529e-05</v>
       </c>
       <c r="CX16" t="n">
-        <v>0.0003414354287087917</v>
+        <v>3.225024556741118e-05</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.0003239192883484066</v>
+        <v>4.476425965549424e-05</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.0003298452065791935</v>
+        <v>6.001096153340768e-06</v>
       </c>
       <c r="DA16" t="n">
-        <v>9.629849228076637e-05</v>
+        <v>2.664009844011161e-05</v>
       </c>
       <c r="DB16" t="n">
-        <v>0.0001858913747128099</v>
+        <v>2.951304850284941e-06</v>
       </c>
       <c r="DC16" t="n">
-        <v>9.480470907874405e-05</v>
+        <v>7.633123459527269e-06</v>
       </c>
       <c r="DD16" t="n">
-        <v>9.49359018704854e-05</v>
+        <v>8.389632057514973e-06</v>
       </c>
       <c r="DE16" t="n">
-        <v>6.453915557358414e-05</v>
+        <v>3.885812111548148e-05</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.0004954907344654202</v>
+        <v>3.717554864124395e-05</v>
       </c>
       <c r="DG16" t="n">
-        <v>0.001213577808812261</v>
+        <v>6.153323965918389e-07</v>
       </c>
       <c r="DH16" t="n">
-        <v>4.241500937496312e-05</v>
+        <v>3.213225863873959e-05</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.0003973935381509364</v>
+        <v>1.729959694785066e-05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.0003113516431767493</v>
+        <v>4.885159796685912e-07</v>
       </c>
       <c r="DK16" t="n">
-        <v>0.0005983144510537386</v>
+        <v>4.365574568510056e-05</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.0003165967063978314</v>
+        <v>5.111316568218172e-05</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.0002986906329169869</v>
+        <v>5.480853724293411e-05</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.586872531333938e-05</v>
+        <v>1.246732426807284e-05</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.0005756384925916791</v>
+        <v>2.821997622959316e-05</v>
       </c>
       <c r="DP16" t="n">
-        <v>0.0001419799373252317</v>
+        <v>1.415976657881401e-05</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.0001549652370158583</v>
+        <v>1.46750571730081e-05</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.001038853428326547</v>
+        <v>4.160834578215145e-05</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.0002704058715607971</v>
+        <v>1.024798893922707e-05</v>
       </c>
       <c r="DT16" t="n">
-        <v>5.058950046077371e-05</v>
+        <v>6.625066816923209e-06</v>
       </c>
       <c r="DU16" t="n">
-        <v>0.0001428826944902539</v>
+        <v>1.939988942467608e-05</v>
       </c>
       <c r="DV16" t="n">
-        <v>0.0005982838338240981</v>
+        <v>3.108296732534654e-05</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.0001364649797324091</v>
+        <v>5.325035454006866e-05</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.0006434574024751782</v>
+        <v>1.929594327521045e-05</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.000540047069080174</v>
+        <v>2.454166133247782e-05</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.0001451805437682196</v>
+        <v>4.664966581913177e-06</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.0003736248181667179</v>
+        <v>1.06396701085032e-05</v>
       </c>
       <c r="EB16" t="n">
-        <v>8.85988338268362e-05</v>
+        <v>1.637875539017841e-05</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.23164276778698e-05</v>
+        <v>9.136863809544593e-06</v>
       </c>
       <c r="ED16" t="n">
-        <v>0.0002712399582378566</v>
+        <v>5.338736082194373e-05</v>
       </c>
       <c r="EE16" t="n">
-        <v>0.0002267922245664522</v>
+        <v>2.321084866707679e-05</v>
       </c>
       <c r="EF16" t="n">
-        <v>0.0002010305470321327</v>
+        <v>2.3436365154339e-05</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.0004890197888016701</v>
+        <v>2.175392000935972e-05</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.000549279386177659</v>
+        <v>1.013100063573802e-05</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.0006855645915493369</v>
+        <v>5.602583769359626e-05</v>
       </c>
       <c r="EJ16" t="n">
-        <v>1.740649167913944e-05</v>
+        <v>1.318847716902383e-05</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.0001035897657857276</v>
+        <v>6.277369720919523e-06</v>
       </c>
       <c r="EL16" t="n">
-        <v>0.0001853327557910234</v>
+        <v>5.176976628717966e-06</v>
       </c>
       <c r="EM16" t="n">
-        <v>5.911008338443935e-05</v>
+        <v>1.761426347002271e-06</v>
       </c>
       <c r="EN16" t="n">
-        <v>0.0002149595529772341</v>
+        <v>6.879326974740252e-07</v>
       </c>
       <c r="EO16" t="n">
-        <v>3.456613194430247e-05</v>
+        <v>3.560988261597231e-06</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.0006014388636685908</v>
+        <v>2.034927274507936e-05</v>
       </c>
       <c r="EQ16" t="n">
-        <v>9.862937440630049e-05</v>
+        <v>1.242615235241828e-05</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.0003393929218873382</v>
+        <v>3.667850978672504e-05</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.0002000547974603251</v>
+        <v>1.411563425790519e-05</v>
       </c>
       <c r="ET16" t="n">
-        <v>7.746285700704902e-05</v>
+        <v>5.355850589694455e-05</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.000266959163127467</v>
+        <v>2.082658284052741e-06</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.0001440921769244596</v>
+        <v>3.300955722806975e-05</v>
       </c>
       <c r="EW16" t="n">
-        <v>0.0005929036415182054</v>
+        <v>5.361918738344684e-06</v>
       </c>
       <c r="EX16" t="n">
-        <v>1.833984060795046e-05</v>
+        <v>1.603591499588219e-06</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.000345874490449205</v>
+        <v>2.343729465792421e-05</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0.0004792411637026817</v>
+        <v>3.902333992300555e-05</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.0003531479742377996</v>
+        <v>6.366387970047072e-05</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.0003188015834894031</v>
+        <v>3.887979346473003e-06</v>
       </c>
       <c r="FC16" t="n">
-        <v>5.122863876749761e-05</v>
+        <v>2.179803595936392e-05</v>
       </c>
       <c r="FD16" t="n">
-        <v>0.0001460885396227241</v>
+        <v>4.45859723186004e-06</v>
       </c>
       <c r="FE16" t="n">
-        <v>0.0001387745141983032</v>
+        <v>2.271336416015401e-05</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.00014382520748768</v>
+        <v>1.155885092885001e-05</v>
       </c>
       <c r="FG16" t="n">
-        <v>0.0001264040038222447</v>
+        <v>1.424312631570501e-05</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.0002421791141387075</v>
+        <v>1.48029466799926e-05</v>
       </c>
       <c r="FI16" t="n">
-        <v>1.107741627492942e-05</v>
+        <v>1.173760028905235e-05</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.0003023716853931546</v>
+        <v>3.351924533490092e-05</v>
       </c>
       <c r="FK16" t="n">
-        <v>5.735323793487623e-05</v>
+        <v>1.103382237488404e-05</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.000116962444735691</v>
+        <v>2.761949872365221e-05</v>
       </c>
       <c r="FM16" t="n">
-        <v>2.090696943923831e-05</v>
+        <v>3.513268893584609e-07</v>
       </c>
       <c r="FN16" t="n">
-        <v>0.0004249743651598692</v>
+        <v>1.229249119205633e-05</v>
       </c>
       <c r="FO16" t="n">
-        <v>7.07386716385372e-05</v>
+        <v>2.130156644852832e-06</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.0002117293333867565</v>
+        <v>6.465789920184761e-05</v>
       </c>
       <c r="FQ16" t="n">
-        <v>5.632874672301114e-05</v>
+        <v>1.929054269567132e-05</v>
       </c>
       <c r="FR16" t="n">
-        <v>8.028504089452326e-05</v>
+        <v>2.826921445375774e-05</v>
       </c>
       <c r="FS16" t="n">
-        <v>8.640289888717234e-05</v>
+        <v>1.540337689220905e-05</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.000459707691334188</v>
+        <v>4.562168760458007e-05</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.0003501501341816038</v>
+        <v>3.146518429275602e-05</v>
       </c>
       <c r="FV16" t="n">
-        <v>0.0001107192729250528</v>
+        <v>1.907944897538982e-05</v>
       </c>
       <c r="FW16" t="n">
-        <v>0.0005088725592941046</v>
+        <v>2.380510522925761e-05</v>
       </c>
       <c r="FX16" t="n">
-        <v>8.250935934484005e-06</v>
+        <v>1.400148266839096e-05</v>
       </c>
       <c r="FY16" t="n">
-        <v>6.939195009181276e-05</v>
+        <v>2.5752106012078e-05</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.0004064759705215693</v>
+        <v>2.820187000907026e-05</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.0001285918551729992</v>
+        <v>7.79118636273779e-06</v>
       </c>
       <c r="GB16" t="n">
-        <v>0.0003919727460015565</v>
+        <v>6.630884308833629e-05</v>
       </c>
       <c r="GC16" t="n">
-        <v>0.0006656856276094913</v>
+        <v>2.004189809667878e-05</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.0004753886605612934</v>
+        <v>4.146634091739543e-05</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.0001176192163256928</v>
+        <v>2.816908818203956e-06</v>
       </c>
       <c r="GF16" t="n">
-        <v>0.0003828332992270589</v>
+        <v>1.705670729279518e-05</v>
       </c>
       <c r="GG16" t="n">
-        <v>0.0001083721872419119</v>
+        <v>4.135750714340247e-05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1.792124294297537e-06</v>
+        <v>0.0016616340726614</v>
       </c>
       <c r="B17" t="n">
-        <v>2.76775645033922e-05</v>
+        <v>0.001517624827101827</v>
       </c>
       <c r="C17" t="n">
-        <v>7.687414836254902e-06</v>
+        <v>0.002256435807794333</v>
       </c>
       <c r="D17" t="n">
-        <v>1.528321035948466e-06</v>
+        <v>0.002166775753721595</v>
       </c>
       <c r="E17" t="n">
-        <v>2.793402745737694e-05</v>
+        <v>0.001790148671716452</v>
       </c>
       <c r="F17" t="n">
-        <v>9.844117448665202e-05</v>
+        <v>0.005419777240604162</v>
       </c>
       <c r="G17" t="n">
-        <v>2.904539360315539e-05</v>
+        <v>0.0004929043934680521</v>
       </c>
       <c r="H17" t="n">
-        <v>4.820129106519744e-05</v>
+        <v>0.002397679490968585</v>
       </c>
       <c r="I17" t="n">
-        <v>1.84868295036722e-05</v>
+        <v>0.001458934624679387</v>
       </c>
       <c r="J17" t="n">
-        <v>2.462308657413814e-06</v>
+        <v>0.001236003125086427</v>
       </c>
       <c r="K17" t="n">
-        <v>1.687399708316661e-05</v>
+        <v>0.001391677418723702</v>
       </c>
       <c r="L17" t="n">
-        <v>8.673978300066665e-06</v>
+        <v>0.002624338492751122</v>
       </c>
       <c r="M17" t="n">
-        <v>5.250427420833148e-06</v>
+        <v>0.001107897725887597</v>
       </c>
       <c r="N17" t="n">
-        <v>1.906759280245751e-05</v>
+        <v>0.003106119344010949</v>
       </c>
       <c r="O17" t="n">
-        <v>7.749975338811055e-05</v>
+        <v>0.005615949630737305</v>
       </c>
       <c r="P17" t="n">
-        <v>1.863354009401519e-05</v>
+        <v>0.0009990991093218327</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.754568751901388e-05</v>
+        <v>0.003559280419722199</v>
       </c>
       <c r="R17" t="n">
-        <v>8.999666079034796e-07</v>
+        <v>0.002428393345326185</v>
       </c>
       <c r="S17" t="n">
-        <v>3.839917553705163e-06</v>
+        <v>6.931315874680877e-05</v>
       </c>
       <c r="T17" t="n">
-        <v>4.586372597259469e-06</v>
+        <v>0.001404742710292339</v>
       </c>
       <c r="U17" t="n">
-        <v>7.912913133623078e-06</v>
+        <v>0.0002114852977683768</v>
       </c>
       <c r="V17" t="n">
-        <v>1.646950840950012e-05</v>
+        <v>0.0002921921259257942</v>
       </c>
       <c r="W17" t="n">
-        <v>2.240675894427113e-05</v>
+        <v>0.0001872797874966636</v>
       </c>
       <c r="X17" t="n">
-        <v>7.144196388253476e-06</v>
+        <v>0.0006323570851236582</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.683292106870795e-06</v>
+        <v>0.0004292218945920467</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.812744812923484e-06</v>
+        <v>9.216366015607491e-05</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.85177076573018e-07</v>
+        <v>0.0001379501482006162</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.438188514337526e-06</v>
+        <v>0.0009251023875549436</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.69286740856478e-05</v>
+        <v>0.0002687987289391458</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.964715556823649e-05</v>
+        <v>3.880325675709173e-05</v>
       </c>
       <c r="AE17" t="n">
-        <v>4.397373231768142e-06</v>
+        <v>0.0009979454334825277</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.020353920466732e-05</v>
+        <v>0.001111682271584868</v>
       </c>
       <c r="AG17" t="n">
-        <v>5.533452167583164e-06</v>
+        <v>0.0006408462068066001</v>
       </c>
       <c r="AH17" t="n">
-        <v>7.468179319403134e-06</v>
+        <v>0.0004513573658186942</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.344816723758413e-06</v>
+        <v>0.0006091062678024173</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.142951300105779e-06</v>
+        <v>0.0007287250482477248</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.936347416631179e-06</v>
+        <v>0.0004078053752891719</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.339159093229682e-06</v>
+        <v>0.002085481770336628</v>
       </c>
       <c r="AM17" t="n">
-        <v>2.193561613239581e-06</v>
+        <v>0.0004063455562572926</v>
       </c>
       <c r="AN17" t="n">
-        <v>6.342163032968529e-06</v>
+        <v>0.0007101717055775225</v>
       </c>
       <c r="AO17" t="n">
-        <v>3.08170092466753e-06</v>
+        <v>0.001539758057333529</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.700803113635629e-05</v>
+        <v>0.001709455391392112</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6.365639819705393e-06</v>
+        <v>0.0002729654952418059</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.607839749340201e-06</v>
+        <v>2.249694080092013e-05</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.547107093661907e-07</v>
+        <v>0.0001743322645779699</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.152381537394831e-05</v>
+        <v>0.0001265766331925988</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.430725569662172e-05</v>
+        <v>0.004841728135943413</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.293675829103449e-06</v>
+        <v>0.0006004832684993744</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.387644624628592e-05</v>
+        <v>0.001275443821214139</v>
       </c>
       <c r="AX17" t="n">
-        <v>2.751862666627858e-05</v>
+        <v>0.0007486403919756413</v>
       </c>
       <c r="AY17" t="n">
-        <v>5.67547685932368e-05</v>
+        <v>0.004250217229127884</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.618828900973313e-05</v>
+        <v>0.001435567275620997</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.583443711046129e-05</v>
+        <v>0.001758241560310125</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.582939512445591e-05</v>
+        <v>0.0008693658746778965</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.334660919383168e-05</v>
+        <v>0.001090232632122934</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.802926246658899e-06</v>
+        <v>0.002982863690704107</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.525455773953581e-06</v>
+        <v>0.0008120452403090894</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.77446872839937e-05</v>
+        <v>0.000536473176907748</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.704434336919803e-05</v>
+        <v>0.003128063166514039</v>
       </c>
       <c r="BH17" t="n">
-        <v>2.490230508556124e-05</v>
+        <v>9.114231215789914e-05</v>
       </c>
       <c r="BI17" t="n">
-        <v>6.980332727835048e-06</v>
+        <v>0.0003019269497599453</v>
       </c>
       <c r="BJ17" t="n">
-        <v>4.238526344124693e-06</v>
+        <v>0.0005538219702430069</v>
       </c>
       <c r="BK17" t="n">
-        <v>9.066521670320071e-06</v>
+        <v>0.0003468439099378884</v>
       </c>
       <c r="BL17" t="n">
-        <v>4.513879048317904e-07</v>
+        <v>0.0002108050684910268</v>
       </c>
       <c r="BM17" t="n">
-        <v>2.609563125588465e-05</v>
+        <v>0.000270390446530655</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.161312775366241e-05</v>
+        <v>0.002203085459768772</v>
       </c>
       <c r="BO17" t="n">
-        <v>5.00428541272413e-06</v>
+        <v>0.0006013450911268592</v>
       </c>
       <c r="BP17" t="n">
-        <v>6.422966635000193e-06</v>
+        <v>0.001329540624283254</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.545722499140538e-06</v>
+        <v>0.0006747323204763234</v>
       </c>
       <c r="BR17" t="n">
-        <v>1.392980811942834e-05</v>
+        <v>0.0003595396992750466</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.382131631544326e-05</v>
+        <v>0.0007264447631314397</v>
       </c>
       <c r="BT17" t="n">
-        <v>1.581044307386037e-05</v>
+        <v>0.001386708812788129</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.582496679475298e-06</v>
+        <v>0.0002569862990640104</v>
       </c>
       <c r="BV17" t="n">
-        <v>1.172101747215493e-05</v>
+        <v>0.00277043366804719</v>
       </c>
       <c r="BW17" t="n">
-        <v>3.809035206359113e-06</v>
+        <v>4.615526995621622e-05</v>
       </c>
       <c r="BX17" t="n">
-        <v>5.768277333118021e-06</v>
+        <v>0.0009607351385056973</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.21105667858501e-05</v>
+        <v>0.0001640740520088002</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.534071063564625e-05</v>
+        <v>0.002503161784261465</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.860421434685122e-06</v>
+        <v>0.0007426514057442546</v>
       </c>
       <c r="CB17" t="n">
-        <v>1.386451822327217e-05</v>
+        <v>0.0003987023083027452</v>
       </c>
       <c r="CC17" t="n">
-        <v>1.861457803897792e-06</v>
+        <v>0.0003399303532205522</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.376749700440996e-07</v>
+        <v>0.0001750926167005673</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.736464810164762e-06</v>
+        <v>0.0007503445958718657</v>
       </c>
       <c r="CF17" t="n">
-        <v>1.162735088655609e-06</v>
+        <v>0.001045159297063947</v>
       </c>
       <c r="CG17" t="n">
-        <v>1.147494003816973e-06</v>
+        <v>7.370807725237682e-05</v>
       </c>
       <c r="CH17" t="n">
-        <v>8.940837687987369e-06</v>
+        <v>0.0003812357608694583</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.74837277882034e-05</v>
+        <v>0.001239218981936574</v>
       </c>
       <c r="CJ17" t="n">
-        <v>7.756063496344723e-06</v>
+        <v>0.0002070373011520132</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.103848990169354e-05</v>
+        <v>9.755103383213282e-05</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.956448159035062e-07</v>
+        <v>0.0003724817943293601</v>
       </c>
       <c r="CM17" t="n">
-        <v>8.338169550370367e-07</v>
+        <v>0.0002496834495104849</v>
       </c>
       <c r="CN17" t="n">
-        <v>5.081728431832744e-06</v>
+        <v>0.0004748578066937625</v>
       </c>
       <c r="CO17" t="n">
-        <v>9.449604476685636e-07</v>
+        <v>0.0004341364547144622</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.160963049391285e-05</v>
+        <v>0.0002853974583558738</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.472608659649268e-05</v>
+        <v>0.002039775950834155</v>
       </c>
       <c r="CR17" t="n">
-        <v>6.382208994182292e-06</v>
+        <v>0.0008118471596390009</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.972851234517293e-06</v>
+        <v>0.0003503282787278295</v>
       </c>
       <c r="CT17" t="n">
-        <v>7.332503628276754e-06</v>
+        <v>0.001041005365550518</v>
       </c>
       <c r="CU17" t="n">
-        <v>8.320598681166302e-06</v>
+        <v>0.0005802036612294614</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.39201290494384e-06</v>
+        <v>9.839523409027606e-05</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.231786654898315e-06</v>
+        <v>0.0004020377236884087</v>
       </c>
       <c r="CX17" t="n">
-        <v>8.392851214011898e-07</v>
+        <v>0.001052376930601895</v>
       </c>
       <c r="CY17" t="n">
-        <v>6.3612185385864e-07</v>
+        <v>4.939673090120777e-05</v>
       </c>
       <c r="CZ17" t="n">
-        <v>6.9046418502694e-06</v>
+        <v>0.0008846427081152797</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.972066093003377e-05</v>
+        <v>0.001515484414994717</v>
       </c>
       <c r="DB17" t="n">
-        <v>6.675934400846018e-06</v>
+        <v>7.347960490733385e-05</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.390568377246382e-05</v>
+        <v>0.0003762734122574329</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.011762030131649e-06</v>
+        <v>0.0003565390361472964</v>
       </c>
       <c r="DE17" t="n">
-        <v>3.86346710001817e-06</v>
+        <v>0.001433212426491082</v>
       </c>
       <c r="DF17" t="n">
-        <v>2.012731783906929e-05</v>
+        <v>0.001178428065031767</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.618362486828119e-06</v>
+        <v>0.0004901631036773324</v>
       </c>
       <c r="DH17" t="n">
-        <v>1.791039176168852e-05</v>
+        <v>0.001006225938908756</v>
       </c>
       <c r="DI17" t="n">
-        <v>1.446875103283674e-06</v>
+        <v>0.0006531724939122796</v>
       </c>
       <c r="DJ17" t="n">
-        <v>5.502201929630246e-07</v>
+        <v>0.001231457339599729</v>
       </c>
       <c r="DK17" t="n">
-        <v>7.592675501655322e-06</v>
+        <v>0.001183269429020584</v>
       </c>
       <c r="DL17" t="n">
-        <v>1.937387423822656e-05</v>
+        <v>0.001635462744161487</v>
       </c>
       <c r="DM17" t="n">
-        <v>1.138016432378208e-05</v>
+        <v>0.001981016481295228</v>
       </c>
       <c r="DN17" t="n">
-        <v>6.432927875721361e-06</v>
+        <v>0.0001222803985001519</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.175584086216986e-07</v>
+        <v>0.001403862028382719</v>
       </c>
       <c r="DP17" t="n">
-        <v>2.87959551314998e-07</v>
+        <v>0.0005498832324519753</v>
       </c>
       <c r="DQ17" t="n">
-        <v>1.064297066477593e-05</v>
+        <v>1.536311174277216e-05</v>
       </c>
       <c r="DR17" t="n">
-        <v>1.686647374299355e-05</v>
+        <v>0.0007500607753172517</v>
       </c>
       <c r="DS17" t="n">
-        <v>2.073742507491261e-05</v>
+        <v>0.0005702014314010739</v>
       </c>
       <c r="DT17" t="n">
-        <v>1.484271524532232e-05</v>
+        <v>0.000229058408876881</v>
       </c>
       <c r="DU17" t="n">
-        <v>7.214505785668734e-06</v>
+        <v>0.0002697466406971216</v>
       </c>
       <c r="DV17" t="n">
-        <v>3.379280315130018e-06</v>
+        <v>0.001270633074454963</v>
       </c>
       <c r="DW17" t="n">
-        <v>2.135527893187827e-06</v>
+        <v>7.338396244449541e-05</v>
       </c>
       <c r="DX17" t="n">
-        <v>4.887738668912789e-06</v>
+        <v>0.001788840629160404</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.299477147171274e-07</v>
+        <v>0.001665729214437306</v>
       </c>
       <c r="DZ17" t="n">
-        <v>1.308937135036103e-05</v>
+        <v>0.000883214408531785</v>
       </c>
       <c r="EA17" t="n">
-        <v>2.979564897032105e-06</v>
+        <v>0.001537976204417646</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.019044157146709e-05</v>
+        <v>0.0001018568582367152</v>
       </c>
       <c r="EC17" t="n">
-        <v>7.988543075043708e-06</v>
+        <v>7.800169987604022e-05</v>
       </c>
       <c r="ED17" t="n">
-        <v>3.432350922594196e-06</v>
+        <v>0.001315104309469461</v>
       </c>
       <c r="EE17" t="n">
-        <v>1.714949212328065e-05</v>
+        <v>0.0007037855684757233</v>
       </c>
       <c r="EF17" t="n">
-        <v>3.088315452259849e-06</v>
+        <v>0.0005973448278382421</v>
       </c>
       <c r="EG17" t="n">
-        <v>9.058093382918742e-06</v>
+        <v>4.470688872970641e-05</v>
       </c>
       <c r="EH17" t="n">
-        <v>7.497086699004285e-06</v>
+        <v>0.0005582688027061522</v>
       </c>
       <c r="EI17" t="n">
-        <v>1.395925573888235e-05</v>
+        <v>0.0002076074597425759</v>
       </c>
       <c r="EJ17" t="n">
-        <v>4.828635155718075e-06</v>
+        <v>0.0009077025461010635</v>
       </c>
       <c r="EK17" t="n">
-        <v>7.328871106437873e-06</v>
+        <v>0.000340718834195286</v>
       </c>
       <c r="EL17" t="n">
-        <v>6.559407211170765e-06</v>
+        <v>1.938379864441231e-05</v>
       </c>
       <c r="EM17" t="n">
-        <v>1.01737750810571e-05</v>
+        <v>0.0002136744151357561</v>
       </c>
       <c r="EN17" t="n">
-        <v>5.403806426329538e-06</v>
+        <v>0.0003717436920851469</v>
       </c>
       <c r="EO17" t="n">
-        <v>2.228117864433443e-06</v>
+        <v>0.0001818822493078187</v>
       </c>
       <c r="EP17" t="n">
-        <v>8.25400093162898e-06</v>
+        <v>0.0008649635128676891</v>
       </c>
       <c r="EQ17" t="n">
-        <v>7.230170922412071e-06</v>
+        <v>3.80657147616148e-05</v>
       </c>
       <c r="ER17" t="n">
-        <v>1.266184153791983e-05</v>
+        <v>0.0002355416800128296</v>
       </c>
       <c r="ES17" t="n">
-        <v>5.302104909787886e-06</v>
+        <v>0.0001721542066661641</v>
       </c>
       <c r="ET17" t="n">
-        <v>6.97286986905965e-06</v>
+        <v>0.001492862356826663</v>
       </c>
       <c r="EU17" t="n">
-        <v>9.989112186303828e-07</v>
+        <v>0.0001523578685009852</v>
       </c>
       <c r="EV17" t="n">
-        <v>2.783749914669897e-05</v>
+        <v>0.0005819621146656573</v>
       </c>
       <c r="EW17" t="n">
-        <v>1.932708255480975e-05</v>
+        <v>0.0003963396302424371</v>
       </c>
       <c r="EX17" t="n">
-        <v>1.700878442534304e-06</v>
+        <v>0.000119730771984905</v>
       </c>
       <c r="EY17" t="n">
-        <v>2.024228933805716e-06</v>
+        <v>0.000790008925832808</v>
       </c>
       <c r="EZ17" t="n">
-        <v>1.019489332065859e-06</v>
+        <v>0.0007732252706773579</v>
       </c>
       <c r="FA17" t="n">
-        <v>9.684795259090606e-07</v>
+        <v>0.0001160407700808719</v>
       </c>
       <c r="FB17" t="n">
-        <v>8.194044312404003e-06</v>
+        <v>0.0004805945209227502</v>
       </c>
       <c r="FC17" t="n">
-        <v>1.768353286024649e-05</v>
+        <v>0.001387955388054252</v>
       </c>
       <c r="FD17" t="n">
-        <v>9.144535397354048e-06</v>
+        <v>0.0002296790771652013</v>
       </c>
       <c r="FE17" t="n">
-        <v>1.340336166322231e-05</v>
+        <v>4.327643546275795e-05</v>
       </c>
       <c r="FF17" t="n">
-        <v>3.323086275486276e-06</v>
+        <v>0.0001479025231674314</v>
       </c>
       <c r="FG17" t="n">
-        <v>5.574707302002935e-06</v>
+        <v>0.0005027813604101539</v>
       </c>
       <c r="FH17" t="n">
-        <v>7.37645950721344e-06</v>
+        <v>0.0003793029754888266</v>
       </c>
       <c r="FI17" t="n">
-        <v>7.989605364855379e-06</v>
+        <v>0.000791694619692862</v>
       </c>
       <c r="FJ17" t="n">
-        <v>1.550434535602108e-05</v>
+        <v>0.001210794551298022</v>
       </c>
       <c r="FK17" t="n">
-        <v>7.602463028888451e-06</v>
+        <v>0.0004166975850239396</v>
       </c>
       <c r="FL17" t="n">
-        <v>1.578780211275443e-05</v>
+        <v>0.00195931363850832</v>
       </c>
       <c r="FM17" t="n">
-        <v>5.547090040636249e-06</v>
+        <v>0.0002651913091540337</v>
       </c>
       <c r="FN17" t="n">
-        <v>1.502699888078496e-06</v>
+        <v>0.0002639318117871881</v>
       </c>
       <c r="FO17" t="n">
-        <v>1.566126798024925e-06</v>
+        <v>0.001517573371529579</v>
       </c>
       <c r="FP17" t="n">
-        <v>2.023197794187581e-06</v>
+        <v>0.0007089662249200046</v>
       </c>
       <c r="FQ17" t="n">
-        <v>1.292723391088657e-05</v>
+        <v>0.000825682538561523</v>
       </c>
       <c r="FR17" t="n">
-        <v>1.871930635388708e-06</v>
+        <v>0.001907067722640932</v>
       </c>
       <c r="FS17" t="n">
-        <v>1.292261003982276e-06</v>
+        <v>0.001593316323123872</v>
       </c>
       <c r="FT17" t="n">
-        <v>2.970270725199953e-05</v>
+        <v>0.002219371031969786</v>
       </c>
       <c r="FU17" t="n">
-        <v>2.053229945886414e-05</v>
+        <v>0.001080773072317243</v>
       </c>
       <c r="FV17" t="n">
-        <v>3.537444626999786e-06</v>
+        <v>0.001360381371341646</v>
       </c>
       <c r="FW17" t="n">
-        <v>6.724016202497296e-06</v>
+        <v>0.002326868008822203</v>
       </c>
       <c r="FX17" t="n">
-        <v>1.144425004895311e-05</v>
+        <v>0.001799254911020398</v>
       </c>
       <c r="FY17" t="n">
-        <v>7.653505235794e-06</v>
+        <v>0.0002240449975943193</v>
       </c>
       <c r="FZ17" t="n">
-        <v>3.330958179503796e-06</v>
+        <v>0.0006541137699969113</v>
       </c>
       <c r="GA17" t="n">
-        <v>7.924590136099141e-06</v>
+        <v>0.001217689947225153</v>
       </c>
       <c r="GB17" t="n">
-        <v>6.648491762462072e-06</v>
+        <v>0.0009754875209182501</v>
       </c>
       <c r="GC17" t="n">
-        <v>2.359005156904459e-05</v>
+        <v>0.0005278683383949101</v>
       </c>
       <c r="GD17" t="n">
-        <v>3.530037702148547e-06</v>
+        <v>5.859821249032393e-05</v>
       </c>
       <c r="GE17" t="n">
-        <v>6.094596301409183e-06</v>
+        <v>0.000263521826127544</v>
       </c>
       <c r="GF17" t="n">
-        <v>8.010078090592287e-06</v>
+        <v>0.0001408884127158672</v>
       </c>
       <c r="GG17" t="n">
-        <v>5.458432497107424e-06</v>
+        <v>6.910758384037763e-05</v>
       </c>
     </row>
   </sheetData>
